--- a/z_RequestData/jobsearch_data104.xlsx
+++ b/z_RequestData/jobsearch_data104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,10 +481,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>20260209</t>
-        </is>
+      <c r="A2" t="n">
+        <v>20260209</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -539,10 +537,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A3" t="n">
+        <v>20260223</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -601,10 +597,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>20260213</t>
-        </is>
+      <c r="A4" t="n">
+        <v>20260213</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -656,10 +650,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>20260222</t>
-        </is>
+      <c r="A5" t="n">
+        <v>20260222</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -714,10 +706,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>20260202</t>
-        </is>
+      <c r="A6" t="n">
+        <v>20260202</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -769,10 +759,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A7" t="n">
+        <v>20260223</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -825,10 +813,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20260219</t>
-        </is>
+      <c r="A8" t="n">
+        <v>20260219</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -880,10 +866,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A9" t="n">
+        <v>20260211</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -935,10 +919,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A10" t="n">
+        <v>20260223</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -992,10 +974,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20260126</t>
-        </is>
+      <c r="A11" t="n">
+        <v>20260126</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1044,10 +1024,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A12" t="n">
+        <v>20260223</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1098,10 +1076,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20260120</t>
-        </is>
+      <c r="A13" t="n">
+        <v>20260120</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1154,10 +1130,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20260219</t>
-        </is>
+      <c r="A14" t="n">
+        <v>20260219</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1207,10 +1181,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20260126</t>
-        </is>
+      <c r="A15" t="n">
+        <v>20260126</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1261,10 +1233,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A16" t="n">
+        <v>20260223</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1315,10 +1285,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A17" t="n">
+        <v>20260211</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1369,10 +1337,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20260206</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20260206</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1423,10 +1389,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20260217</t>
-        </is>
+      <c r="A19" t="n">
+        <v>20260217</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1480,10 +1444,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20260212</t>
-        </is>
+      <c r="A20" t="n">
+        <v>20260212</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1535,10 +1497,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20260223</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1590,10 +1550,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A22" t="n">
+        <v>20260223</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1642,10 +1600,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A23" t="n">
+        <v>20260223</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1697,10 +1653,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20260221</t>
-        </is>
+      <c r="A24" t="n">
+        <v>20260221</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1754,10 +1708,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A25" t="n">
+        <v>20260210</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1817,10 +1769,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20260212</t>
-        </is>
+      <c r="A26" t="n">
+        <v>20260212</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1873,10 +1823,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A27" t="n">
+        <v>20260223</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1928,10 +1876,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20260212</t>
-        </is>
+      <c r="A28" t="n">
+        <v>20260212</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1981,10 +1927,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A29" t="n">
+        <v>20260223</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2037,10 +1981,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A30" t="n">
+        <v>20260223</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2127,10 +2069,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>20260212</t>
-        </is>
+      <c r="A31" t="n">
+        <v>20260212</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2181,10 +2121,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A32" t="n">
+        <v>20260223</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2234,10 +2172,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>20260128</t>
-        </is>
+      <c r="A33" t="n">
+        <v>20260128</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2287,10 +2223,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20260222</t>
-        </is>
+      <c r="A34" t="n">
+        <v>20260222</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2345,10 +2279,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A35" t="n">
+        <v>20260211</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2402,10 +2334,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A36" t="n">
+        <v>20260223</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2457,10 +2387,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>20260219</t>
-        </is>
+      <c r="A37" t="n">
+        <v>20260219</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2510,10 +2438,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A38" t="n">
+        <v>20260223</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2565,10 +2491,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>20260213</t>
-        </is>
+      <c r="A39" t="n">
+        <v>20260213</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2619,10 +2543,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A40" t="n">
+        <v>20260210</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2676,10 +2598,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>20251228</t>
-        </is>
+      <c r="A41" t="n">
+        <v>20251228</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2731,10 +2651,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A42" t="n">
+        <v>20260211</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2787,10 +2705,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20260206</t>
-        </is>
+      <c r="A43" t="n">
+        <v>20260206</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2840,10 +2756,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A44" t="n">
+        <v>20260211</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2895,10 +2809,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>20260202</t>
-        </is>
+      <c r="A45" t="n">
+        <v>20260202</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2950,10 +2862,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20260127</t>
-        </is>
+      <c r="A46" t="n">
+        <v>20260127</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3006,10 +2916,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A47" t="n">
+        <v>20260211</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3064,10 +2972,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A48" t="n">
+        <v>20260223</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3120,10 +3026,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>20260108</t>
-        </is>
+      <c r="A49" t="n">
+        <v>20260108</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3177,10 +3081,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>20260205</t>
-        </is>
+      <c r="A50" t="n">
+        <v>20260205</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3229,10 +3131,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>20251224</t>
-        </is>
+      <c r="A51" t="n">
+        <v>20251224</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3284,10 +3184,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A52" t="n">
+        <v>20260210</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3337,10 +3235,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A53" t="n">
+        <v>20260211</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3390,10 +3286,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>20260123</t>
-        </is>
+      <c r="A54" t="n">
+        <v>20260123</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3447,10 +3341,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A55" t="n">
+        <v>20260223</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3503,10 +3395,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20260120</t>
-        </is>
+      <c r="A56" t="n">
+        <v>20260120</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3562,10 +3452,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>20260219</t>
-        </is>
+      <c r="A57" t="n">
+        <v>20260219</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3615,10 +3503,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A58" t="n">
+        <v>20260223</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3670,10 +3556,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>20260213</t>
-        </is>
+      <c r="A59" t="n">
+        <v>20260213</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3726,10 +3610,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A60" t="n">
+        <v>20260223</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3780,10 +3662,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>20260222</t>
-        </is>
+      <c r="A61" t="n">
+        <v>20260222</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3837,10 +3717,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A62" t="n">
+        <v>20260223</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3893,10 +3771,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20260220</t>
-        </is>
+      <c r="A63" t="n">
+        <v>20260220</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3951,10 +3827,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20260219</t>
-        </is>
+      <c r="A64" t="n">
+        <v>20260219</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4004,10 +3878,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20260212</t>
-        </is>
+      <c r="A65" t="n">
+        <v>20260212</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4056,10 +3928,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20260221</t>
-        </is>
+      <c r="A66" t="n">
+        <v>20260221</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4114,10 +3984,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A67" t="n">
+        <v>20260210</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4170,10 +4038,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A68" t="n">
+        <v>20260223</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4228,10 +4094,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>20260217</t>
-        </is>
+      <c r="A69" t="n">
+        <v>20260217</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4285,10 +4149,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>20260204</t>
-        </is>
+      <c r="A70" t="n">
+        <v>20260204</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4340,10 +4202,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20251120</t>
-        </is>
+      <c r="A71" t="n">
+        <v>20251120</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4395,10 +4255,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A72" t="n">
+        <v>20260210</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4449,10 +4307,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20260209</t>
-        </is>
+      <c r="A73" t="n">
+        <v>20260209</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4503,10 +4359,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A74" t="n">
+        <v>20260223</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4560,10 +4414,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A75" t="n">
+        <v>20260223</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4615,10 +4467,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>20260129</t>
-        </is>
+      <c r="A76" t="n">
+        <v>20260129</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4669,10 +4519,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A77" t="n">
+        <v>20260223</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4724,10 +4572,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A78" t="n">
+        <v>20260211</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4784,10 +4630,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>20260125</t>
-        </is>
+      <c r="A79" t="n">
+        <v>20260125</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4839,10 +4683,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20260213</t>
-        </is>
+      <c r="A80" t="n">
+        <v>20260213</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4893,10 +4735,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>20260213</t>
-        </is>
+      <c r="A81" t="n">
+        <v>20260213</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4950,10 +4790,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>20260202</t>
-        </is>
+      <c r="A82" t="n">
+        <v>20260202</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5007,10 +4845,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>20260123</t>
-        </is>
+      <c r="A83" t="n">
+        <v>20260123</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5062,10 +4898,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A84" t="n">
+        <v>20260223</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5117,10 +4951,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A85" t="n">
+        <v>20260223</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5171,10 +5003,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>20260209</t>
-        </is>
+      <c r="A86" t="n">
+        <v>20260209</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5237,10 +5067,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A87" t="n">
+        <v>20260210</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5293,10 +5121,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A88" t="n">
+        <v>20260223</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -5348,10 +5174,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A89" t="n">
+        <v>20260223</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -5402,10 +5226,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A90" t="n">
+        <v>20260223</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5458,10 +5280,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>20260217</t>
-        </is>
+      <c r="A91" t="n">
+        <v>20260217</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5512,10 +5332,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A92" t="n">
+        <v>20260223</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5566,10 +5384,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A93" t="n">
+        <v>20260223</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5620,10 +5436,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20260209</t>
-        </is>
+      <c r="A94" t="n">
+        <v>20260209</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5674,10 +5488,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20260212</t>
-        </is>
+      <c r="A95" t="n">
+        <v>20260212</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -5729,10 +5541,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20260202</t>
-        </is>
+      <c r="A96" t="n">
+        <v>20260202</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -5785,10 +5595,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A97" t="n">
+        <v>20260223</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5839,10 +5647,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A98" t="n">
+        <v>20260211</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5894,10 +5700,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A99" t="n">
+        <v>20260223</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -5948,10 +5752,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>20260206</t>
-        </is>
+      <c r="A100" t="n">
+        <v>20260206</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6019,10 +5821,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A101" t="n">
+        <v>20260223</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6073,10 +5873,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>20260213</t>
-        </is>
+      <c r="A102" t="n">
+        <v>20260213</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6129,10 +5927,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>20260220</t>
-        </is>
+      <c r="A103" t="n">
+        <v>20260220</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -6183,10 +5979,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A104" t="n">
+        <v>20260223</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -6239,10 +6033,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>20260130</t>
-        </is>
+      <c r="A105" t="n">
+        <v>20260130</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -6292,10 +6084,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>20260211</t>
-        </is>
+      <c r="A106" t="n">
+        <v>20260211</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -6347,10 +6137,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A107" t="n">
+        <v>20260210</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -6405,10 +6193,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A108" t="n">
+        <v>20260223</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -6458,10 +6244,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A109" t="n">
+        <v>20260223</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -6514,10 +6298,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>20251124</t>
-        </is>
+      <c r="A110" t="n">
+        <v>20251124</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -6567,10 +6349,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
+      <c r="A111" t="n">
+        <v>20260101</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -6616,6 +6396,6126 @@
       <c r="J111" t="inlineStr">
         <is>
           <t>https://www.104.com.tw/job/89pxp</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>燦坤總部-資訊部-.NET軟體工程師</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>燦坤實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>家庭電器／設備及用品零售業</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>台北市內湖區 堤頂大道一段331號5樓</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1.	既有系統維運 ASP.NET WebForm (VB.NET)。
+2.	新專案開發 (使用.NET 6以上版本 C# / Docker等主流技術)。
+3.	完成主管交辦任務。
+4.	技術文件撰寫。</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7akaq</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>機電工程人員</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>鈺通營造工程股份有限公司</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">嘉義縣太保市 </t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1. 機電統包/給排水/弱電/空調/消防設備系統等
+2. 根據機電設計圖紙進行現場施工作業
+3. 協調土建介面及平行包間
+4. 施工自主檢查及品質管理
+5. 估驗計價資料之製作
+6. 現場工程監工及作業
+7. 材料送審與文書作業、機電圖面管理</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/86f15</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>替您錄科技股份有限公司(TGC Taiwan, Inc.)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>多媒體傳播相關業</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>台北市松山區 八德路四段760號6樓</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位熱情且富有才華的資料工程師，加入我們的團隊，協助解決廣告投遞的資料內容。在這裡有大量的數據供你發揮所長，將學過的知識及方法應用到實務的工作上。
+我們希望你具備以下三大特質：
+對資料工程領域有強烈興趣和熱情 。
+重視團隊合作，具備</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ekil</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資料工程師</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>崴拓資訊有限公司</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>▎ What You'll Do
+1. 數據中心資料整理統計和資料流程維運與開發
+2. Flink即時滾表維運與開發
+3. 視覺化儀表板維運與開發
+▎ What We're Looking For 
+1. 撰寫Python(Pandas、</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vdvc</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>數據工程師（Data Engineer）</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>創代科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路101號10樓</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>服務具備高可用性與擴展性。
+- 撰寫技術文件與資料流程說明，建立標準化與可維護的工程流程。
+---
+## 三、必要技能與條件
+- 熟悉至少一種程式語言（Python / Java / C# 其一）。
+- 熟悉 SQL，具備關聯式資料庫（如</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ys29</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20260210</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>艾捷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>台中市南屯區 大墩十街300號</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Data 團隊正在尋找一位充滿熱忱的【資料工程師】加入我們！
+熟悉 Data Warehouse、大數據、雲端 (GCP/AWS) 和 CICD
+歡迎加入我們，一起打造高效穩健的數據基石
+【日常工作內容】
+1.開發數據流、報表結轉程式
+2.發</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/88w4t</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>20260211</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>中國信託證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>台北市南港區 經貿二路188號12樓</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>【職務主要內容】
+1. 建立開發標準與規範：制定資料交換標準、建立開發 SOP。
+2. 資料管道與系統串接(ETL/Integration)：協助系統間的資料串接與整合、優化舊有系統的 ETL 流程。
+3. 數據品質與監控：建立預警機制，確保資料</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n6z2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>HUA AO_香港商創金科技有限公司</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大同區 </t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>/CD、Docker 等基礎 DevOps 工具者佳
+3. 參與團隊數據治理與標準制定經驗者尤佳
+【任職資格】
+a. 資訊工程、資料科學、統計、資訊管理等相關理工科系本科以上學歷4年以上
+b. 具備資料工程、BI或數據相關工作經驗 
+c. 樂於</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pr4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>核桃運算股份有限公司</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路一段9號4樓</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備 3-5 年經驗的資料工程師，加入我們的數據團隊。您將負責設計、構建並優化高效率的 Data Pipeline，確保資料從來源端到分析端的準確性與即時性。 此職位不僅需要強大的 Python 與 ETL 開發能力，更需要您對</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8waxf</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20260126</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>文境資科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>專門設計相關業</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師
+1.資料稽核(Data Auditing)、收集(Data Collection)、整合作業(Data Integration) 等資料分析前處理作業
+2.有MS SQL server、SSIS、SSRS</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7g1tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>科技部_Data Engineer 數據工程師</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>美好證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路三段２號4樓</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>/AI 智能化運轉體系，以先進的數據工程、資料平台與 AI 技術，推動投資研究、產品創新與顧問服務的核心能力全面升級。
+此角色將負責設計、建置與維運公司的核心數據基礎設施 (Data &amp; AI Platform)，讓資料能夠在各產品與團隊間穩定流</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7b6bq</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D4000 資料工程師</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>富邦媒體科技股份有限公司(富邦momo)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街96號4樓</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>踐。
+•	確保資料處理流程與存取符合內部資安規範及法規要求。
+6. 創新技術研究
+•	研究並導入新興的資料處理技術，確保內部技術能對齊市場主流技術，確保架構能與目前主流的技術生態系做結合。
+•	探索AI技術應用於資料工程及大數據處理領域，規劃小型驗</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y67g</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>侍達遊戲藝術有限公司</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>台北市信義區 東興路41號5樓</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1. 根據分析需求進行資料建模，並提供視覺化的資料呈現。
+2. 提供分析數據及報表。
+3. 設計與開發資料分析所需要的工具。
+[能力需求]
+1. 具備程式開發經驗 (Python/Golang等)。
+2. 具備 SQL/NoSQL 使用經驗</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85yiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>億力資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.熟悉使用Tableau設計報表與儀表板,至少具備1年以上經驗。
+2.熟悉撰寫SQL進行資料前處理,至少具備1年以上經驗
+</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xplj</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>【新擴編】Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>愛酷智能科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化南路一段2號5樓</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>步汰換舊有的 Digdag 流程。
+2. ETL/ELT 流程開發： 串接 PostgreSQL 與 MongoDB 以及外部資料 等多源數據，清洗並導入 BigQuery。
+3. 數據倉儲模型設計： 使用 dbt 開發與維護數據模型，優化 SQL</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wccg</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20260209</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>東海大學智慧永續循環經濟研究中心誠徵資料工程師</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>東海大學</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>其他教育服務業</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道四段1727號</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具環境工程背景、能將專業知識轉化為結構化資料與知識模型的人才，加入智慧永續循環研究中心，共同建構以環工知識為核心的 AI 與知識圖譜系統。
+本職位的核心任務不是單純做資料清洗或模型訓練，而是：
+把環境工程的「機制、概念與流程」</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y8zy</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>徵  數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>臺北醫學大學</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用之</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xi1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>(C6) 資深數據工程師Senior Data Engineer（內湖）</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>【職位說明】
+參與智慧城市 AI 賦能產品開發，負責建置企業級數據平台(Data as a Service, DaaS)，處理各種形式的資料，並進行完善的資料治理、血緣追蹤與監控。最終將整合生成式 AI（Generative AI）功能，提供智慧</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p0av</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>關貿網路股份有限公司</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>台北市南港區 三重路19之13號6樓(115)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1.大數據應用系統開發維護及專案支援。
+2.數據處理及ETL架構規劃及開發。
+3.熟悉java，會Python/R或撰寫分析演算法程式尤佳。</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4ftgq</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20260126</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Garena - (Senior) Data Engineer (資深)資料工程師</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Garena_新加坡商競舞電競有限公司臺灣分公司</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>台北市信義區 松高路11號16樓</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Hi，勇者！我們是 Garena 的 Data Team，我們 Data 夥伴角色組織完善，為 Garena 海內外的遊戲規劃、建構並維護資料量達 PB 級別的全地端資料倉儲，並與數據分析師 (Data Analyst) 合作，將遊戲內各項有趣的</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8rady</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>永慶房產集團_永慶房屋仲介股份有限公司</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段77號12樓</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>永慶房產集團為房仲產業龍頭，用科技創新引領創新變革，歡迎IT領域的優秀夥伴加入!
+工作內容如下：
+1.規劃集團資料流程，達成資料整合綜效。
+2.建置企業數據中台，管控集團資料倉儲品質與正確性。
+3.與資料分析師協同合作，進行資料分析前處理，提供</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78pf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>資料工程師 ETL / Data Engineer | 半導體 | 工作地點: 新北市</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tezerakt_美商立方體有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新北市板橋區 </t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>[請提供英文簡歷]
+[本職缺] 
+為 Data Infrastructure Support Engineer(資料工程)，主要負責半導體製造產業 ／雲端資料基礎建設的功能開發與強化。工作範疇包含新data pipeline 的 parsing</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yq4u</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>資深工程師(桃園建案)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>德美營造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">桃園市桃園區 </t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 70,000元</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>6年以上</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>高中職以下、高中職、專科</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>建築、安全法規和其他章程。
+5. 預先檢查分包廠商施工前之準備工作。
+6. 確實填寫監工日報表，以留下詳實工程進行的記錄資料。
+7. 進行進場材料品質之點收、存放、使用查驗及結算。
+8. 依據施工狀況向分包廠商協商提出各項建議（如：施工方式之改進、</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7k9at</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>【雲端維運部】DevOps 主任工程師</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>向上集團_向上國際科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>台中市北區 健行路356號</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>月薪 50,000 ~ 85,000元</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>資料異地備分、備援機制穩定運作。
+-持續關注成本，定期檢視並配置合適的雲服務資源。
+● 人員指導
+-工作分配及日常專業操作指導。
+-持續型工作的 SOP 制定與文件撰寫、管理。
+-定期進行團隊工作效率檢視與問題檢討。
+【其他條件】
+●網路設定及資</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8c8cv</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>【外商】[FIN] Sr. Data Engineer／資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號20樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>年薪 1,200,000 ~ 1,400,000元</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pipeline (資料流) 的設計、搭建與優化能力，熟悉 Dagster 或 Airflow 等排程工具。
+• 5 年以上資深資料工程師或相關經驗，並具備獨立主導專案的能力。
+• 卓越的需求訪談與業務邏輯理解能力，能將複雜的技術概念清晰地傳達給非技術背</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dq30</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>英屬開曼群島商萬里雲互聯股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段333號33樓</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>【職務說明】
+       我們正在尋找一位具備高度專業技能的資深資料工程師，加入我們快速成長的資料與AI解決方案團隊。此角色將負責設計並交付可擴展的資料平台、建置資料管道，並推動雲端/地端環境下的資料搬遷，以銜接AI分析應用落地。</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p7ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>新加坡商昇新科技股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞湖街58號5樓</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>加入我們的團隊，負責設計 ETL pipeline，將 MySQL 資料轉換並存入 BigQuery。
+你將與 DBA 和 BI 團隊緊密合作，確保資料質量與查詢效能，並支援資料報表。此職位適合喜歡挑戰、解決資料問題的你！
+【學習與成長機會】</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x352</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>資料工程師 (BI)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>(本職務主要為技術工作而非單純的數據分析)
+1.  商業智慧(BI)專案需求訪談、系統分析並製作系統需求規格書文件
+2.  撰寫整合測試計畫書、測試案例、準備測試資料及測試
+3.  Metadata 中介層設計、Dashboard、Report設</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/37tef</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ETL資料工程師(FJ)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市松山區 </t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>．設計、開發與維護 ETL 流程，確保資料的正確性與一致性
+．使用 NiFi、SSIS 或其他 ETL 工具進行資料擷取、轉換與載入
+．優化現有流程效能，提升資料處理速度與可靠性
+．支援內部系統或跨團隊資料整合專案
+．撰寫並維護技術文件，確保流程</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8usc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>20251228</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>量測/資料工程師(竹北)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>艾思特能源股份有限公司</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>精密儀器相關製造業</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新竹縣竹北市 </t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1. 協助執行太陽能電站之現場檢測與量測作業
+2. 蒐集並整理現場檢測資料，撰寫相關測試與檢測紀錄
+3. 進行數據分析與報告撰寫，需熟悉 Word 文件排版 與 Excel 樞紐分析
+4. 協助撰寫及優化 檢測SOP 與 測試流程文件，建立</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8uri5</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>20260214</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>資深資料工程師 Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>秀曜匯智股份有限公司</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>數位內容產業</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>台北市南港區 重陽路120號2樓207室</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Job Summary
+We are seeking a highly skilled and experienced Senior Data Engineer to join our growing data team. In this role, you will design, build, and maintain scalable data pipelines and infrastructure that support analytics, machine learning, and business intelligence initiatives. You will work closely with data scientists, analysts, and software engineers to ensure data is accessible, reliable, and secure.
+Key Responsibilities
+￭ Design and implement scalable data pipelines for real-time streaming and batch ETL/ELT processing.
+￭ Architect data storage solutions (data lakes, warehouses) to support diverse analytics and ML needs.
+￭ Develop and optimize real-time data streaming systems and corresponding dashboards.
+￭ Ensure data quality, integrity, security, and governance across systems.
+￭ Plan and execute data collection, storage, and maintenance strategies for varied requirements.
+￭ Collaborate with data scientists, analysts, and stakeholders to deliver business-driven data solutions.
+￭ Mentor junior engineers and promote data engineering best practices.
+￭ Monitor and enhance data infrastructure performance and scalability.
+Qualifications
+￭ 5+ years of data engineering experience.
+￭ Expertise in SQL, Python, and big data tools (e.g., Spark, Kafka).
+￭ Familiar with data representation tools (e.g., Tableau, Looker Studio, Superset).
+￭ Proficiency with cloud platforms (e.g., GCP, AWS, Azure) and data services (e.g., 
+BigQuery, Snowflake).
+￭ Proven experience in real-time streaming systems, dashboard development, and large-scale ETL design.
+￭ Strong knowledge of data modeling, governance, and security practices.
+￭ Bachelor’s degree in Computer Science, Engineering, or related field (Master’s preferred).
+￭ Excellent problem-solving, collaboration, and communication skills.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ryui</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>20260301</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer (AI &amp; Application)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>群越廣告科技有限公司</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市南港區 </t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>月薪 70,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>職稱： 資料工程師 Data Engineer (AI &amp; Application)
+我們尋找一位資料敏銳度高、擁有穩健工程實作力的資料工程師，加入我們的遊戲平台廣告競標系統！ 這個職位非常適合熟悉資料處理流程、具備 API 設計與雲端部署經驗</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xjj4</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RD-數據工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>順立智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>台北市內湖區 內湖路一段360巷8號7樓</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>板（命名、開發流程、文件）
+【Must Have】
+－2+ 年資料工程/資料管線相關經驗
+－熟悉 SQL + Python
+－熟悉任一資料倉儲
+－有資料品質/監控/回溯經驗
+－具產品數據概念</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7njt5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>【外商】[RC-Data] Data Engineer／數據工程師</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路捷運中山站六號出口共構大樓</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備雲端與資料工程經驗的 Data Engineer，負責打造穩定且可擴展的資料平台，並協助建立從資料擷取、清洗、建模到資料產品化的完整數據管線（data pipeline）。此角色將與數據團隊、AI 團隊和業務單位密切合作，確保</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wpc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>雲端數據工程師</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>君綺生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>美容／美體業</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>台北市信義區 松智路1號</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>部門介紹:
+我們是集團組織擴編成立的新部門, 在這工作你將會體驗全雲的工作環境, 包含AWS雲端服務及工具, 在工作中學習專案管理、資料庫管理、雲端服務等技術
+工作內容
+1. 參與雲端數據架構發展規劃，設計資料處理、儲存、分析架構，以符合數據</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mcsu</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>20260120</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>數據工程師/Data Engineer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>大數據股份有限公司</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路三段3號7樓</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> API開發與維護
+6.依能力調整Job Title(資深數據工程師/數據工程師)
+【必要技能】 
+1.熟練運用AI工具進行開發上的協作
+2.熟悉Python語法
+3.充分了解HTML結構，能解析網頁交換資料的順序步驟　 
+4.熟悉Git
+5.熟悉</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5o7vg</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>20260301</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>【派遣至知名外商銀行 / 6個月短期專案】Data Engineer資料工程師_年後報到_201HY</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>萬寶華企業管理顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>月薪 65,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 撰寫專案文件並維持程式碼清晰度
+【資格條件】
+- 大學以上學歷
+- 1年以上資料分析 / 資料工程 / 資料清洗相關經驗
+- 必備中階 SQL技能 (Python為加分項)
+</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xaiq</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>資料工程師/後端工程師 (Data Engineer / Backend Engineer)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>典通股份有限公司</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>台北市中正區 愛國西路9號7樓</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>與管理，包括機器環境設定及基礎架構設計（Infrastructure）。
+4. 整合數據管道和資料流處理流程，支持數據分析需求及前端服務。
+5. 與數據分析師、前端工程師及其他業務部門緊密協作，理解並滿足多樣化的數據需求。
+您可以透過以下聯結認識</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8jvge</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>春樹科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路62號9樓</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>能、安全與高可用性有信仰，確保系統不僅「能跑」更能「長跑」。
+-AI 協作夥伴 (MLOps Companion)： 模型落地的推手。與演算法團隊聯手，打造高效的 MLOps 循環。
+我們在意的工程文化
+解決問題： 面對不確定性，能拆解問題並快速</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xjqj</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>柯南國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段1號7樓</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>構、數據分析團隊相關工作經驗。
+8.曾參與問卷、稽查相關之資料處理或專案設計。
+9.能與非工程背景同事溝通需求、用白話說明技術功能。
+10.具備創新思維、主動與責任心並樂於團隊協作。</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wktx</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>旺旺中時媒體集團_(CT) Data Engineer（資料工程師）</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>旺旺中時媒體集團_工商財經數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>電視業</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>台北市萬華區 艋舺大道303號</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>本職位為Data Engineer（資料工程師）
+（依資歷可掛 Senior Data Engineer）
+工作內容 :
+● 設計與實作跨平台資料收集流程（API 與後台匯出並行）
+● 串接並維運以下類型資料來源（依實際情況）：
+YouTube</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wttd</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>大豐有線電視股份有限公司</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>電視業</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>新北市土城區 中華路二段207號</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.集團資料倉儲導入，系統設計、資料超市設計、規格撰寫、程式開發、維運。
+2.ETL流程自動化規劃、設計、開發、撰寫維運、監控。
+3.BI報表規劃、設計、維運。
+4.系統日常維運與問題處理、集團營運報表製作。
+</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8uj1y</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>資料工程師(竹科)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>前進國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新竹市 </t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>ETL Job Migration</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x2u8</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>資料分析工程師 (PS2A0)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>資拓宏宇國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1.熟悉使用Tableau設計報表與儀表板,至少具備1年以上經驗。
+2.熟悉撰寫SQL進行資料前處理,至少具備1年以上經驗。</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8s7c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>MIS網管人員</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>華冠投顧_華冠證券投資顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路二段100號6樓之2</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>月薪 36,000 ~ 40,000元</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>工作內容：
+1. 公司內部電腦、印表機、事務機等設備之軟、硬體 安裝、設定 障礙排除
+2. 機房維運管理及維護
+3. 相關資訊設備資產管理
+4. Linux 伺服器主機軟體安裝、設定(Ubuntu)
+5. Windows Server系統、資料備</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ctkj</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>現場工程師(嘉義)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>宏瑞制程工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>嘉義縣朴子市 台積電AP7廠區</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 45,000元</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.工地現場的狀況處理
+2.施工進度與品質控管
+3.工程介面協調及作業人力協調
+4.工程資料建檔文書作業
+5.需視工程進度配合加班
+6.會cad尤佳
+7.需配合公司外派
+</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8rvil</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>20260125</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1.在Hadoop架構的資料倉儲(Data Warehouse)上建立具備擴充性與高可靠性的資料產品，為數據科學家與業務團隊提供穩健的資料基礎。
+2.與數據科學家和業務分析團隊合作，理解需求並提供適用的資料解決方案。
+3.設計並構建</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n58n</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>20260210</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>遊戲資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>吉恩立數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段106號5樓</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>我們找的就是你：善於溝通、邏輯清晰及執行力的工程師 !
+負責一款遊戲，
+從資料庫初期的建置發佈以及遊戲整體環境建置，到後續服務的長久運行管理。
+在這裡你不會感到孤單，會有同仁一起參與合作與營運，當然，熟悉後也有需要獨自運作的時刻。
+【工作任務</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tymj</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>資料科學工程師 (Data Engineer) -- 資料科學實驗室 (數數發中心,DDT)_I00018190</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[工作內容]
+職務包含但不限於以下內容
+- 基於 Python 語言之產品開發，推廣及後續維護
+- Docker/Kubernetes 相關技術應用研發
+- 雲端技術應用及研究
+- 創新資料科學工程架構研究及開發
+- 大數據專案開發實作
+</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8hztb</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>圖靈數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>台北市中正區 中山北路一段2號11樓</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>行銷判讀，運營，轉化方面的戰略支持與技術方法。成員大多是技術工程師組成，協助客戶收集有用的數據，了解數據，利用數據。
+目前是 Google Marketing Platform、Mixpanel、AB Tasty 認證合作夥伴。
+公司福利：
+・</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7v0e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>(總公司)南山人壽保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>人身保險業</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>台北市信義區 台北市信義區信義路五段150巷2號5樓</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>您是否渴望在金融科技的前沿，以前瞻數據、AI 與 LLM 技術驅動創新，塑造未來金融服務？
+科技創研中心金融科技處，正積極尋找充滿熱忱、具備專業技能的 數據暨AI工程師 加入我們的創新團隊。您將負責金融科技領域的企業級數據平台、AI 平台及</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pkoj</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>資料工程師 / 數據服務架構師</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Phison Electronics Corp_群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>IC設計相關業</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>苗栗縣竹南鎮 群義路1號</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>算引擎（如 Trino）的維運與優化，透過 Infrastructure as Code (IaC) 與 GitOps 實現數據工程的自動化與標準化。
+【工作內容】
+    容器化平台管理：負責 Kubernetes 叢集的日常維運、資源調度與自動</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ve8x</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>資深資料工程師Senior Data Development Engineer</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>明門實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>其他運輸工具及零件製造修配業</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路433號10F</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Why Join Us
+這個角色不只是撰寫報表
+而是實際參與 APS（含 Kinaxis）供應鏈模型資料的建構與整理。
+你所處理的資料，將直接關聯到公司重要的營運規劃與管理決策，
+包含供應鏈計畫、情境模擬與資源配置。
+每一張資料表、每一個資料轉換</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xdmf</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>松凌科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>台北市中正區 衡陽路51號7樓之11</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>專科</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>主要工作項目：
+- 協助客戶核心系統轉換並開發資料轉換程式及驗證資料正確性
+- 依客戶報表需求進行分析與開發及驗證報表正確性
+職務要求：
+- 熟悉資料庫之SQL語法指令(PL/SQL或T-SQL)執行資料轉換及驗證資料正確性實務經驗。
+- 熟悉</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/79ccc</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>20260129</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D02-資料工程師(DE)_旅遊科技部_數據營運組</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>雄獅資訊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路151號</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>我們正在尋找對科技趨勢敏銳、樂於實驗的技術創新人才。你將成為旅遊科技部的技術推進引擎，結合 AI、前沿工具與跨領域思維，探索下一個改變旅遊產業的數位可能。
+1. 介接並整合內外部資料來源，確保資料的高可用性與一致性
+2. 設計、開發、測試與維護</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ppdw</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>AI Data Engineer(AI數據工程師)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>統一資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路155號8F~10F</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>The AI Center team at President Information CORP. has not only won the IT Matters Innovation Award, but has also published papers in top international journals and obtained numerous domestic and international patents. Our AI platform has successfully expanded into the global market, demonstrating our outstanding technological capabilities.
+1.Data Analyst：
+   ■Utilizing Large Language Models (LLMs) for data processing, including data cleaning, field alignment, classification, and data augmentation.
+   ■Building Retrieval-Augmented Generation (RAG) systems for database processing, integrating vector databases such as FAISS, Qdrant, and Weaviate.
+   ■Implementing vector, semantic, and multimodal search technologies to enhance intelligent information retrieval and data understanding.
+2.Design, Create, and Maintain Kubernetes Clusters for AI Applications：
+   ■Manage container images across multiple GCP environments.
+   ■Ensure efficient deployment and scaling of AI applications,using K8S to deploy container service for AI Application.
+3.Manage Cloud Resources：
+   ■Oversee resources across GCP, AWS, and Azure Open AI.
+   ■Manage Identity and Access Management (IAM) policies and roles.
+   ■Implement and monitor cloud security measures.
+   ■Optimize cloud resource usage and cost.
+   ■Automate infrastructure provisioning and management using tools like Terraform and CloudFormation.
+4.Integrate and Host Notification &amp; Queue Services：
+   ■Utilize services such as Amazon SQS, Google Cloud Pub/Sub, and RabbitMQ.
+5.Design and Manage Vector Databases：
+   ■Work with databases like Milvus,AI Vector DB and Pinecone for LLM vector search and query.  
+6.APM and Tracing Systems Integration and Management：
+   ■Implement and manage Application Performance Monitoring (APM) systems, such as Datadog、Databrick、 and Prometheus, for monitoring a.pplication performance.
+   ■Set up tracing systems like Jaeger and Zipkin to monitor usage and uptime.</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/83004</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>20260209</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>後端工程師</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>佐翼科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>自動控制相關業</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>台南市歸仁區 歸仁十三路一段6號三樓</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 58,000元</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>NoSQL也可）
+3. 具後端系統建置經驗佳（如GCP，AWS等開發經驗，或是⾃架資料庫經驗）
+4. RESTful API設計及開發。
+5. 具備與前端工程師協作經驗
+6. 有MQTT、HTTPS、Websocket等經驗
+*會依學經歷調整起薪*</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8m4qv</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>20260301</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>數據工程師 data engineer</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>台灣創博識有限公司</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>台北市中正區 南海路1號13樓</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>data governance, data quality, MLOps
+4. 優化開發者體驗，解決資料科學家開發與部署會遇到的問題
+資料工程師在數位轉型的浪潮下扮演重要的角色，本職位將有機會參與公司數位轉型計畫，並協助建立可靠的數據基礎架構，提供客</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wl9k</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>20260301</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>數據工程師(台中)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>綠品有限公司</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>台中市潭子區 崇德路四段170巷75號</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>月薪 10,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+※熟練掌握 SQL（這是不容妥協的核心能力）。
+※熟悉 Python 或 R 等數據科學常用語言。
+※有資料庫設計、數據清理與特徵工程的實務經驗。
+※溝通韌性： 需與不同背景的客戶溝通，具備耐心、同理心與清晰的邏輯表達。
+【加分條件】
+※開發潛力</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yrdz</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>超越數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 自強南路８號11樓之2</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1.雲端基礎架構規劃、建置及部屬、維護
+2.數據平台規劃、建置及部屬、維護
+3.雲原生平台規劃、建置及部屬、維護
+4.數據整理、清洗、建模及分析</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8si6v</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>20260228</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>大江生醫股份有限公司(TCI CO., Ltd)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>屏東縣長治鄉 神農路12號</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Lake。
+．   與資料科學團隊合作，提供模型所需的資料集與特徵工程支援（如 LightGBM、XGBoost）。
+．   透過Power BI進行資料串接與報表資料結構設計，確保分析資料即時、準確。
+．   撰寫技術文件，維護資料流程運作紀錄</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/69p6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>量化投資金融大數據工程師</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>沛然資訊有限公司</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街150號7樓</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>年薪 800,000 ~ 1,500,000元</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>控與跨市場操作等關鍵場景中。我們開發可用於決策的高互動行動應用，誠摯邀請對產品品質與金融邏輯有熱情的夥伴加入我們的團隊。
+【工作內容】
+1. 台清交成資工系學碩士優先。
+2. 優秀IT科技理工且對量化投資有興趣者。
+3. 量化交易相關資料庫的維運</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7mnu3</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>20260227</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>英屬維京群島商嘉碼科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>台中市西屯區 工業三十八路210號3樓之6</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位數據工程師，不僅具備扎實的技術底子，更擁有主動積極、樂於挑戰的特質。
+加入我們後，您將在這個充滿活力、尊重多元的環境中扮演關鍵角色，透過打造穩健的數據基礎與管道，協助團隊從資料中萃取價值、加速產品與業務的創新。
+如果您對資料領域充</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vvrv</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>統一超商資深資料工程師(uniopen客戶資料平台CDP)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>統一超商股份有限公司</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路163號5樓</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>月薪 50,000 ~ 120,000元</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1. 設計資料模型與數據建模轉化 (Data Modeling)：主導 數據架構規劃與 Medallion 模型設計，定義企業級 Golden Table 規範，確保模型具備高度擴展性以支援 AI/ML 應用。
+2. BI 報表與儀</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p2a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師 (台中)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>微碧愛普科技有限公司</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道二段659號8樓</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>需此職位與產品團隊和前後端工程團隊緊密合作，負責資料基礎建設的穩定性與資料品質，並推動新一代 AI 資料應用的落地。
+【工作內容】
+1. Data Infrastructure 建置與維護：負責 Airflow 的部署、調優與日常維護，確保排程</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xujh</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer_汐止</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>緯謙科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>新北市汐止區 新台五路一段88號</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>針對內部的資料平台，透過Azure雲端與地端環境方案，撰寫Python、SQL、Scala、R語言，進行資料的處理與開發
+工作內容包含: 
+1. 資料需求釐清: 根據內部需求進行相關資料的了解、協助釐清資料需求、盤點建立metadata、與最終的</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8e1a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>工務採發助理、主任</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>森禾建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>建築及工程技術服務業</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>台中市北屯區 台中市北屯區遼寧路二段90號</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>月薪 36,000 ~ 46,000元</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>1.預算編列及數量估算：
+        協助編制預算，評估所需資金。
+        估算所需材料和工程量。
+2.採購發包及廠商詢價討論：
+        與供應商溝通，詢價並討論採購事宜。
+        確保採購流程順利進行。
+3.協助繪圖</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/87b92</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>品保人員</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>久誼股份有限公司</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>加工紙製造業</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>台中市外埔區 長生路806號</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>月薪 32,000 ~ 33,500元</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1. 協助進行進出貨、製程及成品的品質檢測，並記錄測試結果
+2. 協助監控與提升產品品質，確保穩定性與一致性
+3. 執行製程與產品的抽檢與驗收，確保符合標準
+4. 分析檢驗數據，協助提出品質優化建議
+5. 整理並歸檔產品歷史記錄，維持資料完整與可</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4fjko</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>悠遊卡股份有限公司</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>台北市南港區 園區街3之1號13樓</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1.需求釐清: 依內部需求進行資料模型分析，如資料表增減、欄位增減、規則轉換、調整分析結果，並產出分析文件
+2.設定規則: 依分析文件撰寫SQL語法及ETL設定處理，並進行資料驗證
+3.平台維運: 日常監控及定期檢查
+4.平台串接: 平台與應用系</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ikwv</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>冠德建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>台北市松山區 民福里民權東路三段169號</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1.數據源擷取與整合(30%)
+-主導數據獲取策略，透過網路爬蟲(Web Scraping)、API介接或資料庫查詢等方式，自動化整合內外部多源數據。
+-建立並維護數據清洗、驗證與特徵工程的流程，確保數據品質，為後續建模奠定穩固基礎。
+2.預測</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tick</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer【數位數據發展本部】</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>東南旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段60號</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>統性整合資料支撐分析與AI應用的發展
+●	建置優化Data Pipeline，並建立資料品質監控管理機制，確保資料品質和效率
+●	與DA / DS 協作，開發實作數據 / AI產品，參與模型的部署上線與維運
+●	協作工程師設計大規模資料遷移，參與</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tbys</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>網管工程師</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>吉利達國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>機械設備租賃業</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>台北市大安區 基隆路二段207號2樓</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>此職位將負責公司內部資訊系統、資料備份及網路環境的維運與改善，屬跨 MIS、網路管理與基礎資料工程的綜合角色。主要工作內容如下：
+一、資料備份與管理（Data Management &amp; Backup）
+•	建置並維護公司資料備份機制（含 NAS、</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wmkv</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>20260301</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>【派遣至知名外商銀行|6個月短期專案】Data Engineer資料工程師_201C</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>萬寶華企業管理顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>月薪 65,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>學以上學歷
+-1年以上資料分析/資料工程/資料清洗相關經驗
+-必備中階 SQL技能(Python為加分項)
+【加分條件】
+-熟悉財務資料或報表流程
+-具備大數據平台(Hive、Hadoop)經驗者佳
+-有金融業相關經驗佳</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x37g</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>20251124</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>資料工程師(雲端工程師)-AI系統整合team【全家便利商店關係企業】</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>精藤股份有限公司</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段61號11樓</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>護），更有完善的公司治理與開發標準，可做為所有資訊人員執行專案時的後盾。
+除此之外，精藤近年來亦不斷追求更多新領域的發展，例如：雲端科技應用、大數據資料分析以及行動裝置管理技術等等，誠摯的歡迎所有對於零售流通有興趣的伙伴一同加入精藤的大家庭。</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p8r6</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>【產品處】【數據組DataTeam】資料工程師/數據工程師/Data Engineer</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>域動行銷股份有限公司</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>台北市松山區 松山區南京東三段285號10樓  (安泰大樓)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>，提供前瞻性的觀點，引領數據行銷的未來。
+組織介紹：
+域動Data Team是由一群對『數據分析』及『AI應用』具有研究及開發熱誠的成員所組成。在這裡你可以接觸到大量即時的使用者行為資料，並將資料科學模型應用於:
+『網路廣告投放優化』
+『網路用戶</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/86d2k</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>20251124</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>資料工程師-情報系統二team【全家便利商店關係企業】</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>精藤股份有限公司</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段61號11樓</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>護），更有完善的公司治理與開發標準，可做為所有資訊人員執行專案時的後盾。
+除此之外，精藤近年來亦不斷追求更多新領域的發展，例如：雲端科技應用、大數據資料分析以及行動裝置管理技術等等，誠摯的歡迎所有對於零售流通有興趣的伙伴一同加入精藤的大家庭。</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/84xyg</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>遠雄房地產-數據/資料工程師</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>遠雄房地產發展股份有限公司</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段200號8樓</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>1.模型開發-根據專案需求建立預測或分析模型。
+2.資料處理-資料定義及資料預處理，以利開發及後續成果分析。
+3.模型優化-隨著資料的質或量的變動，優化原先預測或分析模型。
+4.資料優化-隨資料蒐集度與市場變化，適時調整資料或資料預處理流程。
+5</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tony</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>數位科技處-數據工程師</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>永豐商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>台北市中山區 八德路二段308號</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>1. 設計與規劃ETL(ELT)，整合跨部門之系統分析與報表需求。
+2. 針對營運場景建置批次與資料處理流程，確保資料品質與可用性。
+3. 與業務單位協作，將需求落地為可衡量的數據產品與資料集。
+4. 優化資料模型與SQL查詢效能，提升指標產出效</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/87lum</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>【凱基證券/數位創新部】數據工程師</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>凱基證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>台北市中正區 重慶南路一段</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1. 資料倉儲等系統或機器學習建模之資料收集、開發處理與管理維護
+2. 業務單位數據需求開發</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7jogm</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>20260213</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>P7-Python資料工程師</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>意藍資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號12樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>月薪 35,000 ~ 45,000元</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>本公司是國內搜尋及語意分析市占率最高的廠商，專注研發非結構資料之數據處理，尋找熟悉Python及物件導向設計的人才加入。工作主要為開發與維運資料產線，搜集語料、資料儲存處理，並提供API服務供下游服務使用。
+工作內容如下：
+- 資料搜集程式開發</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7csnw</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>數據科技部-資料工程師 / 數據服務架構師</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>玉山綜合證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>台北市中山區 撫順街41巷13號5樓</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 資料倉儲管理與數據中心建置與管理
+2. 負責資料蒐集及處理各項數據、設計資料模型和ETL 流程設計
+3. 設計與開發自動化流程
+4. 進行數據應用與串接之需求訪談
+5. 營運事項之主協辦及其他交辦事項
+</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/889qn</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資深資料工程師(Python)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>宇利峯有限公司</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>台中市西屯區 市政路386號</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>職位概要:
+我們正在尋找一位專精於資料整理和Python開發的Python資料工程師，主要負責資料的清洗、標準化和品質控制工作。
+1. 數據清洗和標準化:
+- 處理原始資料，識別和處理異常值。
+- 統一資料格式和編碼標準。
+- 補齊缺失值和修正</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>久浪智醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 新竹縣竹北市生醫路2段150號</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 生醫與影像數據統計分析
+2. 數據庫建立與維護
+3. AI/ML 模型建立
+4. 自動化及優化工作及數據流程
+5. 具備AI Agent &amp; MCP protocol專案經驗
+</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8idjr</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>數據ETL/資料工程師</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>昇恒昌股份有限公司</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>其他零售業</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>台北市內湖區 新湖二路289號</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>工作內容:
+1 設計和建立資料分析報告和資料儀表板，
+2.提供資訊視覺化及說明分析。
+3.運用統計概念與資料驅動思維，收集和清理各類型資料，並設計資料分析方法，建立相關資料應用。
+4.跨系統資料梳理及資料倉儲整合(ETL)應用(SSIS、</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/878sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>【凱基證券/數位創新部】數據工程師</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>凱基金融控股股份有限公司|凱基證券|凱基銀行|中華開發資本|凱基投信</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>台北市中正區 重慶南路一段</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1. 資料倉儲等系統或機器學習建模之資料收集、開發處理與管理維護
+2. 業務單位數據需求開發</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/89pxp</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>115年-資料工程師(專員) - 總管理室／數據組</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>國家住宅及都市更新中心</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路一段21號</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>數據處理流程。
+5.處理資料清理與轉換（Data Cleaning &amp; Transformation），並與數據科學家及BI分析師合作，提供其高品質的數據供分析使用。</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y4vs</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>【前瞻研究籌獲中心】資料工程師(台南)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>國家資通安全研究院</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>其他專業／科學及技術業</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台南市歸仁區 </t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1. 設計並實作資料處理流程(ETL/ELT)，確保資料的準確性與一致性，支援後續的數據分析與應用
+2. 管理關聯式與非關聯式資料庫系統，進行效能調校與查詢最佳化
+3. 與跨領域團隊合作，提供資料支援並共同設計數據驅動解決方案
+4. 支援開發自動</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8rkm9</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>果實夥伴股份有限公司</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路610號2樓</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>【工作內容 】
+-  ETL 之開發、處理(資料清理、儲存、分析)與監測
+- 開發與設計專案所需 API 服務並與後端工程師合作，完成系統產品化程序
+- 依據不同業務需求，完成建置/維運/更新各式 Data infra 的需求
+- 與數據產品管理</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7dpwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>台積電駐廠機電課助理工程師(需輪班-無經驗可)-龍潭</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>河叡五金有限公司</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>空調水機電工程業</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>桃園市龍潭區 龍園六路101號</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>月薪 34,500元以上</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+5.定期巡檢/保養/抄錶/紀錄填寫與6S。
+6.協助工程師進行問題(異常、缺失)排除與解決。
+7.主管交辦事項。
+機械保養業務
+1.負責值班及日常設備維護作業。
+2.空污/空調/轉動系統設備(培林、軸承)維護、保養(會有高架、天花板夾層作業)。</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8h017</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>20260303</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>製造資訊軟體系統工程師(MES/ERP)(有經驗者,薪資可議,AI應用經驗尤佳)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>燿華電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>印刷電路板製造業(PCB)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>新北市土城區 中山路4巷3號(近北二高交流道）</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.C# / .NET 系統開發： 能運用至少一項工具 ASP.NET、WinForm、Web API 
+2. SQL Server 資料庫運用
+3. 利用以上工具，處理對應報表開發與異常處理 </t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ym6w</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>20260211</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>爬蟲工程師</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>恆昌科技有限公司</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台中市西屯區 </t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1. 使用 Python 協助應用程式開發與維護，支援數據處理與自動化需求。
+2. 開發、擴充並維護網路爬蟲程式，確保資料抓取穩定性與數據品質，並持續優化爬蟲策略。
+3. 維護現有爬蟲的可用性，監控運行狀態並排查錯誤。
+4. 與後端工程師協作，整</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8gb4l</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>20260117</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>艾捷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>台中市南屯區 大墩十街300號</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>【核心任務】
+Data 團隊是公司數據戰略的核心引擎，肩負著建構企業級數據基礎設施的重要使命。我們打造的數據中台每日處理數億筆交易數據，連接數百個業務數據源，構建高效能的資料管道。通過嚴謹的數據治理，我們不僅確保數據的品質與一致性，更將複雜的數據</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8kwnr</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>數據工程師 - RPA流程自動化人員(IDS)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>宏燁資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>台北市中正區 北平東路30號7樓</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1. RPA軟體流程自動化(UiPath / Automation Anywhere)需求訪談、流程規劃、流程開發與維護。
+2. 設定軟體自動化流程、伺服器平台運用、流程開發。
+3. 個性主動積極，具程式開發相關經驗佳。  
+4. 有良好的溝通與表達能力，具團隊合作精神。
+5. 具有RPA經驗者佳。
+6. 依個人經驗與期望安排對應專案職務(駐點客戶端等)。
+7. 無RPA經驗可，歡迎想要學習與實作RPA機器人的夥伴加入。</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/874x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>20260227</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Data Engineer / BI 資料工程師 / 資料分析師</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>璽亦科技有限公司</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路2段51號6樓之10</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>月薪 70,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位資料分析師 / BI 開發人員，此職位主要負責分析與解讀數據，產出具體可執行的洞察，協助公司進行商業決策。
+工作內容
+ • 分析與詮釋數據，提供決策支持
+ • 設計與建立資料模型
+ • 開發商業智慧（BI）解決方案
+ • 製作報</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yqul</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>20260213</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>喬美國際網路股份有限公司</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>台北市南港區 忠孝東路六段21號12樓之7</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>工作內容:
+開發與維護自動化數據處理流程（ex: Pipeline、Airflow）
+建置並優化各式網路爬蟲（ex: Requests、Playwright、Scrapy ）
+使用 Django 開發後端服務與 API，串接資料庫與前端系統
+操作</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7gpj8</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>數據工程師 - 數據分析人員(IDS)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>宏燁資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>台北市中正區 北平東路30號7樓</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1. 工作內容數據分析專案資料清理、建模、分析呈現。
+2.依專案內容進行SQL、ETL、BI、Python等技術開發。
+3.與團隊合作共同執行數據相關專案，內容包含資料庫結構分析、資料預處理、數據分析問題假設與原因剖析、多面向資料源數據報表假設證</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ip4q</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>產品三部 | 資料工程師(高雄)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>騰雲科技服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中華四路45號2樓</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>✅ 工作內容｜你會負責的任務
+1.數據建模：負責設計與維護 MDP 平台的資料模型，確保能有效支撐財務、銷售、行為等多維度主題數據。
+2.ETL 流程開發：配合使用 ETL 工具，撰寫高效能的 T-SQL 邏輯進行數據清洗、轉換與載入。
+3.效能</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xvzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ETL 資料工程師/大數據工程師</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>歐立威科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>台北市大同區 鄭州路87號11樓之1</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Pentaho PDI、Talend、Informatica、Microsoft SSIS 等）進行數據抽取、轉換與載入，確保資料正確性與完整性。
+3.熟悉 Python 或 Java 等程式語言，能撰寫 ETL 腳本與自動化流程。
+4.設計並維護 Data</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ugrj</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>久泰精業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>通用機械設備製造修配業</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>雲林縣斗六市 榴中里民有街36號</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>工作內容：
+1. 監控與程式開發
+ SCADA / 圖控軟體開發與設計
+ PLC 程式設計與人機介面 (HMI) 開發
+ 控制盤體規劃設計與系統整合
+2. 資料處理與系統應用
+ 工控數據採集、傳輸與資料庫管理
+ PHP / Web 前端程式設計，</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wfqn</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Data Engineer - Generative AI Pipelines 資料工程師</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>宇泰華科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>台北市南港區 園區街3之1號5樓之2(G棟）</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>***由此連結提交你的履歷: https://jobs.ashbyhq.com/palup*** 
+We’re looking for a Data Engineer —to build scalable data pipelines that power Generative AI applications like RAG, summarization, NER, and FAQ systems. You’ll design systems to scrape, ingest, transform, and enrich data at scale, ensuring it’s clean and optimized for AI/ML workflows.
+What you will do:
+1. Build and optimize ETL/ELT pipelines for large-scale structured &amp; unstructured data
+2. Develop data enrichment workflows (entity extraction, embeddings, metadata tagging)
+3. Manage data lakes, warehouses, and vector databases to support AI retrieval
+4. Collaborate with ML engineers on AI-ready data infrastructure
+5. Ensure pipeline reliability, scalability, and observability
+Who You Are:
+- 5+ years in data engineering (Python, SQL, Spark/Dask/Ray)
+- Experience with web scraping frameworks (Scrapy, Playwright, Selenium)
+- Strong knowledge of cloud platforms (AWS/GCP/Azure) &amp; orchestration tools (Airflow/Prefect/Dagster)
+- Familiarity with GCP storage solutions such as BigQuery, Cloud Storage etc.
+- Familiarity with vector search databases (Pinecone, Weaviate, Elasticsearch)
+- Understanding of NLP concepts relevant to generative AI</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/69or3</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AI 提示工程師（Prompt Engineer）</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>台灣骨王生技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>台中市大雅區 科雅路41號2樓</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>AI 提示工程師（Prompt Engineer）
+地點：台中市／台中科學園區
+部門：研發部
+職位性質：全職
+職務說明
+我們正在尋找一位具有 語言模型理解與應用能力、同時能結合提示工程（Prompt Engineering）與 Python</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8r08j</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>115年-資料工程師(資深專員／專員) - 行政管理部／資訊組</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>國家住宅及都市更新中心</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路一段21號</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>上線與後續維護
+•與廠商合作進行各業務系統平台資料整合與介接
+【必要條件】
+•三年以上資料工程相關工作經驗，具備獨立完成資料工程項目的能力
+•精通 Python 程式語言，具備良好的程式設計能力與程式碼品質意識，熟悉常用的資料處理函式庫
+•熟悉</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x8mk</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據架構工程師) – (數數發中心, DDT)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>【關於我們】
+我們是國泰產險的資料科學（DS）團隊，使命在於持續進化數據應用，創造並釋放數據價值。目前正在藉由數據上雲、數據治理與 AI 技術應用，推動由底層架構到業務應用的全端數據生態建構與 AI 轉型準備。
+我們尋找認同以下團隊文化的夥伴：</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8opms</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>20260223</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>軟體工程師</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>奇翼醫電股份有限公司</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 文興路257號11樓</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 進行效能分析、記憶體與 CPU 優化（含多線程、SIMD、定點數實作等）、並規劃壓力測試場景。
+6. 與 iOS/Android/嵌入式工程師共同將演算法移植或包裝（例如 C/C++ / Rust library 或 WASM），或作為雲端</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tjo6</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>20260206</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>AI 全端工程師(豐原、中壢)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>吉翔樂_旻新科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>資料儲存媒體製造及複製業</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>台中市豐原區 豐原大道一段430號</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>關於我們
+我們是賽鴿產業的科技創新者，專注於開發 GPS 即時追蹤系統與數據分析平台。隨著 AI 技術快速發展，我們正積極將 AI Agent 導入產品與內部流程，尋找能夠擁抱這波浪潮、用新方法解決問題的工程師加入團隊。
+職位概述
+我們正在尋找</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wo3z</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>澧曜數據有限公司</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>台中市西區 忠明南路497號2樓</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 開發/維護/設計處理數據架構與服務以及部署服務。
+2. 負責ETL（數據提取、轉換、加載）流程設計，包括數據清洗、預處理及自訂程式開發。
+3. 擁有CI/CD經驗，熟悉Jenkins、GitLab、Airflow等CI/CD工具和流程。
+</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dclx</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>20260225</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>製造資料科學工程師</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>紫式大數據決策股份有限公司</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>新竹市 光復路二段376-1號2樓</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>碩士</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1.	依據客戶端於製造資料科學需求（例如：製程參數優化、產品瑕疵檢測、設備預測保養）進行資料健檢、開發與導入符合需求的AI演算法，並以實際數據進行離線驗證。
+2.	與客戶端軟體團隊合作，將演算法封裝成API進行系統整合串接，並協</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ww7h</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Digital Twin工程師、資料工程師、後端工程師_14874</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>和碩集團_和碩聯合科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>電腦及其週邊設備製造業</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>台北市北投區 立功街76號</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>碩士</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 模型、data engineering和simulation environment集成到企業工作流程中。
+4.與產品經理、資料科學家和工程師合作，將業務需求轉化為技術解決方案。
+5.確保數位孿生系統應用程序的高性能、可擴展性和安全性，滿足企業級需</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vzq3</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>資深資料工程師 (企業架構處)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>全球人壽保險股份有限公司_總公司</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>人身保險業</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>台北市信義區 市民大道6段288號15F</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1.	數據相關應用系統開發與維運: 帶領小組成員一起完成 
+2.	專案管理: 數據治理,數據服務平台
+3.	一般支援: 數據相關解決方案研發、資安/法遵/行政庶務</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8phhn</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>20260302</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>科技金融_資料工程師</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>中國信託商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>台北市南港區 經貿二路168號 (中國信託總部)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1. 負責需求分析與流程規劃，洞察潛在關鍵應用或數據，並運用內外部數據進行前期探索分析及策略建議。
+2. 負責梳理並規劃機器學習研發資料庫架構，建立數據品質流程管理與維護計畫，掌握數據產品策略及生命週期。
+3. 能將數據應用產品轉化為需求文件、系</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/73am4</t>
         </is>
       </c>
     </row>

--- a/z_RequestData/jobsearch_data104.xlsx
+++ b/z_RequestData/jobsearch_data104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,10 +481,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A2" t="n">
+        <v>20260316</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -539,10 +537,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A3" t="n">
+        <v>20260318</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -596,10 +592,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
+      <c r="A4" t="n">
+        <v>20260224</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -652,10 +646,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>20260309</t>
-        </is>
+      <c r="A5" t="n">
+        <v>20260309</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -706,10 +698,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>20260305</t>
-        </is>
+      <c r="A6" t="n">
+        <v>20260305</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -760,10 +750,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A7" t="n">
+        <v>20260312</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -832,10 +820,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A8" t="n">
+        <v>20260316</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -887,10 +873,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20260225</t>
-        </is>
+      <c r="A9" t="n">
+        <v>20260225</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -939,10 +923,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20260223</t>
-        </is>
+      <c r="A10" t="n">
+        <v>20260223</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -994,10 +976,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A11" t="n">
+        <v>20260316</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1052,10 +1032,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A12" t="n">
+        <v>20260316</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1107,10 +1085,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A13" t="n">
+        <v>20260312</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1161,10 +1137,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A14" t="n">
+        <v>20260316</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1215,10 +1189,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A15" t="n">
+        <v>20260316</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1270,10 +1242,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20260225</t>
-        </is>
+      <c r="A16" t="n">
+        <v>20260225</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1323,10 +1293,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A17" t="n">
+        <v>20260318</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1380,10 +1348,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20260315</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20260315</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1439,10 +1405,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
+      <c r="A19" t="n">
+        <v>20260224</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1492,10 +1456,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20260310</t>
-        </is>
+      <c r="A20" t="n">
+        <v>20260310</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1549,10 +1511,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20260228</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20260228</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1604,10 +1564,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A22" t="n">
+        <v>20260312</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1658,10 +1616,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A23" t="n">
+        <v>20260312</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1713,10 +1669,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A24" t="n">
+        <v>20260316</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1770,10 +1724,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A25" t="n">
+        <v>20260316</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1842,10 +1794,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A26" t="n">
+        <v>20260317</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1897,10 +1847,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A27" t="n">
+        <v>20260311</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1952,10 +1900,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A28" t="n">
+        <v>20260311</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2006,10 +1952,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A29" t="n">
+        <v>20260316</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2060,10 +2004,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20260310</t>
-        </is>
+      <c r="A30" t="n">
+        <v>20260310</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2114,10 +2056,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A31" t="n">
+        <v>20260316</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2169,10 +2109,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A32" t="n">
+        <v>20260318</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2235,10 +2173,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>20260313</t>
-        </is>
+      <c r="A33" t="n">
+        <v>20260313</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2289,10 +2225,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A34" t="n">
+        <v>20260210</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2345,10 +2279,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A35" t="n">
+        <v>20260316</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2401,10 +2333,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A36" t="n">
+        <v>20260316</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2455,10 +2385,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A37" t="n">
+        <v>20260316</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2509,10 +2437,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A38" t="n">
+        <v>20260318</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2564,10 +2490,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A39" t="n">
+        <v>20260318</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2621,10 +2545,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A40" t="n">
+        <v>20260316</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2677,10 +2599,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>20260309</t>
-        </is>
+      <c r="A41" t="n">
+        <v>20260309</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2736,10 +2656,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A42" t="n">
+        <v>20260318</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2792,10 +2710,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20260302</t>
-        </is>
+      <c r="A43" t="n">
+        <v>20260302</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2849,10 +2765,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>20260219</t>
-        </is>
+      <c r="A44" t="n">
+        <v>20260219</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2904,10 +2818,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A45" t="n">
+        <v>20260317</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2961,10 +2873,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A46" t="n">
+        <v>20260318</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3018,10 +2928,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A47" t="n">
+        <v>20260316</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3078,10 +2986,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>20251124</t>
-        </is>
+      <c r="A48" t="n">
+        <v>20251124</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3131,10 +3037,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A49" t="n">
+        <v>20260316</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3187,10 +3091,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A50" t="n">
+        <v>20260316</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3242,10 +3144,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>20260126</t>
-        </is>
+      <c r="A51" t="n">
+        <v>20260126</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3294,10 +3194,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A52" t="n">
+        <v>20260312</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3350,10 +3248,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A53" t="n">
+        <v>20260316</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3405,10 +3301,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A54" t="n">
+        <v>20260316</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3461,10 +3355,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A55" t="n">
+        <v>20260317</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3518,10 +3410,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A56" t="n">
+        <v>20260317</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3575,10 +3465,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A57" t="n">
+        <v>20260316</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3633,10 +3521,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A58" t="n">
+        <v>20260316</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3686,10 +3572,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A59" t="n">
+        <v>20260316</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3741,10 +3625,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A60" t="n">
+        <v>20260318</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3795,10 +3677,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>20260310</t>
-        </is>
+      <c r="A61" t="n">
+        <v>20260310</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3849,10 +3729,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A62" t="n">
+        <v>20260312</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3904,10 +3782,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A63" t="n">
+        <v>20260316</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3961,10 +3837,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A64" t="n">
+        <v>20260316</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -4016,10 +3890,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A65" t="n">
+        <v>20260311</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4071,10 +3943,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20260310</t>
-        </is>
+      <c r="A66" t="n">
+        <v>20260310</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4125,10 +3995,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A67" t="n">
+        <v>20260311</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4182,10 +4050,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A68" t="n">
+        <v>20260317</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4238,10 +4104,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A69" t="n">
+        <v>20260317</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4295,10 +4159,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A70" t="n">
+        <v>20260311</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4351,10 +4213,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A71" t="n">
+        <v>20260311</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4410,10 +4270,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A72" t="n">
+        <v>20260316</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4467,10 +4325,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A73" t="n">
+        <v>20260312</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4534,10 +4390,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A74" t="n">
+        <v>20260316</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4588,10 +4442,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A75" t="n">
+        <v>20260316</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4644,10 +4496,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A76" t="n">
+        <v>20260317</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4699,10 +4549,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>20260226</t>
-        </is>
+      <c r="A77" t="n">
+        <v>20260226</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4758,10 +4606,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>20260209</t>
-        </is>
+      <c r="A78" t="n">
+        <v>20260209</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4812,10 +4658,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A79" t="n">
+        <v>20260318</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4866,10 +4710,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20260314</t>
-        </is>
+      <c r="A80" t="n">
+        <v>20260314</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4921,10 +4763,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>20260313</t>
-        </is>
+      <c r="A81" t="n">
+        <v>20260313</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4978,10 +4818,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A82" t="n">
+        <v>20260317</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -5034,10 +4872,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>20251124</t>
-        </is>
+      <c r="A83" t="n">
+        <v>20251124</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5087,10 +4923,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A84" t="n">
+        <v>20260317</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5141,10 +4975,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A85" t="n">
+        <v>20260317</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5198,10 +5030,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A86" t="n">
+        <v>20260316</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5251,10 +5081,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A87" t="n">
+        <v>20260316</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5306,10 +5134,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A88" t="n">
+        <v>20260316</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -5360,10 +5186,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>20260309</t>
-        </is>
+      <c r="A89" t="n">
+        <v>20260309</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -5416,10 +5240,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A90" t="n">
+        <v>20260312</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5503,10 +5325,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A91" t="n">
+        <v>20260316</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5559,10 +5379,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>20260302</t>
-        </is>
+      <c r="A92" t="n">
+        <v>20260302</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5613,10 +5431,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
+      <c r="A93" t="n">
+        <v>20260101</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5666,10 +5482,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A94" t="n">
+        <v>20260316</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5722,10 +5536,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20260129</t>
-        </is>
+      <c r="A95" t="n">
+        <v>20260129</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -5776,10 +5588,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20260309</t>
-        </is>
+      <c r="A96" t="n">
+        <v>20260309</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -5832,10 +5642,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A97" t="n">
+        <v>20260318</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5886,10 +5694,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>20260310</t>
-        </is>
+      <c r="A98" t="n">
+        <v>20260310</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5939,10 +5745,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A99" t="n">
+        <v>20260316</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -5992,10 +5796,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>20260318</t>
-        </is>
+      <c r="A100" t="n">
+        <v>20260318</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6048,10 +5850,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A101" t="n">
+        <v>20260316</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6105,10 +5905,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A102" t="n">
+        <v>20260312</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6164,10 +5962,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A103" t="n">
+        <v>20260316</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -6219,10 +6015,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A104" t="n">
+        <v>20260311</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -6274,10 +6068,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A105" t="n">
+        <v>20260316</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -6330,10 +6122,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A106" t="n">
+        <v>20260317</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -6385,10 +6175,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A107" t="n">
+        <v>20260316</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -6440,10 +6228,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A108" t="n">
+        <v>20260312</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -6493,10 +6279,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>20260317</t>
-        </is>
+      <c r="A109" t="n">
+        <v>20260317</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -6549,10 +6333,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A110" t="n">
+        <v>20260312</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -6603,10 +6385,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
+      <c r="A111" t="n">
+        <v>20260101</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -6652,6 +6432,6096 @@
       <c r="J111" t="inlineStr">
         <is>
           <t>https://www.104.com.tw/job/7jogm</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Java工程師-高雄(T)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>凌網科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 新光路</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1.Java 網頁應用程式全端開發： 負責 Java Web 專案開發，包含後端商業邏輯、資料處理及前端頁面呈現（依專案需求使用 JSP/JavaScript 或 Vue.js）。
+2.資料庫管理與設計： 負責 MS SQL 資料庫 Schema</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5yxhv</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>網路行銷事業部主管(底薪10萬+每月部門淨利分紅最高50%+周休三日)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>戰國策網路科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>台北市信義區 松德路159號13樓</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>月薪 100,000 ~ 210,000元</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>業的顧客售後服務。 
+3.負責達成公司規定部門業績目標及達成客戶滿意。 
+4.提供產品相關資訊及申辦資料流程協助並幫助顧客解決問題。 
+5.執行主管交辦事項。 
+6.團隊招募及訓練
+薪資及獎金福利:
+1.底薪10萬起是指:
+a.有網頁設計、網路行</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/86ydf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>20260323</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Regional Data Engineer 數據工程師(台北工作)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>香港商麥迪康亞太有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路1段163號4樓之3(市府站1號出口)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1.設計、開發和維護可擴展的數據管道和ETL流程。
+2.與數據科學家、分析師和利益相關者合作，了解數據需求並提供解決方案。
+3.優化和改進現有數據系統，以提高性能和可靠性。
+4.實施數據質量檢查，確保各類數據源的數據完整性。
+5.開發和維護數據工程</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8m4mk</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>數據工程師 / Data Engineer (Data Infrastructure)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>富華創新股份有限公司台中分公司</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>建築及工程技術服務業</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>台中市北屯區 太原路三段1315號</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士、博士</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>協助各業務單位理解數據價值，推動企業從「經驗法則」逐步邁向「數據驅動」的決策模式。
+▍我們期待你具備
+・3 年以上資料工程、後端開發或資料庫管理經驗，精通 SQL 與 Python。
+・熟悉 GCP 雲端數據與 AI 生態系：具備</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zban</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RD-數據工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>順立智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>台北市內湖區 內湖路一段360巷8號7樓</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>板（命名、開發流程、文件）
+【Must Have】
+－2+ 年資料工程/資料管線相關經驗
+－熟悉 SQL + Python
+－熟悉任一資料倉儲
+－有資料品質/監控/回溯經驗
+－具產品數據概念</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7njt5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20260311</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>中國信託證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>台北市南港區 經貿二路188號12樓</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>【職務主要內容】
+1. 建立開發標準與規範：制定資料交換標準、建立開發 SOP。
+2. 資料管道與系統串接(ETL/Integration)：協助系統間的資料串接與整合、優化舊有系統的 ETL 流程。
+3. 數據品質與監控：建立預警機制，確保資料</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n6z2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>20260312</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>資深資料工程師 Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>秀曜匯智股份有限公司</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>數位內容產業</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>台北市南港區 重陽路120號2樓207室</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Job Summary
+We are seeking a highly skilled and experienced Senior Data Engineer to join our growing data team. In this role, you will design, build, and maintain scalable data pipelines and infrastructure that support analytics, machine learning, and business intelligence initiatives. You will work closely with data scientists, analysts, and software engineers to ensure data is accessible, reliable, and secure.
+Key Responsibilities
+￭ Design and implement scalable data pipelines for real-time streaming and batch ETL/ELT processing.
+￭ Architect data storage solutions (data lakes, warehouses) to support diverse analytics and ML needs.
+￭ Develop and optimize real-time data streaming systems and corresponding dashboards.
+￭ Ensure data quality, integrity, security, and governance across systems.
+￭ Plan and execute data collection, storage, and maintenance strategies for varied requirements.
+￭ Collaborate with data scientists, analysts, and stakeholders to deliver business-driven data solutions.
+￭ Mentor junior engineers and promote data engineering best practices.
+￭ Monitor and enhance data infrastructure performance and scalability.
+Qualifications
+￭ 5+ years of data engineering experience.
+￭ Expertise in SQL, Python, and big data tools (e.g., Spark, Kafka).
+￭ Familiar with data representation tools (e.g., Tableau, Looker Studio, Superset).
+￭ Proficiency with cloud platforms (e.g., GCP, AWS, Azure) and data services (e.g., 
+BigQuery, Snowflake).
+￭ Proven experience in real-time streaming systems, dashboard development, and large-scale ETL design.
+￭ Strong knowledge of data modeling, governance, and security practices.
+￭ Bachelor’s degree in Computer Science, Engineering, or related field (Master’s preferred).
+￭ Excellent problem-solving, collaboration, and communication skills.</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ryui</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer_汐止</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>緯謙科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>新北市汐止區 新台五路一段88號</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>針對內部的資料平台，透過Azure雲端與地端環境方案，撰寫Python、SQL、Scala、R語言，進行資料的處理與開發
+工作內容包含: 
+1. 資料需求釐清: 根據內部需求進行相關資料的了解、協助釐清資料需求、盤點建立metadata、與最終的</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8e1a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20260316</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>文境資科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>專門設計相關業</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師
+1.資料稽核(Data Auditing)、收集(Data Collection)、整合作業(Data Integration) 等資料分析前處理作業
+2.有MS SQL server、SSIS、SSRS</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7g1tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>宇清數位智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>新竹市 東區金山七街1號6樓</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>精準的完成需求
+ 3. 負責產品資料處理、資料架構開發、維護以及監控機制
+ 4. 協助專案產品的導入與開發、以及相關的推廣與後續維護
+ 5. 與演算法工程師及專案經理合作，依專案需求整合資料格式</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/76kp9</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ETL資料工程師(FJ)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市松山區 </t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>．設計、開發與維護 ETL 流程，確保資料的正確性與一致性
+．使用 NiFi、SSIS 或其他 ETL 工具進行資料擷取、轉換與載入
+．優化現有流程效能，提升資料處理速度與可靠性
+．支援內部系統或跨團隊資料整合專案
+．撰寫並維護技術文件，確保流程</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8usc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>侍達遊戲藝術有限公司</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>台北市信義區 東興路41號5樓</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1. 根據分析需求進行資料建模，並提供視覺化的資料呈現。
+2. 提供分析數據及報表。
+3. 設計與開發資料分析所需要的工具。
+[能力需求]
+1. 具備程式開發經驗 (Python/Golang等)。
+2. 具備 SQL/NoSQL 使用經驗</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85yiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20260228</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>大江生醫股份有限公司(TCI CO., Ltd)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>屏東縣長治鄉 神農路12號</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Lake。
+．   與資料科學團隊合作，提供模型所需的資料集與特徵工程支援（如 LightGBM、XGBoost）。
+．   透過Power BI進行資料串接與報表資料結構設計，確保分析資料即時、準確。
+．   撰寫技術文件，維護資料流程運作紀錄</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/69p6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>世祥汽材製造廠股份有限公司</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>汽車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>台中市西屯區 市政北七路98號20樓</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1. SAP 與資料來源串接
+．與 SAP 系統（如 SAP ECC、SAP S/4HANA、SAP BW 等）進行資料串接與抽取
+．熟悉 SAP 相關數據表結構，使用 SAP Connector、ODBC/OData API、或中介平台進行資料</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yyej</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>【派遣至知名外商銀行|1年期專案】Data Engineer資料工程師_201C</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>萬寶華企業管理顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>月薪 65,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1年以上資料分析/資料工程/資料清洗相關經驗
+-必備中階以上SQL技能(Python, Dashboard為加分項)
+【加分條件】
+-熟悉財務資料或報表流程
+-具備大數據平台(Hive、Hadoop)經驗者佳
+-有金融業相關經驗佳</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8z3gy</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>【Data Engineer】 資料工程師</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>新加坡商昇新科技股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞湖街58號5樓</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>我們正處於數據架構升級的關鍵階段。尋找一位數據工程專家與我們共同重新定義數據流。
+你將負責冷熱數據分離架構的落地，並優化我們的 Data Warehouse 架構，確保在海量數據環境下，數據依然能兼具查詢效能與成本。
+【你將面臨的核心技術挑戰】</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x352</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>數據工程師(台中)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>綠品有限公司</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>台中市潭子區 崇德路四段170巷75號</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+※熟練掌握 SQL（這是不容妥協的核心能力）。
+※熟悉 Python 或 R 等數據科學常用語言。
+※有資料庫設計、數據清理與特徵工程的實務經驗。
+※溝通韌性： 需與不同背景的客戶溝通，具備耐心、同理心與清晰的邏輯表達。
+【加分條件】
+※開發潛力</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y0th</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>數據工程師(台中)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>綠品有限公司</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>台中市潭子區 崇德路四段170巷75號</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>月薪 10,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+※熟練掌握 SQL（這是不容妥協的核心能力）。
+※熟悉 Python 或 R 等數據科學常用語言。
+※有資料庫設計、數據清理與特徵工程的實務經驗。
+※溝通韌性： 需與不同背景的客戶溝通，具備耐心、同理心與清晰的邏輯表達。
+【加分條件】
+※開發潛力</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yrdz</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>【SaaS】資料工程師 / AI工程師</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>鼎恒數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>台北市信義區 東興路45號2樓</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>在尋找一位熟悉雲端數據架構與自動化資料管線 (Data Pipeline) 開發，且對 AI演算法/LLM模型有興趣，有志一起發展數據應用的技術人才。
+您將全程參與數據的生命週期：從底層數據湖架構設計、ETL 管道建置，一路延伸到數據應用的開發與技</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvlq</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>契星科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路23號3樓</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>月薪 45,000元以上</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>工作內容：
+1. 開發資料科學管線、提供軟體產品背後演算邏輯及資料科學應用
+2. 與PM、後端工程師、技術主管協作進行專案開發及測試
+3. 熟悉SQL
+4. 熟悉 Python
+5. 熟悉 Git，會用Github
+6. 會使用 Numpy,</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/88tmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>20260310</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>資料工程師 Junior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>亞太智能機器股份有限公司</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路266號2樓</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>：** 撰寫腳本處理冗餘資訊、移除格式雜訊，並進行繁簡轉換、全半形正規化等 NLP 前處理，兼顧工程健壯性與處理效率。
+### 2. LLM 資料整備與優化
+* **文本切塊 (Chunking)：** 針對長文本設計合理的切分策略，優化檢索效</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vkrx</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>資料/數據工程師 Data engineer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>智星網路科技有限公司</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>台北市信義區 松仁路89號5樓A室</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>【關於本職缺｜About the Role】
+Data Engineer 是公司資料基礎建設的核心角色，負責建置、維護與優化資料管線、資料倉儲與數據工程架構，確保來自 GTM、RevOps 與各商務系統的資料能被穩定整合、清洗、轉換並提供給分析與</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ztyy</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>AI 數位企劃師 / AI Digital Planner《企劃部》【台北事業處】</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>千享國際企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段285號5樓</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 48,000元</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>縣市觀光局處的內容需求被準確轉化為網站頁面
+2. AI 智慧平台企劃協作
+   參與 AI 旅遊中樞系統的企劃開發——
+   協助規劃 AI 客服的前台互動流程、使用者介面配置，
+   與 Prompt Engineer、AI 工程師協作，</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ygub</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>自動化設備電控設計工程師(PC Based)@桃園_01050033</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>乾坤科技股份有限公司_台達電子集團</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>被動電子元件製造業</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>桃園市龜山區 桃園市龜山區山鶯路268號(桃園) (龜山工業區)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1. 自動化設備異常排查、改善、優化
+2. 自動化設備PC程式與資料庫維護(VB、C#、SQL)
+3. 供應商的溝通與聯繫
+4. 建立並管理設備標準文件
+5. 其他主管交辦事項
+√符合桃園市青年安薪就業讚方案資格者，可向政府單位申請上限21,</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xh7s</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>替您錄科技股份有限公司(TGC Taiwan, Inc.)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>多媒體傳播相關業</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>台北市松山區 八德路四段760號6樓</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位熱情且富有才華的資料工程師，加入我們的團隊，協助解決廣告投遞的資料內容。在這裡有大量的數據供你發揮所長，將學過的知識及方法應用到實務的工作上。
+我們希望你具備以下三大特質：
+對資料工程領域有強烈興趣和熱情 。
+重視團隊合作，具備</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ekil</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>圖靈數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>台北市中正區 中山北路一段2號11樓</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>行銷判讀，運營，轉化方面的戰略支持與技術方法。成員大多是技術工程師組成，協助客戶收集有用的數據，了解數據，利用數據。
+目前是 Google Marketing Platform、Mixpanel、AB Tasty 認證合作夥伴。
+公司福利：
+・</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7v0e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資深資料工程師(Python)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>宇利峯有限公司</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>台中市西屯區 市政路386號</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>職位概要:
+我們正在尋找一位專精於資料整理和Python開發的Python資料工程師，主要負責資料的清洗、標準化和品質控制工作。
+1. 數據清洗和標準化:
+- 處理原始資料，識別和處理異常值。
+- 統一資料格式和編碼標準。
+- 補齊缺失值和修正</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>20260323</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>資料工程師/後端工程師 (Data Engineer / Backend Engineer)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>典通股份有限公司</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>台北市中正區 愛國西路9號7樓</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>與管理，包括機器環境設定及基礎架構設計（Infrastructure）。
+4. 整合數據管道和資料流處理流程，支持數據分析需求及前端服務。
+5. 與數據分析師、前端工程師及其他業務部門緊密協作，理解並滿足多樣化的數據需求。
+您可以透過以下聯結認識</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8jvge</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>數據分析師/資料工程師/BI工程師</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>揚明光學股份有限公司_YoungOptics Inc.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>光學器材製造業</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>新竹市 科學園區新安路7號</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1. ETL / 資料整合開發：
+     ￭ 設計並開發資料清洗、轉換、整併流程（SAP DS / ETL Pipeline）
+     ￭ 維護批次程序、提升執行效能、確保資料品質與正確性
+2. SAP BW / 資料倉儲管理：</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8q2xn</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>核桃運算股份有限公司</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路一段9號4樓</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備 3-5 年經驗的資料工程師，加入我們的數據團隊。您將負責設計、構建並優化高效率的 Data Pipeline，確保資料從來源端到分析端的準確性與即時性。 此職位不僅需要強大的 Python 與 ETL 開發能力，更需要您對</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8waxf</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>關貿網路股份有限公司</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>台北市南港區 三重路19之13號6樓(115)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1.大數據應用系統開發維護及專案支援。
+2.數據處理及ETL架構規劃及開發。
+3.熟悉java，會Python/R或撰寫分析演算法程式尤佳。</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4ftgq</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>數據工程師【明基BenQ雲端創新中心】</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>明基電通股份有限公司</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>台北市內湖區 基湖路16號</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>As a data engineer in BenQ Data Application Department, to host website data collection by GTM is part of your main task, and to build up modern data foundation by GCP and AWS for AI agents will be the exciting parts. Join our talented team and take the challenges in this agentic era.
+Job description:
+1. Ownership of Google Tag Manager for BenQ global websites and co-work with data analyst to make sure the data quality in Google Analytics and BigQuery. A meticulous and patient personality is essential.
+2. 3rd party plug-in maintenance and to communicate with global marcom teams.
+3. ETL maintenance, familiar with any one orchestrator tools like: airflow, glue, step function,  composer, etc.
+4. Strong execution of data governance with well-defined rules across GCP, AWS, Databricks, and on premise servers. 
+5. AI agent development for business requirements.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5yq72</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ETL資料工程師</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>欣創科技有限公司</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號9樓之4</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1. 熟悉執行ETL資料轉換作業(Informatica PowerCenter、IBM DataStage、Microsoft SSIS、Trinity等ETL工具)
+2. 資料庫安裝、設定及操作實務經驗
+3. 具備STORE</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/80lq4</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據架構工程師) – (數數發中心, DDT)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>【關於我們】
+我們是國泰產險的資料科學（DS）團隊，使命在於持續進化數據應用，創造並釋放數據價值。目前正在藉由數據上雲、數據治理與 AI 技術應用，推動由底層架構到業務應用的全端數據生態建構與 AI 轉型準備。
+我們尋找認同以下團隊文化的夥伴：</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8opms</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>資料工程師 (ETL)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1. 使用 ETL工具開發或是資料庫/資料表系統相關之程式設計及開發
+2. 依規格設計開發包含 SQL Script 以及 Store Procedure 等對資料進行處理的程式，並進行UT測試，撰寫驗證報告
+3. 資料管理與處理相關專案之需求訪</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/81zdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>【外商】[RC-Data] (Sr.) Data Engineer-Streaming／數據工程師-Streaming</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路捷運中山站六號出口共構大樓</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>個國家。隨著全球業務持續擴展，我們正積極強化台灣團隊，並持續投入金融系統、風險模型與資料智能等領域的優秀人才。
+【關於該職位】 
+我們正在尋找一位 Streaming Data Engineer（即時資料工程師），負責設計並建置可擴展的即時資料處</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wpc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>徵  數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>臺北醫學大學</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用之</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xi1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>雲端數據工程師</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>君綺生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>美容／美體業</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>台北市信義區 松智路1號</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>部門介紹:
+我們是集團組織擴編成立的新部門, 在這工作你將會體驗全雲的工作環境, 包含AWS雲端服務及工具, 在工作中學習專案管理、資料庫管理、雲端服務等技術
+工作內容
+1. 參與雲端數據架構發展規劃，設計資料處理、儲存、分析架構，以符合數據</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mcsu</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D4000 資料工程師(湖倉平台) </t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>富邦媒體科技股份有限公司(富邦momo)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街96號4樓</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>資料品質檢核、排程監控儀表板等。
+● 設計並實作數據存取 API，為下游分析與 AI/ML 團隊提供穩定的數據服務介面。
+● 撰寫完整的單元測試與整合測試，確保交付程式碼符合軟體工程品質標準。
+3. 數據串流與即時處理（加分項）
+● 協助設計與開發即</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y67g</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>20260328</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>英屬維京群島商嘉碼科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>台中市西屯區 工業三十八路210號3樓之6</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位數據工程師，不僅具備扎實的技術底子，更擁有主動積極、樂於挑戰的特質。
+加入我們後，您將在這個充滿活力、尊重多元的環境中扮演關鍵角色，透過打造穩健的數據基礎與管道，協助團隊從資料中萃取價值、加速產品與業務的創新。
+如果您對資料領域充</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vvrv</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>20260323</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>【台北 / 彈性遠端】Sr. Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>布魯斯人事顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中正區 </t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>月薪 1,400,000元以上</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1. 負責大規模資料的雲端基礎架構設計與演進，涵蓋資料流、整合處理、儲存分析與事件偵測等核心能力。
+2. 與相關團隊協作，提出並實作資料架構的優化與轉移計畫，打造具高可用性、可擴展性與韌性的基礎設施。
+3. 兼顧業務成長與工程實作</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wrnj</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>資深數據工程師（Senior - Data Engineer）</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>創代科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路101號10樓</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位 Senior to 小主管 Level 的數據工程師 (Data Engineer)，主要負責 資料庫建置、ETL 流程設計與開發、數據處理與分析。目前創代科技曾執行過的專案包含了 大型語言模型產品開發（涵蓋雲端、地端、雲地混合</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8hlwh</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>20260321</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D02-資料工程師(DE)_旅遊科技部_數據營運組</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>雄獅資訊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路151號</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>我們正在尋找對科技趨勢敏銳、樂於實驗的技術創新人才。你將成為旅遊科技部的技術推進引擎，結合 AI、前沿工具與跨領域思維，探索下一個改變旅遊產業的數位可能。
+1. 介接並整合內外部資料來源，確保資料的高可用性與一致性
+2. 設計、開發、測試與維護</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ppdw</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>像素數科技術有限公司</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>台北市大同區 承德路一段 2 號</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>年薪 1,000,000 ~ 1,800,000元</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+- 監控數據流程和數據質量，及時發現和解決數據品質問題；
+- 維護和更新工程處理中的文件與資料字典；
+- 編寫清晰的程式碼文件和註釋，以確保團隊成員能夠理解和使用你的程式碼；
+- 持續關注數據技術的發展趨勢，不斷學習和探索新的數據技術和工具。
+</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7rkad</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>FAE工程師</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>鼎志電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段96號，嘉新大樓(距離捷運民權西/雙連站步行5分鐘)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>工作內容
+1.技術支援 - 協助客戶處理及排除相關產品品質和技術問題。
+2.教育訓練 - 對國內外客戶進行產品及開發相關內容的教育訓練。
+3.客戶服務 - 依據客戶需求提供相關服務
+4.業務支援 - 與供應商確認新產品規格及應用;將資料建檔並協助</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7ucg4</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>【STAFF】ERP/PLM系統流程規劃設計師 (台北)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>士林電機廠股份有限公司</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>電力機械器材製造修配業</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>台北市士林區 中山北路六段88號12樓</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>月薪 35,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ERP 系統建置與流程優化
+協助 Oracle ERP / 鼎新系統的導入、流程設計、客製開發與例行維運。
+擔任企業內部顧問，理解跨部門流程、提出改善建議、串接資訊系統與營運現場。
+絕對不會是只會「修系統」的角色！
+2.資料庫維運與效能調教
+負責</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7xem0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>允和科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>高雄市前鎮區 建基街9號5樓</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>月薪 35,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1.	自動化數據採集：設計與維護高效能 ETL 爬蟲程式，定期抓取氣象署 (CWA)、環境部等國內外開放資料 (Open Data) 及傳感器數據。
+2.	依據專案需求，進行系統功能開發、優化與維護。
+3.	與產品經理、專案經理協作</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yb0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>英屬開曼群島商萬里雲互聯股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段333號33樓</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>【職務說明】
+       我們正在尋找一位具備高度專業技能的資深資料工程師，加入我們快速成長的資料與AI解決方案團隊。此角色將負責設計並交付可擴展的資料平台、建置資料管道，並推動雲端/地端環境下的資料搬遷，以銜接AI分析應用落地。</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p7ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>資料科學工程師 (Data Engineer) -- 資料科學實驗室 (數數發中心,DDT)_I00018190</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[工作內容]
+職務包含但不限於以下內容
+- 基於 Python 語言之產品開發，推廣及後續維護
+- Docker/Kubernetes 相關技術應用研發
+- 雲端技術應用及研究
+- 創新資料科學工程架構研究及開發
+- 大數據專案開發實作
+</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8hztb</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ETL資料工程師</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>緯德科技股份有限公司 (TechLink Corporation)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號8F-13</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>- 熟悉資料庫之SQL語法執行ETL資料轉換作業(ETL Job Developing、IBM DataStage、Informatica PowerCenter、Microsoft SSIS、Trinity)實務經驗1年以上。
+- 熟悉資料庫安</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5e9ei</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>松凌科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>台北市中正區 衡陽路51號7樓之11</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>專科</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>主要工作項目：
+- 協助客戶核心系統轉換並開發資料轉換程式及驗證資料正確性
+- 依客戶報表需求進行分析與開發及驗證報表正確性
+職務要求：
+- 熟悉資料庫之SQL語法指令(PL/SQL或T-SQL)執行資料轉換及驗證資料正確性實務經驗。
+- 熟悉</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/79ccc</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Garena - (Senior) Data Engineer (資深)資料工程師</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Garena_新加坡商競舞電競有限公司臺灣分公司</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>台北市信義區 松高路11號16樓</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Hi，勇者！我們是 Garena 的 Data Team，我們 Data 夥伴角色組織完善，為 Garena 海內外的遊戲規劃、建構並維護資料量達 PB 級別的全地端資料倉儲，並與數據分析師 (Data Analyst) 合作，將遊戲內各項有趣的</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8rady</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>麥當勞授權發展商_和德昌股份有限公司</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>其他餐飲業</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>台北市中正區 林森南路一號</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>【角色與職責】
+• 負責資料技術底層的實作與優化，將數據產品規劃轉為穩定、高效的技術架構。
+• 參與Data Lakehouse與Feature Store建置，協助PM梳理跨系統資料串接，撰寫程式碼與資料模型，支持使用者自助分析與應用。
+【工</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ecsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資料工程師</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>崴拓資訊有限公司</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>▎ What You'll Do
+1. 數據中心資料整理統計和資料流程維運與開發
+2. Flink即時滾表維運與開發
+3. 視覺化儀表板維運與開發
+▎ What We're Looking For 
+1. 撰寫Python(Pandas、</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vdvc</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>【2026年度研發替代役】資料工程師／資料分析師【數據組】</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>群健科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路363號12樓</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>★ 工作內容：
+負責 Cofit 資料工程與分析工作，包含資料清洗、轉換與 ETL/ELT 流程維護，整合 App、CRM、醫療等多來源資料，使用 SQL/Python 進行資料處理與分析。協助建立維護儀表板，產出數據報告與趨勢分析，支援行銷、營</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vxrw</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>DBA工程師</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>遠鑫網路科技有限公司</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>月薪 50,000 ~ 120,000元</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>。
+3. 設計資料庫備份(xtrabackup)、高可用及災難復原計劃。
+4. 協助開發部門 SQL 語法調優及 index 設計與優化。
+5. Linux 基本操作與 Shell script 撰寫自動運維。
+6. 日常工作、票務和故障排除。
+7</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wrj2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>【C005】ETL工程師</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>一騰資訊服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位思緒清晰、對雲端和地端資料庫都熟悉的ETL工程師，來協助推動金融科技相關系統專案。
+這不只是一份工作，更是與技術與商業策略接軌的關鍵角色！
+【工作內容】
+1. 負責AWS雲端資料倉儲數據管理，包含：來源系統資料導入雲端、雲端倉儲</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zwnr</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>資料工程師 (BI)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>(本職務主要為技術工作而非單純的數據分析)
+1.  商業智慧(BI)專案需求訪談、系統分析並製作系統需求規格書文件
+2.  撰寫整合測試計畫書、測試案例、準備測試資料及測試
+3.  Metadata 中介層設計、Dashboard、Report設</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/37tef</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>職務目的：參與銀行級大型資料倉儲與雲端轉型專案。
+工作內容：
+1.維運數據倉儲 ODS 資料庫：
+•規劃與管理資料庫空間與使用者權限。
+•監控系統運作狀況，進行問題排查與修復。
+•確保資料庫效能與穩定性。
+2.資料導入流程管理：
+•設計與實作</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7p5ll</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ETL 資料工程師/大數據工程師</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>歐立威科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>台北市大同區 鄭州路87號11樓之1</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Pentaho PDI、Talend、Informatica、Microsoft SSIS 等）進行數據抽取、轉換與載入，確保資料正確性與完整性。
+3.熟悉 Python 或 Java 等程式語言，能撰寫 ETL 腳本與自動化流程。
+4.設計並維護 Data</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ugrj</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>20260224</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>果實夥伴股份有限公司</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路610號2樓</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>【工作內容 】
+-  ETL 之開發、處理(資料清理、儲存、分析)與監測
+- 開發與設計專案所需 API 服務並與後端工程師合作，完成系統產品化程序
+- 依據不同業務需求，完成建置/維運/更新各式 Data infra 的需求
+- 與數據產品管理</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7dpwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>短期專案支援資料工程師(2-3個月)(台中)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>葳誠科技有限公司</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>台中市西屯區 科園路一號</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>月薪 70,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>駐點在中科客戶端 
+工作內容
+負責報表資料異常問題之分析與處理，透過 ASP.NET 網頁/SSRS 追蹤資料來源。
+回溯 ETL 作業流程，確認來源資料表是否異常，並重新執行 ETL job 以修正資料。
+協助處理系統操作相關問題，並進行專案成</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zlld</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>20260125</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1.在Hadoop架構的資料倉儲(Data Warehouse)上建立具備擴充性與高可靠性的資料產品，為數據科學家與業務團隊提供穩健的資料基礎。
+2.與數據科學家和業務分析團隊合作，理解需求並提供適用的資料解決方案。
+3.設計並構建</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n58n</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>(C6) 資深數據工程師Senior Data Engineer（內湖）</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>【職位說明】
+參與智慧城市 AI 賦能產品開發，負責建置企業級數據平台(Data as a Service, DaaS)，處理各種形式的資料，並進行完善的資料治理、血緣追蹤與監控。最終將整合生成式 AI（Generative AI）功能，提供智慧</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p0av</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>製造資料科學工程師</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>紫式大數據決策股份有限公司</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>新竹市 光復路二段376-1號2樓</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>碩士</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1.	依據客戶端於製造資料科學需求（例如：製程參數優化、產品瑕疵檢測、設備預測保養）進行資料健檢、開發與導入符合需求的AI演算法，並以實際數據進行離線驗證。
+2.	與客戶端軟體團隊合作，將演算法封裝成API進行系統整合串接，並協</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ww7h</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>20251124</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>資料工程師(雲端工程師)-AI系統整合team【全家便利商店關係企業】</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>精藤股份有限公司</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段61號11樓</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>護），更有完善的公司治理與開發標準，可做為所有資訊人員執行專案時的後盾。
+除此之外，精藤近年來亦不斷追求更多新領域的發展，例如：雲端科技應用、大數據資料分析以及行動裝置管理技術等等，誠摯的歡迎所有對於零售流通有興趣的伙伴一同加入精藤的大家庭。</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p8r6</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>VN-越南廠區-品保主管(越南)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>智惠創富股份有限公司</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>其他金屬相關製造業</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>越南 越南北寧省</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>月薪 75,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>品保儲備幹部(越南)：
+1. 具備沖壓/CNC/表面處理等五金加工製程品質管理相關經驗
+2. 相關客訴處理及報告撰寫,ISO 體系內部稽核與外部認證
+3. 客訴分析及了解IQC/PQC/MQA/TQA 流程管理,客戶稽核資料準備與陪同 
+4.</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pwk7</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>自動化與資訊系統軟體工程師</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>富星科技有限公司</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>自動控制相關業</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>彰化縣彰化市 泰和中街360號</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1、參與 PC-Based 自動化控制系統之程式開發、測試與維護。
+2、依專案需求開發與維護相關應用程式與工具，並協助系統效能與穩定性優化。
+3、協助系統資料整合與應用流程實作，支援設備與系統間之資料交換需求。
+4、參與內部用資訊系統（ERP）相</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/6xijv</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師 (台中)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>微碧愛普科技有限公司</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道二段659號8樓</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>需此職位與產品團隊和前後端工程團隊緊密合作，負責資料基礎建設的穩定性與資料品質，並推動新一代 AI 資料應用的落地。
+【工作內容】
+1. Data Infrastructure 建置與維護：負責 Airflow 的部署、調優與日常維護，確保排程</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xujh</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>【外商】[FIN] Sr. Data Engineer／資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號20樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>年薪 1,200,000 ~ 1,400,000元</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>深資料工程師或相關經驗，並具備獨立主導專案的能力。
+6. 卓越的需求訪談與業務邏輯理解能力，能將複雜的技術概念清晰地傳達給非技術背景利害關係人。
+7. 具備良好的溝通協作能力，主動積極解決問題，並樂於分享知識。
+【我們提供】
+1. 開放、合作且具</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dq30</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>數據工程師｜打造零售界的神級Data Build</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>統一資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路155號8F~10F</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>你是資料界的打怪高手嗎？
+我們正在尋找一位能將數據煉金的工程師，一起升級零售產業的數據系統，從地端到雲端，穩定輸出、精準命中！
+這份工作不只是 coding，更是策略規劃、技術架構與商業價值的 combo 技。
+如果你喜歡優化效能、挑戰架構、解任</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4bma8</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>久浪智醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 新竹縣竹北市生醫路2段150號</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 生醫與影像數據統計分析
+2. 數據庫建立與維護
+3. AI/ML 模型建立
+4. 自動化及優化工作及數據流程
+5. 具備AI Agent &amp; MCP protocol專案經驗
+</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8idjr</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>數據工程師 Data engineer</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>台灣歐力士股份有限公司</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>台北市大安區 復興南路一段303號9樓(大安捷運站旁)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1. Data Pipeline 建立與維護：從原始資料來源到可分析資料的全自動流程。
+2. 異質資料清洗（ETL）：整理各資料來源（如內部系統資料庫、Excel），並確認資料格式正確。
+3. 資料庫管理：負責資料表設計、排程更新邏輯，並優化資料</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ztbt</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號 (或桃園市龜山區頂湖路33號)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>職務影響力
+本職位以資料工程與分析平台建設為核心，負責打造穩定、可擴展且可維運的工程數據基礎設施，作為工程與研發團隊進行數據決策的關鍵支撐。透過提升資料管道品質、系統自動化與整體擴展性，使資料分析工程師與工程團隊能在一致且可信的數據基礎上，規模化</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wzpl</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>【校園徵才】【工程部】部門｜大數據工程師 BigData Engineer (JIRA705)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>全曜財經資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>新北市板橋區 文化路一段266號10樓</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>數據同步、運算模組，使數據分析師可針對不同資料源（Kafka, Mongo, MySQL, MsSQL, ELK, etc.） 的資料進行客製化處理。
+3. 升級與強化數據中台：持續優化既有中台功能、穩定性與可觀測性，學習並實作大數據底層技術以提升系</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8z29l</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Cloud &amp; Data Engineer 雲端與資料工程師</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>阿卡希亞股份有限公司</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>桃園市桃園區 中正路1125號7樓</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Job Summary:
+本職務 Cloud &amp; Data Engineer 將同時建構與維護雲端、資料、AI 與資安相關系統的設計與交付，協同技術團隊成員提供系統整合（System Integrator, SI）服務，服務跨國企業集團或上市櫃客</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yz82</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>數據ETL/資料工程師</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>昇恒昌股份有限公司</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>其他零售業</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>台北市內湖區 新湖二路289號</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>工作內容:
+1 設計和建立資料分析報告和資料儀表板，
+2.提供資訊視覺化及說明分析。
+3.運用統計概念與資料驅動思維，收集和清理各類型資料，並設計資料分析方法，建立相關資料應用。
+4.跨系統資料梳理及資料倉儲整合(ETL)應用(SSIS、</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/878sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>20260226</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>AI工程師</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>汎海科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>新北市三重區 光復路一段61巷27號9樓之3</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Python 後端工程師 / 技術合夥人（SaaS 平台）
+我們不是找員工，而是找一起打造產業平台的夥伴。
+SaaS 後端架構設計
+設計 Multi-tenant 架構
+API 設計與版本控管
+JWT 認證與權限系統
+製程邏輯設計
+可擴充架構規劃</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8molp</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>數據工程師(Data Engineer) - Python/ETL/MongoDB</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>果友科技有限公司</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段333號</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備後端架構思維的「數據工程師」，能與企業客戶的數據分析、工程團隊協作，打造穩定且可擴展的數據處理流程。
+這份職缺主要任務是設計並維運高可靠性的 ETL 與 Airflow 數據流程，確保資料能自動化運行、正確轉換，成為企業決策與</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8urkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>數位發展工程師</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>名人預拌混凝土股份有限公司</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>台南市新市區 中山路183號</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+- 雲端平台（Azure/AWS/GCP）與 DevOps CI/CD
+AI/資料工程師:
+- OCR/NLP 技術解析 PDF 報告。
+- 訓練 AI 模型，讓系統能自動判讀不同格式並填入預設格式。
+- 建立資料清洗與標準化流程，確保回傳資訊與</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zrq0</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>資料工程師(資訊部)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>三立電視台_三立電視股份有限公司</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>電視業</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>台北市內湖區 舊宗路一段159號1樓(114)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>三立電視，為三立集團旗下媒體公司是台灣大型有線電視全媒體頻道。集團下還有多個事業體，跨足電商平台。我們希望應用AI的技術，在海量的訊息中找尋有價值的資料，提高用戶的體驗及便捷度
+工作內容：
+1.熟悉linux系統,略懂AWS架構以及實際操作經驗</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/6dcfl</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>20260320</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>【國泰投信】資料工程師 Data Engineer_I00022210</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>國泰證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號6樓</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Kubernetes）。
+5. 實現湖倉一體（Lakehouse）與存算分離架構。
+【必要條件】
+1. 1 年以上資料工程或資料分析經驗，具備資料處理或資料分析的程式開發能力。
+2. 具備 Python 軟體開發或資料處理經驗。
+3. 具備 Linux 系</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qbni</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>重高科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段162號12樓之2</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>月薪 50,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>【必要條件】
+具備 2 年以上 Python +SQl開發經驗。
+【主要職責】
+使用 Python 產製資料報表：
+1. 產製需求所需資料報表
+2. 產製行銷活動資料報表
+以上曾有 1 項經驗者，尤佳！
+依需求撰寫查詢並進行基礎數據分析
+（如</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvez</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>115年-資料工程師(資深專員／專員) - 行政管理部／資訊組</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>國家住宅及都市更新中心</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路一段21號</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>上線與後續維護
+•與廠商合作進行各業務系統平台資料整合與介接
+【必要條件】
+•三年以上資料工程相關工作經驗，具備獨立完成資料工程項目的能力
+•精通 Python 程式語言，具備良好的程式設計能力與程式碼品質意識，熟悉常用的資料處理函式庫
+•熟悉</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x8mk</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>20251124</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>資料工程師-情報系統二team【全家便利商店關係企業】</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>精藤股份有限公司</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段61號11樓</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>護），更有完善的公司治理與開發標準，可做為所有資訊人員執行專案時的後盾。
+除此之外，精藤近年來亦不斷追求更多新領域的發展，例如：雲端科技應用、大數據資料分析以及行動裝置管理技術等等，誠摯的歡迎所有對於零售流通有興趣的伙伴一同加入精藤的大家庭。</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/84xyg</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>20260116</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>AI圖像標記工程師</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>兆徠科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>台北市內湖區 行愛路77巷69號2樓</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>月薪 32,000元以上</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>- 影像資料整理
+- 影像標記
+在當今資訊科技發展的浪潮下，人工智慧領域成為了未來的發展趨勢。作為人工智慧工程師，您將有機會參與開發最新的機器學習/深度學習技術，應用在產品開發中，並為公司的發展貢獻自己的智慧和能力。
+如果您符合以上要求，請立即</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8efnn</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>20260319</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>【凱基證券/數位創新部】數據工程師</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>凱基證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>台北市中正區 重慶南路一段</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1. 資料倉儲等系統或機器學習建模之資料收集、開發處理與管理維護
+2. 業務單位數據需求開發</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7jogm</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>AJ15-資深雲端資料工程師</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>緯穎科技服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>電腦及其週邊設備製造業</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>新北市汐止區 新台五路一段90號8樓</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備全局視野、深厚技術實力與跨領域協作能力的資深資料工程師，加入雲端資料平台核心團隊。
+您將在企業級Lakehouse與分散式資料處理架構中扮演關鍵角色，負責核心資料平台設計與架構持續演進，同時確保資料從來源端到分析端的準確性、即</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zm9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>20260327</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>前端工程師</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>方達科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>新北市中和區 板南路659號8樓</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位對使用者體驗充滿熱情、具備良好開發習慣的前端工程師，加入我們的產品開發團隊。你將負責打造直覺、互動性高、效能良好的 Web 應用，與設計師、後端工程師密切合作，實現產品功能與使用者介面。
+工作內容
+1.與設計師合作，將 UI/</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pxix</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>20260304</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>(高雄NATC) 軟體測試工程師</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>IBM_台灣國際商業機器股份有限公司</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>高雄市前鎮區 復興四路1號4樓</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">* 手動測試、使用者測試、撰寫自動化測試腳本
+* 根據產品需求設計測試計畫（Test Plan）與測試案例（Test Case）。
+* 執行功能測試、整合測試與回歸測試，確保開發品質。
+* 開發與維護自動化測試腳本（如 Selenium, Appium, JUnit）。
+* 追蹤 Bug 修復進度，並與開發團隊溝通品質風險。
+Your primary responsibilities include: 
+ * Execute System Integration Testing (SIT) for a new core banking system
+ * Develop and run test cases and test scripts
+ * Conduct API testing (via Postman) and backend validation
+ * Log, track, and support defect resolution
+ * Assist with test automation (if applicable)
+ * Collaborate remotely with cross-functional teams and report issues effectively
+</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8jlae</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>BI 數據工程師  (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>神來也麻將_慧邦科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>台北市中正區 羅斯福路二段100號10樓</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1. 建置與維運遊戲數據 ETL / ELT 排程。
+2. 與分析、PM、營運合作，提供即時數據查找並建置固定排程或後台功能。
+3. 進行資料品質檢查、異常偵測與基礎探索分析。
+4. 開發與維護數據後台、API 與資料平台相關功能。
+【專業條</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/6u7bu</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>20260324</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>產品三部 | 資料工程師(高雄)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>騰雲科技服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中華四路45號2樓</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>✅ 工作內容｜你會負責的任務
+1.數據建模：負責設計與維護 MDP 平台的資料模型，確保能有效支撐財務、銷售、行為等多維度主題數據。
+2.ETL 流程開發：配合使用 ETL 工具，撰寫高效能的 T-SQL 邏輯進行數據清洗、轉換與載入。
+3.效能</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xvzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>HUA AO_香港商創金科技有限公司</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大同區 </t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>/CD、Docker 等基礎 DevOps 工具者佳
+3. 參與團隊數據治理與標準制定經驗者尤佳
+【任職資格】
+a. 資訊工程、資料科學、統計、資訊管理等相關理工科系本科以上學歷4年以上
+b. 具備資料工程、BI或數據相關工作經驗 
+c. 樂於</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pr4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>聯想感行銷科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>台北市松山區 民生東路三段135號3樓</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 90,000元</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>【工作內容】
+與團隊協作，共同完成各客戶的資料流開發，同時協助團隊梳理與排除運作中的 data pipeline 產生的各種突發程式狀況，並完成記錄與建檔，您應可獨立開發系統串接、大資料清整。在工作過程中，您會與工程團隊、設計團隊、產品團隊溝通協</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8t66i</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>K100 數據工程部/數據工程師</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>OB嚴選_橘熊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>台北市南港區 八德路四段768巷1弄18號13樓</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1、打造直覺好用的 BI 儀表板，讓數據一看就懂。
+2、【Power BI / Tableau】BI 報表設計與製作，包含儀表板規劃、視覺化呈現與使用者體驗優化。
+3、將營運/行銷數據轉化為決策洞察，支持業績成長。
+4、建立穩定的資料來源（SQL</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zs13</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer【數位數據發展本部】</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>東南旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段60號</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>統性整合資料支撐分析與AI應用的發展
+●	建置優化Data Pipeline，並建立資料品質監控管理機制，確保資料品質和效率
+●	與DA / DS 協作，開發實作數據 / AI產品，參與模型的部署上線與維運
+●	協作工程師設計大規模資料遷移，參與</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tbys</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>20251224</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>【前瞻研究籌獲中心】大數據工程師(台北)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>國家資通安全研究院</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>其他專業／科學及技術業</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中正區 </t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1. 設計並維護高效的大數據資料管道(ETL/ELT)，整合多元資料來源，載入資料湖與資料倉儲
+2. 管理Hadoop/Spark等分散式計算架構，最佳化SQL/NoSQL資料庫效能，確保資料一致與可靠
+3. 建構資料模型，規劃儲存策略以提升查詢</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8rkm1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>20260325</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>【擴編】資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>聖文森商瑞德克斯科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>台中市西屯區 朝富路213號19樓</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+※ 工作專業需求：
+1. 具資料視覺化工具（Tableau / PowerBI / Metabase）經驗</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xdrn</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>AIR SPACE_新地國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>鞋類／布類／服飾品批發業</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>台北市士林區 中山北路五段(近士林捷運站210公尺)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>AIR SPACE為台灣第一女裝品牌，
+我們提供安心的工作環境、人才培育訓練課程，
+願您能成為永續經營的共同夥伴，歡迎加入AIR SPACE團隊！
+【我們在找什麼樣的你】
+熟悉資料庫、ETL 流程與數據建模，能有效整理、清理與分析大量數據，</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8fvcr</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>永慶房產集團_永慶房屋仲介股份有限公司</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段77號12樓</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>永慶房產集團為房仲產業龍頭，用科技創新引領創新變革，歡迎IT領域的優秀夥伴加入!
+工作內容如下：
+1.規劃集團資料流程，達成資料整合綜效。
+2.建置企業數據中台，管控集團資料倉儲品質與正確性。
+3.與資料分析師協同合作，進行資料分析前處理，提供</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78pf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>20260310</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>網管工程師</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>吉利達國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>機械設備租賃業</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>台北市大安區 基隆路二段207號2樓</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>此職位將負責公司內部資訊系統、資料備份及網路環境的維運與改善，屬跨 MIS、網路管理與基礎資料工程的綜合角色。主要工作內容如下：
+一、資料備份與管理（Data Management &amp; Backup）
+•	建置並維護公司資料備份機制（含 NAS、</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wmkv</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>20260210</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>遊戲資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>吉恩立數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段106號5樓</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>我們找的就是你：善於溝通、邏輯清晰及執行力的工程師 !
+負責一款遊戲，
+從資料庫初期的建置發佈以及遊戲整體環境建置，到後續服務的長久運行管理。
+在這裡你不會感到孤單，會有同仁一起參與合作與營運，當然，熟悉後也有需要獨自運作的時刻。
+【工作任務</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tymj</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>春樹科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路62號9樓</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>能、安全與高可用性有信仰，確保系統不僅「能跑」更能「長跑」。
+-AI 協作夥伴 (MLOps Companion)： 模型落地的推手。與演算法團隊聯手，打造高效的 MLOps 循環。
+我們在意的工程文化
+解決問題： 面對不確定性，能拆解問題並快速</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xjqj</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師(錦州街)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>山富國際旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>台北市中山區 錦州街46號10樓</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>月薪 48,000元以上</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">與效能調校。
+與後端工程師協作，確保數據收集與儲存的效率與規範。
+探索並導入新興的數據技術與工具，持續提升團隊的數據處理能力。
+</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/73ifb</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>AI數據工程師</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>建準電機工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>專用生產機械製造修配業</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中正一路120號12樓(近捷運-苓雅運動園區站)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>1. 建立、維護與優化企業數據中台，整合內部各系統資料，確保資料一致性與可用性。
+2. 設計 ETL 流程與資料庫架構，提供 AI 模型與報表系統所需資料。
+3. 監控資料質量，定期進行資料清洗與效能優化，確保數據中台穩定運作。
+4. 報表開發</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xjwv</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>AI 具身智能與系統整合工程師</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>和椿科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>自動控制相關業</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街60號</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+2.系統整合：將 AI 模型（視覺、語義理解）嵌入硬體執行流程，優化 AI 推理與機器人控制（如 ROS2）間的通訊延遲。
+3.邊緣運算：在 NVIDIA Jetson/Orin 等裝置上進行模型部署與資源調配。
+三、機器人數據工程與訓練
+1.</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zyp9</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>20260330</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>太陽能量測/資料分析工程師(竹北)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>艾思特能源股份有限公司</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>精密儀器相關製造業</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新竹縣竹北市 </t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>1. 協助執行太陽能電站之現場檢測與量測作業(台灣及東南亞地區)
+2. 蒐集並整理現場檢測資料，撰寫相關測試與檢測紀錄
+3. 進行數據分析與報告撰寫，需熟悉 Word 文件排版 與 Excel 樞紐分析
+4. 協助撰寫及優化 檢測SOP 與 測試</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8uri5</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>20260326</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>龍騰文化事業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>書籍出版業</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>新北市五股區 五工六路30號(五權七路1號交叉口)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位 資深數據工程師，加入我們打造新一代 AI Knowledge Platform。
+這個角色將聚焦於 RAG（Retrieval-Augmented Generation）核心知識庫與後端平台建設，負責從資料接入、解析、切片、索引</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zjm4</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>【研究發展處】Big Data Engineer 資料工程師 / Senior Big Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>現觀科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段42號2樓</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Dashboard Visualization，並與產品開發團隊進行資料探勘及研究。
+[工作內容]
+1.開發大數據系統資料處理平台
+2.串流資料平行處理程序開發,熟悉分散式運算,平行運算
+3.解決大量資料處理時所衍生的效能,擴充與維護維運資料庫</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7bdqr</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>20260401</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>AI工程師/Data Scientist</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>日成科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>電力機械器材製造修配業</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路2段157號3樓</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>AI工程師/Data Scientist
+1. 熟悉machine learning, advanced pattern recognition, data mining, neural logic, and other data</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/89sj9</t>
         </is>
       </c>
     </row>

--- a/z_RequestData/jobsearch_data104.xlsx
+++ b/z_RequestData/jobsearch_data104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J221"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6436,10 +6436,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A112" t="n">
+        <v>20260330</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -6489,10 +6487,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A113" t="n">
+        <v>20260401</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -6548,10 +6544,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>20260323</t>
-        </is>
+      <c r="A114" t="n">
+        <v>20260323</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -6604,10 +6598,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A115" t="n">
+        <v>20260330</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -6659,10 +6651,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A116" t="n">
+        <v>20260330</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -6717,10 +6707,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A117" t="n">
+        <v>20260311</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -6772,10 +6760,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>20260312</t>
-        </is>
+      <c r="A118" t="n">
+        <v>20260312</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -6844,10 +6830,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A119" t="n">
+        <v>20260331</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -6898,10 +6882,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>20260316</t>
-        </is>
+      <c r="A120" t="n">
+        <v>20260316</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -6952,10 +6934,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>20260327</t>
-        </is>
+      <c r="A121" t="n">
+        <v>20260327</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -7007,10 +6987,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A122" t="n">
+        <v>20260401</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -7063,10 +7041,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A123" t="n">
+        <v>20260401</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -7120,10 +7096,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>20260228</t>
-        </is>
+      <c r="A124" t="n">
+        <v>20260228</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -7175,10 +7149,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A125" t="n">
+        <v>20260326</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -7229,10 +7201,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A126" t="n">
+        <v>20260330</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -7286,10 +7256,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A127" t="n">
+        <v>20260326</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -7340,10 +7308,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A128" t="n">
+        <v>20260401</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -7398,10 +7364,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A129" t="n">
+        <v>20260401</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -7456,10 +7420,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A130" t="n">
+        <v>20260331</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -7509,10 +7471,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A131" t="n">
+        <v>20260330</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -7567,10 +7527,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>20260310</t>
-        </is>
+      <c r="A132" t="n">
+        <v>20260310</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -7621,10 +7579,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A133" t="n">
+        <v>20260326</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -7674,10 +7630,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A134" t="n">
+        <v>20260330</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -7730,10 +7684,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A135" t="n">
+        <v>20260330</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -7787,10 +7739,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A136" t="n">
+        <v>20260330</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -7842,10 +7792,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A137" t="n">
+        <v>20260326</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -7897,10 +7845,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A138" t="n">
+        <v>20260331</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -7954,10 +7900,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>20260323</t>
-        </is>
+      <c r="A139" t="n">
+        <v>20260323</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -8009,10 +7953,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A140" t="n">
+        <v>20260330</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -8064,10 +8006,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A141" t="n">
+        <v>20260331</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -8116,10 +8056,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>20260327</t>
-        </is>
+      <c r="A142" t="n">
+        <v>20260327</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -8170,10 +8108,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A143" t="n">
+        <v>20260330</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -8228,10 +8164,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A144" t="n">
+        <v>20260330</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -8282,10 +8216,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A145" t="n">
+        <v>20260330</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -8336,10 +8268,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A146" t="n">
+        <v>20260330</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -8390,10 +8320,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>20260327</t>
-        </is>
+      <c r="A147" t="n">
+        <v>20260327</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -8444,10 +8372,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A148" t="n">
+        <v>20260326</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -8499,10 +8425,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A149" t="n">
+        <v>20260326</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -8554,10 +8478,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A150" t="n">
+        <v>20260330</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -8610,10 +8532,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>20260328</t>
-        </is>
+      <c r="A151" t="n">
+        <v>20260328</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -8664,10 +8584,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>20260323</t>
-        </is>
+      <c r="A152" t="n">
+        <v>20260323</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -8719,10 +8637,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
+      <c r="A153" t="n">
+        <v>20260324</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -8771,10 +8687,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>20260321</t>
-        </is>
+      <c r="A154" t="n">
+        <v>20260321</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -8825,10 +8739,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A155" t="n">
+        <v>20260326</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -8882,10 +8794,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A156" t="n">
+        <v>20260330</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -8938,10 +8848,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A157" t="n">
+        <v>20260330</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -8995,10 +8903,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A158" t="n">
+        <v>20260330</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -9050,10 +8956,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A159" t="n">
+        <v>20260330</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -9103,10 +9007,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>20260327</t>
-        </is>
+      <c r="A160" t="n">
+        <v>20260327</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -9162,10 +9064,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A161" t="n">
+        <v>20260330</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -9215,10 +9115,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A162" t="n">
+        <v>20260331</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -9272,10 +9170,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A163" t="n">
+        <v>20260330</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -9324,10 +9220,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A164" t="n">
+        <v>20260401</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -9379,10 +9273,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A165" t="n">
+        <v>20260331</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -9436,10 +9328,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
+      <c r="A166" t="n">
+        <v>20260325</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -9489,10 +9379,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A167" t="n">
+        <v>20260331</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -9546,10 +9434,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A168" t="n">
+        <v>20260330</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -9601,10 +9487,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A169" t="n">
+        <v>20260330</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -9656,10 +9540,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A170" t="n">
+        <v>20260331</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -9715,10 +9597,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A171" t="n">
+        <v>20260326</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -9769,10 +9649,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>20260224</t>
-        </is>
+      <c r="A172" t="n">
+        <v>20260224</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -9825,10 +9703,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>20260327</t>
-        </is>
+      <c r="A173" t="n">
+        <v>20260327</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -9881,10 +9757,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>20260125</t>
-        </is>
+      <c r="A174" t="n">
+        <v>20260125</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -9936,10 +9810,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A175" t="n">
+        <v>20260326</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -9989,10 +9861,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A176" t="n">
+        <v>20260326</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -10043,10 +9913,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>20251124</t>
-        </is>
+      <c r="A177" t="n">
+        <v>20251124</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -10096,10 +9964,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A178" t="n">
+        <v>20260330</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -10152,10 +10018,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A179" t="n">
+        <v>20260330</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -10207,10 +10071,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
+      <c r="A180" t="n">
+        <v>20260325</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -10261,10 +10123,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A181" t="n">
+        <v>20260330</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -10317,10 +10177,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A182" t="n">
+        <v>20260330</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -10372,10 +10230,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A183" t="n">
+        <v>20260330</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -10429,10 +10285,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A184" t="n">
+        <v>20260326</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -10483,10 +10337,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A185" t="n">
+        <v>20260326</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -10536,10 +10388,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A186" t="n">
+        <v>20260330</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -10589,10 +10439,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A187" t="n">
+        <v>20260330</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -10642,10 +10490,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A188" t="n">
+        <v>20260401</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -10698,10 +10544,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>20260226</t>
-        </is>
+      <c r="A189" t="n">
+        <v>20260226</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -10757,10 +10601,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A190" t="n">
+        <v>20260326</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -10810,10 +10652,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A191" t="n">
+        <v>20260401</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -10867,10 +10707,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
+      <c r="A192" t="n">
+        <v>20260325</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -10921,10 +10759,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>20260320</t>
-        </is>
+      <c r="A193" t="n">
+        <v>20260320</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -10978,10 +10814,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A194" t="n">
+        <v>20260401</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -11038,10 +10872,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A195" t="n">
+        <v>20260330</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -11095,10 +10927,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>20251124</t>
-        </is>
+      <c r="A196" t="n">
+        <v>20251124</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -11148,10 +10978,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>20260116</t>
-        </is>
+      <c r="A197" t="n">
+        <v>20260116</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -11203,10 +11031,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>20260319</t>
-        </is>
+      <c r="A198" t="n">
+        <v>20260319</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -11256,10 +11082,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>20260327</t>
-        </is>
+      <c r="A199" t="n">
+        <v>20260327</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -11309,10 +11133,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>20260327</t>
-        </is>
+      <c r="A200" t="n">
+        <v>20260327</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -11363,10 +11185,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>20260304</t>
-        </is>
+      <c r="A201" t="n">
+        <v>20260304</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -11427,10 +11247,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A202" t="n">
+        <v>20260330</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -11483,10 +11301,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>20260324</t>
-        </is>
+      <c r="A203" t="n">
+        <v>20260324</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -11538,10 +11354,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A204" t="n">
+        <v>20260401</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -11595,10 +11409,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A205" t="n">
+        <v>20260330</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -11648,10 +11460,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A206" t="n">
+        <v>20260401</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -11703,10 +11513,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A207" t="n">
+        <v>20260330</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -11758,10 +11566,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>20251224</t>
-        </is>
+      <c r="A208" t="n">
+        <v>20251224</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -11812,10 +11618,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>20260325</t>
-        </is>
+      <c r="A209" t="n">
+        <v>20260325</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -11866,10 +11670,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A210" t="n">
+        <v>20260330</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -11922,10 +11724,8 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A211" t="n">
+        <v>20260331</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -11978,10 +11778,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>20260310</t>
-        </is>
+      <c r="A212" t="n">
+        <v>20260310</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -12032,10 +11830,8 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>20260210</t>
-        </is>
+      <c r="A213" t="n">
+        <v>20260210</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -12088,10 +11884,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A214" t="n">
+        <v>20260331</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -12143,10 +11937,8 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A215" t="n">
+        <v>20260330</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -12198,10 +11990,8 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A216" t="n">
+        <v>20260330</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -12253,10 +12043,8 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A217" t="n">
+        <v>20260331</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -12309,10 +12097,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>20260330</t>
-        </is>
+      <c r="A218" t="n">
+        <v>20260330</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -12364,10 +12150,8 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>20260326</t>
-        </is>
+      <c r="A219" t="n">
+        <v>20260326</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -12417,10 +12201,8 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A220" t="n">
+        <v>20260401</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -12473,10 +12255,8 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>20260401</t>
-        </is>
+      <c r="A221" t="n">
+        <v>20260401</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -12522,6 +12302,6278 @@
       <c r="J221" t="inlineStr">
         <is>
           <t>https://www.104.com.tw/job/89sj9</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>20260522</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>維修工程師</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>睿運科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>精密儀器相關製造業</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>桃園市楊梅區 中山北路一段199巷67號</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>月薪 35,000元以上</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>高中職、專科</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1. 現場測試、維修及相關售後服務。
+2. 提供維修的內容與報價。
+3. 基本客訴應對。
+4. 配合客戶維修時間，至客戶端進行例行檢查及保養。
+5. 分析產品功能異常狀況，並建立資料庫。
+6. 分析產品功能異常狀況，並建立資料庫。
+產品維修</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8surj</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>20260517</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>網頁前端工程師</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>紫海數位科技有限公司</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>數位內容產業</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區 環南路二段11號</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>月薪 33,000 ~ 43,000元</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>技術與新工具
+加分條件：
+熟悉資料庫操作
+擅長工具：
+VSCode、GIT</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78gb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>20260427</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>核桃運算股份有限公司</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路一段9號4樓</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備 3-5 年經驗的資料工程師，加入我們的數據團隊。您將負責設計、構建並優化高效率的 Data Pipeline，確保資料從來源端到分析端的準確性與即時性。 此職位不僅需要強大的 Python 與 ETL 開發能力，更需要您對</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8waxf</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>20260514</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>【Data Engineer】 資料工程師</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>新加坡商昇新科技股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞湖街58號5樓</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>我們正處於數據架構升級的關鍵階段。尋找一位數據工程專家與我們共同重新定義數據流。
+你將負責冷熱數據分離架構的落地，並優化我們的 Data Warehouse 架構，確保在海量數據環境下，數據依然能兼具查詢效能與成本。
+【你將面臨的核心技術挑戰】</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x352</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>IT資料工程師(Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>GARMIN_台灣國際航電股份有限公司</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>電信相關業</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>新北市汐止區 新台五路一段97號37樓</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【Job Description】
+We are seeking a highly skilled and motivated IT Data Engineer to join our team in Taiwan. This role involves designing, building, and maintaining scalable data pipelines, ensuring data reliability, and enabling insights that drive critical business decisions. The ideal candidate will have a strong background in distributed systems, database management, and data analytics tools, combined with a passion for innovation and continuous improvement.
+【Responsibilities】
+1.	Data Pipeline Development
+	- Design, develop, and optimize scalable data pipelines using Hadoop, Spark, and Kafka.
+        - Ensure real-time and batch data processing pipelines meet business requirements.
+2.	Database Management
+        - Write complex SQL queries and manage RDBMS platforms such as Oracle, MSSQL, and PostgreSQL.
+        - Implement and maintain data models and warehouses for analytics.
+3.	Workflow Automation
+        - Develop and maintain automated workflows using tools like Apache Airflow.
+4.	Programming and Development
+        - Build efficient and maintainable solutions using Python or Scala.
+        - Collaborate with cross-functional teams to integrate data solutions.
+5.	Containerization and Deployment
+        - Leverage Docker and Kubernetes to deploy and manage applications in a containerized environment.
+6.	Data Visualization and Analytics
+        - Create interactive dashboards and reports using Qlik, Tableau, or PowerBI.
+7.	System Administration and Scripting
+        - Perform Linux system administration and scripting to support data infrastructure.
+【Skills】
+1.     Essential:
+        - Proven experience with distributed systems like Hadoop, Spark, and Kafka.
+        - Strong SQL skills and hands-on experience with Oracle, MSSQL, and PostgreSQL.
+        - Proficiency in Python or Scala for data engineering tasks.
+        - Experience with workflow schedulers like Apache Airflow.
+        - Familiarity with Docker, Kubernetes, and containerization technologies.
+        - Solid understanding of data modeling and warehousing principles.
+        - Knowledge of Linux administration and shell scripting.
+        - Expertise in using BI tools such as Qlik, Tableau, or PowerBI.
+2.     Desirable:
+        - Experience implementing lakehouse architectures and managing Iceberg tables on S3 object storage (a plus).
+        - Ability to develop and deploy REST APIs and web services.
+        - Familiarity with AI/ML pipelines and associated tools.
+3.     Preferred Skills:
+        - Strong analytical and problem-solving skills.
+        - Effective communication and teamwork abilities.
+        - Ability to work in a fast-paced, dynamic environment with attention to detail.
+</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7z55c</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>AI Data Engineer AI 資料工程師</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>摩速科技有限公司</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>台北市大安區 仁愛路三段17號3樓</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>性、可解釋性、結果正確性
+- 調查資料異常與不一致問題，找出根本原因，並建立可持續的預防與監控機制。
+- 與產品、商務與工程團隊合作，對齊資料定義並交付關鍵資料資產。
+- 建立或延伸 AI 產品功能，例如：Agent workflow、推薦邏輯、自</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91odq</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>重高科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段162號12樓之2</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Technical Skills)--
+我們希望候選人在以下多數領域具備實作經驗：
+1. Python：精通 Python，特別是在資料工程與自動化流程的應用（而不僅僅是撰寫簡單腳本或 ML 模型）。
+2. SQL：專家級別，具備 BigQuery 或類似雲端資料</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvez</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>20260522</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>【AI Lab】資深數據工程師 Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>愛卡拉互動媒體股份有限公司</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中山區 </t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>【Responsibilities】
+- Design, build, and maintain scalable data pipelines that meet evolving product and analytics needs.
+- Identify, design, and implement internal process improvements: automating manual processes, optimizing data delivery, re-designing infrastructure for greater scalability, etc.
+- Create data tools that enable analytics and data scientist team members to build and ship faster.
+- Build and maintain the services that deliver our data to product, analytics, and external consumers.
+- Partner with data and analytics teams to evolve our data infrastructure.
+- Support cross functional, cross BU data integration tasks.
+【Must to Have】
+- Bachelor's degree in Computer Science, Engineering, or a related field, or equivalent practical experience; Master's is a plus
+- Strong proficiency in Python 3.10+ and shell scripting (Bash), with 5+ years of backend / data engineering experience and 3+ years owning production data pipelines
+- Experience with workflow orchestration tools, e.g. Argo Workflow, Airflow, Dagster
+- Experience with RDBMS, OLAP, and search databases, e.g. PostgreSQL, StarRocks (or BigQuery / ClickHouse / Snowflake / Druid), Elasticsearch
+- Experience with backend API development and deployment, e.g. gRPC, REST (FastAPI)
+- Experience deploying and operating services on Kubernetes with Docker
+- Comfortable developing, deploying, and debugging in Linux environments
+【Nice to Have】
+- Basic knowledge of machine learning algorithms
+- Basic knowledge of Data Lake and Data Warehouse Design
+- Experience with streaming processing systems, e.g. Kafka, Apache Flink, Cloud Dataflow, Apache Beam, Pub/Sub
+- Experience with Go programming language
+- Experience with gRPC and Protocol Buffers
+- Experience with production-grade operations — monitoring, debugging, and maintaining your own work after deployment</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91m1t</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>【外商】[RC-Data] Data Engineer / 資料工程師</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路捷運中山站六號出口共構大樓</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>【職位亮點】
+1. 數據規模化：處理全球跨時區、千萬級日活躍用戶產生的金融級即時交易數據流。
+2. 技術主權：參與從 0 到 1 的架構重構與技術選型，我們鼓勵工程師定義數據標準。
+3. 前沿技術棧：深度實踐三層式資料湖架構（Medallion</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wyu9</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>資料工程師 (電商專案)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>碩誠國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路170號14樓D室</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+3.跨部門協作: 訪談需求單位，配合業務目標，應用AI智能模型與數據技術規劃落地於業務場景之方案。
+4.數據處理與特徵工程: 從零開始進行數據清洗、特徵工程及分析，確保數據質量與模型效能最佳化。
+5.資料建模分析: 透過訓練機器學習模型及數據分析，</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/915ue</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>20260517</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師(錦州街)</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>山富國際旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>台北市中山區 錦州街46號10樓</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>月薪 48,000元以上</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">與效能調校。
+與後端工程師協作，確保數據收集與儲存的效率與規範。
+探索並導入新興的數據技術與工具，持續提升團隊的數據處理能力。
+</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/73ifb</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>成強科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>新北市林口區 仁愛路二段502號1808A</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>月薪 32,000 ~ 40,000元</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>公司目前正著手跨領域製作新型遊戲  (運動相關)，
+詳見官網:https://jacfit.com.tw/
+主要工作內容:
+1.對現有資料分析算法進行維護。
+2.與研發團隊針對設備軟體數據資料，進行採集及分析。
+3.根據產品開發要求，與團隊協作</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8e1v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>開元食品工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>其他食品製造業</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>台北市內湖區 民善街</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士、博士</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具創新精神並熱衷於資料科學領域的 資料工程師 加入我們的團隊。您將負責建立及維護高效的資料處理架構，確保數據在多元系統間流暢流通，並能夠進行高效的數據存儲與分析。若您對資料技術充滿熱情，並擁有相關的技能與經驗，我們非常期待您的加入</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8lttn</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>數據工程師（Data Engineer）</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>創代科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路101號10樓</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>定性。
+- 運用 Airflow、dbt 等工具，設計並優化高效、可觀測（Observable）的現代化資料管線。
+- 與機器學習工程師合作，建置穩定可靠的機器學習資料管線（ML Pipeline），支援模型訓練、部署與推論流程。
+- 參與資料湖倉</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ys29</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師 (台中)</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>微碧愛普科技有限公司</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道二段659號8樓</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>需此職位與產品團隊和前後端工程團隊緊密合作，負責資料基礎建設的穩定性與資料品質，並推動新一代 AI 資料應用的落地。
+【工作內容】
+1. Data Infrastructure 建置與維護：負責 Airflow 的部署、調優與日常維護，確保排程</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xujh</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>數據工程師 / Data Engineer (Data Infrastructure)</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>富華創新股份有限公司台中分公司</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>建築及工程技術服務業</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>台中市北屯區 太原路三段1315號</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士、博士</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>協助各業務單位理解數據價值，推動企業從「經驗法則」逐步邁向「數據驅動」的決策模式。
+▍我們期待你具備
+・3 年以上資料工程、後端開發或資料庫管理經驗，精通 SQL 與 Python。
+・熟悉 GCP 雲端數據與 AI 生態系：具備</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zban</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>資料工程師（Python／PySpark）(FAM)</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>【工作內容】
+．使用 Python 進行資料處理、分析及自動化程式開發。
+．使用 PySpark 執行大數據資料處理與分析作業。
+．協助資料清理、轉換、整合及維護資料品質。
+．製作資料視覺化報表與分析儀表板。
+．配合專案需求進行資料分析與技術支援</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y61l</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>行銷部-數據工程師 ( Data Engineer )</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>全聯福利中心_全聯實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>量販流通相關業</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>台北市中山區 敬業四路33號</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>動力，能適應快速變化的技術環境，持續精進技能 
+4. 勇於挑戰創新 - 保持開放心態，不設限自己的發展，樂於嘗試新技術與跨領域合作
+數據工程師的核心挑戰與工作內容：
+1. 數據處理與自動化 — 了解與整合異質數據來源（API、資料庫、CSV、</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7xcgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>20260413</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>文境資科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>專門設計相關業</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師
+1.資料稽核(Data Auditing)、收集(Data Collection)、整合作業(Data Integration) 等資料分析前處理作業
+2.有MS SQL server、SSIS、SSRS</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7g1tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Tableau資料工程師</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>緯德科技股份有限公司 (TechLink Corporation)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號8F-13</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>- 熟悉數據分析和Tableau報表開發實務經驗1年以上。
+- 熟悉資料庫安裝、設定及操作實務經驗1年以上。(Oracle、MS SQL Server、MySQL至少一種)
+- 可獨立或與團隊合作，工作態度積極、負責，能配合公司規定。
+- 依不同</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>20260423</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>【台北 / 彈性遠端】Sr. Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>布魯斯人事顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中正區 </t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>月薪 1,400,000元以上</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1. 負責大規模資料的雲端基礎架構設計與演進，涵蓋資料流、整合處理、儲存分析與事件偵測等核心能力。
+2. 與相關團隊協作，提出並實作資料架構的優化與轉移計畫，打造具高可用性、可擴展性與韌性的基礎設施。
+3. 兼顧業務成長與工程實作</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wrnj</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>春樹科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路62號9樓</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>能、安全與高可用性有信仰，確保系統不僅「能跑」更能「長跑」。
+-AI 協作夥伴 (MLOps Companion)： 模型落地的推手。與演算法團隊聯手，打造高效的 MLOps 循環。
+我們在意的工程文化
+解決問題： 面對不確定性，能拆解問題並快速</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xjqj</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>營造 ISO 品管稽查員（ISO 9001）(台北)</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>大三億營造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路168號10樓</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>月薪 45,000元以上</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>負責公司品質管理系統（ISO 9001）之稽核、維護與推動，確保各工程專案與內部作業符合品質管理制度要求，並持續提升專案執行品質與制度落實程度。
+主要工作內容
+（一）內部稽核執行
+1.執行公司各工程專案 ISO 9001 內部稽核作業
+2.規</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zyjz</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>[高雄]兼職行政助理</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Linker Vision Co., Ltd._鑫蘊林科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>高雄市鼓山區 蓬萊路23號</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>月薪 196 ~ 196元</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Teams）
+•協助主管日常行政事務與優先事項管理
+3. 招募與人資營運支援（People Operations）
+•協助招募流程運作：面試安排、候選人聯繫
+•支援人資相關行政作業與資料整理
+4. 採購、差旅與內部活動支援
+•採購流程協助與費用單據整理</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91s58</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>旺旺中時媒體集團_(CT) Data Engineer（資料工程師）</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>旺旺中時媒體集團_工商財經數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>電視業</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>台北市萬華區 艋舺大道303號</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>本職位為Data Engineer（資料工程師）
+（依資歷可掛 Senior Data Engineer）
+工作內容 :
+● 設計與實作跨平台資料收集流程（API 與後台匯出並行）
+● 串接並維運以下類型資料來源（依實際情況）：
+YouTube</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wttd</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>【國泰投信】資深資料工程師 Senior Data Engineer_I00022193</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>國泰證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號6樓</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>定 ETL 資料處理流程（資料存取、蒐集、處理和儲存）的開發標準與最佳實踐，確保系統的高效、穩定與可擴展性。
+4. 負責數據架構的效能優化，指導並帶領團隊解決技術難題。
+【必要條件】
+1. 5 年以上資料工程經驗，具備分散式系統與容器化經驗。
+2</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qbnl</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資深資料工程師(Python)</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>宇利峯有限公司</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>台中市西屯區 市政路386號</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>職位概要:
+我們正在尋找一位專精於資料整理和Python開發的Python資料工程師，主要負責資料的清洗、標準化和品質控制工作。
+1. 數據清洗和標準化:
+- 處理原始資料，識別和處理異常值。
+- 統一資料格式和編碼標準。
+- 補齊缺失值和修正</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>眾匯智能健康股份有限公司</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>其他醫療保健服務業</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>台北市南港區 三重路19-13號E棟5樓(南港軟體園區)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>數位健康產業是台灣的另一座護國神山，歡迎有志於探索數位健康創新事業模式發展之夥伴，加入我們的團隊!
+1.健康數據庫之清理、彙整及運用管理
+2.參與開發【AI分身健康管理】服務
+3.支援營運團隊各種AI專案之數據運用
+4.協助管理階層決策所需數據分析運用
+5.其他AI或數據技術創新服務開發</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5wvxj</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>20260514</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Data Engineer (Mid Level)  資料工程師（中階）</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>極酷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路2段26號2樓</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> optimize scalable data infrastructure.
+此角色將支援公司整體資料工程專案，包括 BigQuery 數據倉儲優化、事件追蹤品質與資料管線建置。
+ This role will support company-wide</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvll</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>(C6) 資深數據工程師Senior Data Engineer（內湖）</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>【職位說明】
+參與智慧城市 AI 賦能產品開發，負責建置企業級數據平台(Data as a Service, DaaS)，處理各種形式的資料，並進行完善的資料治理、血緣追蹤與監控。最終將整合生成式 AI（Generative AI）功能，提供智慧</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p0av</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>圖靈數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>台北市中正區 中山北路一段2號11樓</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>行銷判讀，運營，轉化方面的戰略支持與技術方法。成員大多是技術工程師組成，協助客戶收集有用的數據，了解數據，利用數據。
+目前是 Google Marketing Platform、Mixpanel、AB Tasty 認證合作夥伴。
+公司福利：
+・</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7v0e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>20260510</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D02-資料工程師(DE)_旅遊科技部_數據營運組</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>雄獅資訊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路151號</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>我們正在尋找對科技趨勢敏銳、樂於實驗的技術創新人才。你將成為旅遊科技部的技術推進引擎，結合 AI、前沿工具與跨領域思維，探索下一個改變旅遊產業的數位可能。
+1. 介接並整合內外部資料來源，確保資料的高可用性與一致性
+2. 設計、開發、測試與維護</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ppdw</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>英屬開曼群島商萬里雲互聯股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段333號33樓</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>【職務說明】
+       我們正在尋找一位具備高度專業技能的資深資料工程師，加入我們快速成長的資料與AI解決方案團隊。此角色將負責設計並交付可擴展的資料平台、建置資料管道，並推動雲端/地端環境下的資料搬遷，以銜接AI分析應用落地。</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p7ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>AI資料工程師</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>力新國際科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>台北市內湖區 新湖一路128巷15號6樓</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> schema設計、KG-RAG整合。
+七、設計多租戶資料隔離（Multi-tenant Collection/ Namespace），防止跨租戶資料污染。
+八、實作增量同步機制：文件變更偵測、CDC、增量索引，避免每次全量重建。
+九、建構Data</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/9188l</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D4000 資料工程師(湖倉平台)</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>富邦媒體科技股份有限公司(富邦momo)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街96號4樓</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>資料品質檢核、排程監控儀表板等。
+● 設計並實作數據存取 API，為下游分析與 AI/ML 團隊提供穩定的數據服務介面。
+● 撰寫完整的單元測試與整合測試，確保交付程式碼符合軟體工程品質標準。
+3. 數據串流與即時處理（加分項）
+● 協助設計與開發即</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y67g</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>ETL資料工程師</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>欣創科技有限公司</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號9樓之4</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>1. 熟悉執行ETL資料轉換作業(Informatica PowerCenter、IBM DataStage、Microsoft SSIS、Trinity等ETL工具)
+2. 資料庫安裝、設定及操作實務經驗
+3. 具備STORE</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/80lq4</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>20260511</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>像素數科技術有限公司</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>台北市大同區 承德路一段 2 號</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>年薪 1,000,000 ~ 1,800,000元</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+- 監控數據流程和數據質量，及時發現和解決數據品質問題；
+- 維護和更新工程處理中的文件與資料字典；
+- 編寫清晰的程式碼文件和註釋，以確保團隊成員能夠理解和使用你的程式碼；
+- 持續關注數據技術的發展趨勢，不斷學習和探索新的數據技術和工具。
+</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7rkad</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>科技部_Data Engineer 數據工程師 (Data &amp; AI Product)</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>美好證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路三段２號4樓</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>】
+我們正在打造新一代的 DATA/AI 智能化運轉體系，以先進的數據工程、資料平台與 AI 技術，推動投資研究、產品創新與顧問服務的核心能力全面升級。
+此角色將負責設計、建置與維運公司的核心數據基礎設施 (Data &amp; AI Platform)</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7b6bq</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>【數據】資料工程師</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>將來商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段95號6樓</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>一、雲端數據架構設計： 負責設計並管理基於公有雲（AWS, GCP 或 Azure）的資料倉儲（Data Warehouse）與數據湖（Data Lake）架構，建立穩健且具擴展性的底層環境。
+二、 ETL 開發： 運用 Python、SQL 或</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x4v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>英屬維京群島商嘉碼科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>台中市西屯區 工業三十八路210號3樓之6</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位數據工程師，不僅具備扎實的技術底子，更擁有主動積極、樂於挑戰的特質。
+加入我們後，您將在這個充滿活力、尊重多元的環境中扮演關鍵角色，透過打造穩健的數據基礎與管道，協助團隊從資料中萃取價值、加速產品與業務的創新。
+如果您對資料領域充</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vvrv</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>AI 原生資料工程師</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>104人力銀行_一零四資訊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>新北市新店區 寶中路119號之一10樓(231)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>月薪 65,000元以上</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>一、協助 AP 遷移與營運
+  1. 將運作於 legacy 資料湖上的 APs 遷移到湖倉上。
+    - 會掌握到支援實際產品、基於 AWS 的開發生命週期及實務 CI/CD 流水線。
+    - 可參與 Databricks 資料應用程式的</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91l06</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ETL資料工程師</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>緯德科技股份有限公司 (TechLink Corporation)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號8F-13</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>- 熟悉資料庫之SQL語法執行ETL資料轉換作業(ETL Job Developing、IBM DataStage、Informatica PowerCenter、Microsoft SSIS、Trinity)實務經驗1年以上。
+- 熟悉資料庫安</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5e9ei</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>【研究發展處】Big Data Engineer 資料工程師 / Senior Big Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>現觀科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段42號2樓</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Dashboard Visualization，並與產品開發團隊進行資料探勘及研究。
+[工作內容]
+1.開發大數據系統資料處理平台
+2.串流資料平行處理程序開發,熟悉分散式運算,平行運算
+3.解決大量資料處理時所衍生的效能,擴充與維護維運資料庫</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7bdqr</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>康統醫學科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>台北市中正區 北平東路16號8樓</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>熟悉至少一種關聯式資料庫：PostgreSQL / MySQL / SQL Server 其一或多種。會設計 schema（正規化）、index、view、stored procedure。
+扎實 SQL 能力：複雜 JOIN、視圖、</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x02n</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>工務 (無經驗可但需積極、工作內容皆會教學、有工務經驗佳)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>普渼登實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>土木工程業</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>台北市松山區 南京東路5段46號6樓</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>月薪 32,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>高中職以下、高中職、專科</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>0,與同事、主管能正向友善溝通
+1,工班的調度、溝通
+2,與工地現場承辦協調、溝通
+3,進場時間與施工材料管控
+4,現場監工、驗收、缺失完工
+5,計價請款單製作、提交
+6,其他主管交辦事項
+說明：
+0,公司賺得多工作也多，希望可以找到經營一輩子的地方你可以考慮我們公司
+1,大部分時間會跑工地，必須自備機車通勤
+2,剛進公司需要熟悉公司產品及服務內容
+3,抗壓性高，善於溝通
+4,主動學習，主動學習，對工作有責任心
+5,出差通勤、住宿、基本餐費公司提供
+工作內容確實掌握後，自主服務專案有案件分潤可以努力
+**若為有能者會迅速彈性調整薪資，薪水不會止步不前**
+**正式上班後會依表現於每季度調整薪資**</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8kybq</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>後端 - 軟體工程師 | JAVA Developer (擴編招募中)  Fintech</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>一通數位有限公司</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路288號7樓</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 80,000元</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自我介紹
+We are a Hong Kong listed, licensed securities and compliant futures brokerage firm, with our holding company having successfully completed an initial public offering on the Nasdaq in 2022 (Nasdaq: TOP).
+Building on our proven Hong Kong based business model and solid industry expertise, we have established an International Securities Software Maintenance and Research &amp; Development Centre in Taipei. The centre is dedicated to the development and continuous enhancement of our international securities application platforms, delivering stable, high-quality systems to global clients.
+As part of our team, you will participate in the analysis, design, development, and testing of software and services across multiple products. We regard each team member as a key partner and provide opportunities for cross-functional collaboration, enabling you to strengthen your ability to clarify complex requirements and resolve real-world problems.
+We foster a culture of knowledge sharing and continuous learning within the team, encouraging professional growth and technical excellence. Our goal is to grow together with our people and build a sustainable, long-term development model.
+我們是香港上市上櫃的持牌證券與合規期貨經紀商，總公司並於2022年正式於納斯達克上IPO (Nasdaq: TOP) 建基於香港的商業模式及經驗，我們在台北設立了國際證券軟體維護暨研發中心，主力開發和完善的國際證券應用平台系統提供給客戶。你將會參與不同產品的軟體與服務之分析、設計、開發及測試。我們將您視為重要的夥伴且能在跨部門的溝通中培養釐清問題以及解決問題能力，並且營造部門內相互學習的風氣，與更精進自我的學習態度，期望能與夥伴們共同成長以達成永續經營的發展模式。
+工作內容
+- 與團隊合作，負責交易平台後端服務設計、開發、建置與維護
+- 提升解決方案的效能，穩定性，可擴充性和發展彈性
+- 與產品開發、專案支援以及前端、QA等團隊密切合作
+- 熟開發流程，並配合CI/CD，DevOps等開發模式
+- 能快速學習且適應變化，以滿足不斷改變的環境需求
+- 支援團隊的開發工作，例如幫助維護backlog, 優化, sprint planning...等
+- 確保符合標準和開發的最佳方法，包括系統更新管理, 版更管理, 及程式碼管理
+- 主動，擁有獨立思考和良好的溝通和邏輯能力，同時喜歡與團隊溝通思辨、合作解決問題並達成目標。希望您以開發者以使用者的角度去開發，讓用戶體驗更好
+希望你會
+- Java Spring Framework /Java Spring Boot實務經驗
+- 有微服務經驗(維護或開發都可)
+- 有OpenAPI/Message Queue使用經驗
+- 有 Docker/Kubernetes微服務架構使用經驗(optional)
+- NoSQL如Redis/MongoDB使用經驗(optional)
+- 系統分析實務經驗(optional)加分
+職務需求
+1. 依據專案需求進⾏系統設計與功能規劃。
+2. Java程式碼調優。
+3. 開發相關⽂件編寫。
+4. 參與產品開發技術⽅案制定。
+面試流程
+#面試流程 (採遠端面談)
+第一階段面談（人事聊聊）公司介紹、背景了解、初步技術問答以及第二階段面試準備
+第二階段面談（技術主管與部門夥伴們）線上技術面試以及主管聊
+【一通數位想對每一位正在找方向的你，說幾句話】
+★ 不知道自己想做什麼很正常。勇敢去嘗試，慢慢找出真正喜歡與不喜歡的事物。
+★不是本科系畢業也沒關係，人生的道路是靠「不斷嘗試」走出來的，而不是一開始就能「完美規劃」的。
+★相信你的直覺，它會在很多關鍵時刻幫你做出最適合的選擇。
+★隨時問問自己「此刻我最在意的是什麼？」不同階段會有不同答案，這很正常。
+★Be authentic！面試不只是考核，更是雙向的了解與匹配，找到彼此都期待的未來合作才是最重要的。
+★Find your passion！才能走得長久、走得踏實。
+★我們希望，未來你在一通數位所累積的經驗與專業，能成為你未來職涯中更有競爭力的養分。
+★ 無論現在在哪個階段，請勇敢探索、勇敢前進，未來一定會有屬於你的舞台。 
+</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/81utd</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>20260409</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>遊戲資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>吉恩立數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段106號5樓</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>我們找的就是你：善於溝通、邏輯清晰及執行力的工程師 !
+負責一款遊戲，
+從資料庫初期的建置發佈以及遊戲整體環境建置，到後續服務的長久運行管理。
+在這裡你不會感到孤單，會有同仁一起參與合作與營運，當然，熟悉後也有需要獨自運作的時刻。
+【工作任務</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tymj</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>20260512</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>東海大學智慧永續循環經濟研究中心誠徵資料工程師</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>東海大學</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>其他教育服務業</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道四段1727號</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具環境工程背景、能將專業知識轉化為結構化資料與知識模型的人才，加入智慧永續循環研究中心，共同建構以環工知識為核心的 AI 與知識圖譜系統。
+本職位的核心任務不是單純做資料清洗或模型訓練，而是：
+把環境工程的「機制、概念與流程」</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y8zy</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D4000 資料工程師(推薦/搜尋)</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>富邦媒體科技股份有限公司(富邦momo)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街96號4樓</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1. 負責推薦、搜尋平台系統的資料流設計，並協助開發滿足相關數據產品發展的需求，協助業務團隊發揮數據商業價值
+2. 與資料科學家、演算法工程師、資料分析師等，協作開發推薦、搜尋引擎模型，進行機器學習、深度學習之模型自動化、模型服務架</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8lxd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>20260511</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Data Engineer (Mid Level)  資料工程師（中階）</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>極酷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路2段26號2樓</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✨加入 KICKS CREW，與我們一起成長！CAN'T STOP WON'T STOP✨
+We are a rapidly growing global e-commerce platform specializing in sneakers and apparel. Our engineering team is committed to building cutting-edge technologies that continuously transform how customers discover, shop, and engage with our platform.
+We are looking for a Data Engineer with 3+ years of experience building and optimizing data infrastructure. This role will focus on BigQuery warehouse optimization, event tracking quality, and scalable data pipeline design.
+✨Key Responsibilities
+Data Warehouse Optimization
+• Optimize and refactor BigQuery data models for performance and cost efficiency
+• Improve table structure, partitioning, clustering, and query performance
+• Maintain and enhance ELT pipelines
+• Enforce data quality checks and documentation standards
+Event Tracking Quality
+• Audit and redesign Mixpanel and GA4 tracking architecture
+• Validate GTM, SDK, and server-side event implementation (QA Process)
+• Standardize event naming and tracking schema
+• Identify and close tracking gaps
+Data Pipeline &amp; Integration
+• Build and maintain scalable data pipelines into BigQuery
+• Handle structured and semi-structured data
+• Support cross-domain data integration
+BAU &amp; Collaboration
+• Support BI team on optimization-related data requests
+• Troubleshoot discrepancies across warehouse and tracking tools
+• Document data lineage and ownership
+✨Requirements
+Experience
+• Minimum 3 years of experience as Data Engineer or similar role
+• Strong hands-on experience with cloud warehouse.
+• Experience with event tracking architecture and debugging (QA)
+Technical Skills
+• SQL/Programming Proficiency
+• Workflow Orchestration (e.g Apache/Airflow/Dagster, etc)
+• Experience with ETL or ELT pipeline design
+• Familiar with event-based tracking models
+• Understanding of data modeling and warehouse best practices
+Nice to Have
+• Experience with the modern data stack (e.g., dbt, Airbyte, Datahub)
+• Familiarity with Docker and Kubernetes
+• Experience integrating and managing Mixpanel and GA4 data
+</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90m7j</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>雲端數據工程師</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>君綺生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>美容／美體業</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>台北市信義區 松智路1號</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>部門介紹:
+我們是集團組織擴編成立的新部門, 在這工作你將會體驗全雲的工作環境, 包含AWS雲端服務及工具, 在工作中學習專案管理、資料庫管理、雲端服務等技術
+工作內容
+1. 參與雲端數據架構發展規劃，設計資料處理、儲存、分析架構，以符合數據</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mcsu</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>20260522</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>宇清數位智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>新竹市 東區金山七街1號6樓</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>家協作，快速理解各產業生產資料的脈絡，精準完成資料整合需求。
+4. 資料流維運：負責產品端資料處理流程、ETL 架構開發、資料品質監控與異常告警機制。
+5. 跨團隊協作：與演算法工程師、專案經理密切合作，依排程模型需求整合資料格式，確保資料與排程模</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/76kp9</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>BI 數據工程師  (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>神來也麻將_慧邦科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>台北市中正區 羅斯福路二段100號10樓</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>1. 建置與維運遊戲數據 ETL / ELT 排程。
+2. 與分析、PM、營運合作，提供即時數據查找並建置固定排程或後台功能。
+3. 進行資料品質檢查、異常偵測與基礎探索分析。
+4. 開發與維護數據後台、API 與資料平台相關功能。
+【專業條</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/6u7bu</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>CRM數據工程師</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>忠泰建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>台北市大安區 市民大道三段178號8樓</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>專科</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>1.	集團數據中台建設與管理：
+-	設計並執行跨系統資料管道（ETL），將多公司數據清洗、標準化後匯入集團 CRM，優化整體資訊流。
+-	制定集團數據標準規範，負責資料庫（SQL/NoSQL）效能優化與生命週期管理。
+-	主導資料去識別化與資安合</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91241</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>20260514</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>資料工程師 Junior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>亞太智能機器股份有限公司</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路266號2樓</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>轉換、全半形正規化等 NLP 前處理，兼顧工程健壯性與處理效率。
+二、 LLM 資料整備與優化
+● 文本切塊 (Chunking)：針對長文本設計合理的切分策略，優化檢索效率與語意完整性，並能考慮到不同應用場景的需求。
+● 資料去重 (</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vkrx</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>【新擴編】Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>愛酷智能科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化南路一段2號5樓</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>步汰換舊有的 Digdag 流程。
+2. ETL/ELT 流程開發： 串接 PostgreSQL 與 MongoDB 以及外部資料 等多源數據，清洗並導入 BigQuery。
+3. 數據倉儲模型設計： 使用 dbt 開發與維護數據模型，優化 SQL</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wccg</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>資深資料科學工程師 Sr. Data R&amp;D Engineer (Backend) - 台中 數據技術發展 (數數發中心, DDT)_I00020704</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>台中市烏日區 台中市烏日區高鐵一路299號</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>[工作內容]
+資深後端工程師職務可能包含但不限如下相關內容：
+- 開發與維護現有應用服務
+- 與前端人員合作設計 API 接口
+- 熟悉資料與 AI 模型應用服務開發，與資料科學家合作解決商業命題
+- 具有 Open Source 研究與使用經驗</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n5io</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SWRD_Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Position Impact：
+資料工程師的核心價值在於設計、建置並維護整體的數據解決方案，確保全公司的數據具備高可用性、可靠性及可擴充性。在此職位中，您將處理大規模數據庫，主動識別潛在風險，並開發能提升數據效能與品質的解決方案。您將與後端工程師</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ti6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>侍達遊戲藝術有限公司</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>台北市信義區 東興路41號5樓</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>1. 根據分析需求進行資料建模，並提供視覺化的資料呈現。
+2. 提供分析數據及報表。
+3. 設計與開發資料分析所需要的工具。
+[能力需求]
+1. 具備程式開發經驗 (Python/Golang等)。
+2. 具備 SQL/NoSQL 使用經驗</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85yiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>永慶房產集團_永慶房屋仲介股份有限公司</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段77號12樓</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>永慶房產集團為房仲產業龍頭，用科技創新引領創新變革，歡迎IT領域的優秀夥伴加入!
+工作內容如下：
+1.規劃集團資料流程，達成資料整合綜效。
+2.建置企業數據中台，管控集團資料倉儲品質與正確性。
+3.與資料分析師協同合作，進行資料分析前處理，提供</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78pf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>徵  數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>臺北醫學大學</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用之</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xi1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>資料工程師 (資料治理/ETL)</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>1. 使用 ETL工具開發或是資料庫/資料表系統相關之程式設計及開發
+2. 依規格設計開發包含 SQL Script 以及 Store Procedure 等對資料進行處理的程式，並進行UT測試，撰寫驗證報告
+3. 資料管理與處理相關專案之需求訪</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/81zdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>資料科學工程師 (Data Engineer) -- 資料科學實驗室 (數數發中心,DDT)_I00018190</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[工作內容]
+職務包含但不限於以下內容
+- 基於 Python 語言之產品開發，推廣及後續維護
+- Docker/Kubernetes 相關技術應用研發
+- 雲端技術應用及研究
+- 創新資料科學工程架構研究及開發
+- 大數據專案開發實作
+</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8hztb</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市萬華區 </t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>【職務需求】
+1. 以 Data Engineering 為主，包含 hands-on data pipeline、ETL、data modeling、以及上游系統整合經驗。
+2. 需具備資料整合、資料品質與資料模型設計能力。
+3. 熟悉</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>HUA AO_香港商創金科技有限公司</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大同區 </t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>/CD、Docker 等基礎 DevOps 工具者佳
+3. 參與團隊數據治理與標準制定經驗者尤佳
+【任職資格】
+a. 資訊工程、資料科學、統計、資訊管理等相關理工科系本科以上學歷4年以上
+b. 具備資料工程、BI或數據相關工作經驗 
+c. 樂於</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pr4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>資料工程師 (BI)</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>(本職務主要為技術工作而非單純的數據分析)
+1.  商業智慧(BI)專案需求訪談、系統分析並製作系統需求規格書文件
+2.  撰寫整合測試計畫書、測試案例、準備測試資料及測試
+3.  Metadata 中介層設計、Dashboard、Report設</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/37tef</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>工地主任</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>寶順興開發實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台中市沙鹿區 </t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>月薪 70,000元以上</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.現場工作計畫執行與安排。
+2.施工圖數量，檢討與施工品質管已與監督。
+3.現場進料點收存放，確認。
+4.廠商請款數量核算與計價。
+5.施工日報表確實填寫。
+6.現場施作安全，衛生管理。
+</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yuee</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Junior IT Support Engineer (Taiwan)</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>安道創新科技有限公司</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>新北市林口區 仁愛路二段502號8樓</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>We're hiring a hands-on Junior IT Support Engineer who's ready to own tickets end-to-end (not just pass them on). You'll troubleshoot across Microsoft 365 and get exposure to Azure (VMs/servers) as you grow.
+At AccessOrange, we're big on teamwork, proactive support, and learning on the job. If you like solving puzzles, helping people work smarter, and building solid skills in Microsoft cloud, you’ll fit right in.
+What You'll Do
+· L1/L2 IT Support – Troubleshoot and resolve issues across Windows 10/11, Microsoft 365, and core IT services.
+· Microsoft 365 Admin – Support Teams, SharePoint, Exchange, OneDrive, licensing, and security settings.
+· Azure Basics (with support) – Help troubleshoot Azure Virtual Machines and virtual server issues and learn best practices along the way.
+· Security &amp; Compliance – Support secure setups like MFA, device policies, and compliance configurations.
+· User Support for Collaboration Tools – Keep users productive by fixing issues in Teams, Outlook, and SharePoint.
+· Hardware &amp; Software Troubleshooting – Diagnose issues with Windows devices, printers, basic networking, and business apps.
+· Own It – Take ownership until the issue is fixed, escalating only when it truly makes sense.
+· Document &amp; Share Knowledge – Write simple notes/runbooks and share fixes with the team.
+· Keep Learning (Certs included) – You'll be expected to grow. Working toward MS-102, AZ-104, or similar Microsoft certs is required (we'll support you).
+You'll Be a Great Fit If You're…
+· A team player – You collaborate well and believe great support is a team sport.
+· A problem-solver – You investigate, test, and learn (not just forward tickets).
+· Self-motivated – You’re curious, you ask good questions, and you want to level up in Microsoft 365 + Azure.
+Minimum Requirements
+· Core IT skills – Windows 10/11, Microsoft 365 basics, and solid troubleshooting fundamentals.
+· Experience – 1 years in IT support (L1/L2), helpdesk, or junior system administration.
+· Languages – Fluent English + Mandarin (spoken and written). Cantonese is a plus.
+· Cert mindset – Microsoft certs (MS-102, AZ-104, or similar) are a strong plus. If you don't have them yet, you must be willing to obtain them.
+· Taiwan ARC Holder – We cannot provide working VISA
+What You'll Get
+· Hands-on work – Real tickets, real environments, real learning (not just scripted responses).
+· Certification support – We’ll support you working toward Microsoft 365 and Azure certifications.
+· Regional exposure – Support customers across Asia and learn how different orgs run their IT.
+· Work-life basics – 5-day workweek, annual leave package, and clear growth opportunities.
+Work Location
+· Taiwan Office: Linkou, New Taipei City
+· Core hours: 09:00–18:00 (incl. lunch)
+· Working arrangement: Hybrid; Mondays in-office, otherwise remote. Customer onsite support as needed, transportation fee will be provided.
+工作內容
+· 一線/二線 IT 支援（L1/L2）－協助排除並解決 Windows 10/11、Microsoft 365 與核心 IT 服務相關問題。
+· Microsoft 365 管理－支援 Teams、SharePoint、Exchange、OneDrive、授權與安全性設定。
+· Azure 基礎（有資深同仁支援）－協助排除 Azure 虛擬機與虛擬伺服器相關問題，並在過程中學習最佳實務。
+· 資安與合規－協助導入與支援 MFA、裝置政策與合規設定等安全配置。
+· 解決協作工具問題－處理 Teams、Outlook、SharePoint 等問題，確保使用者維持高效率。
+· 硬體與軟體問題排除－診斷 Windows 裝置、印表機、基礎網路與商務應用程式問題。
+· 全程負責問題處理直到解決－直到問題解決前都持續追蹤與處理，僅在必要時才進行升級通報。
+· 文件整理與知識分享－撰寫簡易筆記/Runbook，並與團隊分享處理方式與解法。
+· 持續學習（含證照支持）－期待你持續成長；需以取得 MS-102、AZ-104 或同等 Microsoft 證照為目標（公司會提供考題資源與證照費用）。
+如果你符合以下特質，你會很適合…
+· 團隊合作－善於協作，並相信好的支援來自團隊共同努力。
+· 問題解決能力－願意查證、測試與學習（而不是只把工單轉出去）。
+· 主動積極－保持好奇心、會問好問題，並希望在 Microsoft 365 + Azure 持續進步。
+基本條件
+· 核心 IT 能力－熟悉 Windows 10/11、Microsoft 365 基礎，並具備良好的問題排除能力。
+· 工作經驗－具 1 年以上 IT 支援（L1/L2）、Helpdesk 或初階系統管理相關經驗。
+· 語言能力－英文與中文聽說讀寫流利；會粵語者加分。
+· 證照意願－具 Microsoft 證照（MS-102、AZ-104 或同等）者加分；若尚未取得，需願意在到職後規劃並取得。（公司會提供考題資源與證照費用）。
+· 持有台灣身分或是ARC居留證 － 公司無提供工作簽證
+工作地點
+· 台灣辦公室：新北市林口
+· 上班時間：09:00–18:00（含午休）
+· 工作安排：可混合辦公；每週一固定進辦公室，其餘可遠端。視需求需至客戶現場提供支援(額外補貼交通費)。</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/81mcj</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>20260125</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1.在Hadoop架構的資料倉儲(Data Warehouse)上建立具備擴充性與高可靠性的資料產品，為數據科學家與業務團隊提供穩健的資料基礎。
+2.與數據科學家和業務分析團隊合作，理解需求並提供適用的資料解決方案。
+3.設計並構建</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n58n</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>20260424</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>量化投資金融大數據工程師</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>沛然資訊有限公司</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街150號7樓</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>年薪 800,000 ~ 1,500,000元</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>控與跨市場操作等關鍵場景中。我們開發可用於決策的高互動行動應用，誠摯邀請對產品品質與金融邏輯有熱情的夥伴加入我們的團隊。
+【工作內容】
+1. 台清交成資工系學碩士優先。
+2. 優秀IT科技理工且對量化投資有興趣者。
+3. 量化交易相關資料庫的維運</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7mnu3</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>P7-Python資料工程師</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>意藍資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號12樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>月薪 35,000 ~ 45,000元</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>本公司是國內搜尋及語意分析市占率最高的廠商，專注研發非結構資料之數據處理，尋找熟悉Python及物件導向設計的人才加入。工作主要為開發與維運資料產線，搜集語料、資料儲存處理，並提供API服務供下游服務使用。
+工作內容如下：
+- 資料搜集程式開發</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7csnw</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據架構工程師) – (數數發中心, DDT)</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>【關於我們】
+我們是國泰產險的資料科學（DS）團隊，使命在於持續進化數據應用，創造並釋放數據價值。目前正在藉由數據上雲、數據治理與 AI 技術應用，推動由底層架構到業務應用的全端數據生態建構與 AI 轉型準備。
+我們尋找認同以下團隊文化的夥伴：</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8opms</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer【數位數據發展本部】</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>東南旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段60號</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>統性整合資料支撐分析與AI應用的發展
+●	建置優化Data Pipeline，並建立資料品質監控管理機制，確保資料品質和效率
+●	與DA / DS 協作，開發實作數據 / AI產品，參與模型的部署上線與維運
+●	協作工程師設計大規模資料遷移，參與</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tbys</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>20260321</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>【凱基證券/數位創新部】數據工程師</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>凱基金融控股股份有限公司|凱基證券|凱基銀行|中華開發資本|凱基投信</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>台北市中正區 重慶南路一段</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>1. 資料倉儲等系統或機器學習建模之資料收集、開發處理與管理維護
+2. 業務單位數據需求開發</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/89pxp</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>20260510</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>【台中】資料工程師</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>敦謙國際智能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>台中市西區 國泰金融大樓(台中市西區英才路 530 號) 24 樓</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 90,000元</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>職務工作內容：
+營運策略系統 (RMS)
+透過資料分析、資料探勘和數據處理技術，為旅宿提供精準的營運決策依據。
+建模預測，根據歷史銷售資料，建立銷售量、住宿率等預測模型，為旅宿決策的制定提供參考。
+協助開發專為旅宿設計的智能客服機器人。
+職務需</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/75oc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>職務目的：參與銀行級大型資料倉儲與雲端轉型專案。
+工作內容：
+1.維運數據倉儲 ODS 資料庫：
+•規劃與管理資料庫空間與使用者權限。
+•監控系統運作狀況，進行問題排查與修復。
+•確保資料庫效能與穩定性。
+2.資料導入流程管理：
+•設計與實作</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7p5ll</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>資料科學工程師 （Data Science R&amp;D）雲原生平台產品開發 - 資料科學研發 (數數發中心, DDT)_I00015788</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>隸屬於國泰金控下的資料科學實驗室 Cathay Data Lab Team，實驗室的使命是研究先端的資料科學與人工智慧技術，落地在國泰場景提升資料應用價值。 身為一名資料科學家與研究者，你必須適應 Cathay Data Lab Team 以下文</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/87vo6</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>20260407</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>資料工程師-情報系統二team【全家便利商店關係企業】</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>精藤股份有限公司</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段61號11樓</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>護），更有完善的公司治理與開發標準，可做為所有資訊人員執行專案時的後盾。
+除此之外，精藤近年來亦不斷追求更多新領域的發展，例如：雲端科技應用、大數據資料分析以及行動裝置管理技術等等，誠摯的歡迎所有對於零售流通有興趣的伙伴一同加入精藤的大家庭。</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/84xyg</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>製程資料工程師</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>聯亞光電工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>台南市善化區 西善一路9號</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>1、了解產線流程，協助將製程與生產資料系統化
+2、規劃並建置製造相關資料庫，確保資料可追溯、可查詢
+3、開發或維護內部系統，降低人工紀錄與 Excel 作業
+4、建立基本報表與視覺化畫面，呈現產線狀態與歷史趨勢
+5、與製程、工程、設備單位合作，支</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x7cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>聯想感行銷科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>台北市松山區 民生東路三段135號3樓</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>月薪 1,100,000元以上</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>獨立掌握與釐清客戶資料處理需求、定義資料流規格、定義資料模型，確認運行規格。
+需面對企業客戶並給予資料流與資料 schema 上的回應。
+【專案管理能力】
+熟悉資料流開發、資料流驗証等流程。
+熟悉編寫資料流規格書。
+評估議定工作時程表（WBS</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8t673</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>20260522</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>〔資訊〕數據工程師</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>台新新光金控_台新國際商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>台北市內湖區 舊宗路二段207號</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>工作內容：
+1.資料數據進行ETL開發、測試與維護ETL資料轉換工作
+2.具備 T-SQL 語法及Stored Procedure開發經驗
+3.分析系統之開發(含批次、介面及報表)
+4. Hadoop Eco System(Spark、Hive、</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8s444</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>數據工程師 | 數據中台【股感媒體科技】</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>股感媒體科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>台北市松山區 民生東路三段135號3樓</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+	• 負責設計、開發與維運公司級 數據中台（Data Platform）。
+	• 建立可治理、可擴展、可對外服務的資料基礎設施。
+	• 支援多品牌、多業務（金融 / 保險 / 行銷 / 內容 / MA / DM）的數據應用，同時也會跨足不同生態圈產業</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xfuh</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據應用工程師) – (數數發中心, DDT)_I00020717</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+* 目標成果導向：重視成果並具合作互助精神
+* 積極主動、持續進步：樂於學習與自我成長
+* 熱愛數據、對技術充滿熱忱：積極探索與應用新技術
+【工作內容】
+資料工程的世界千變萬化，以下是你的任務指南：
+1. 數據蒐集與處理，接觸各種資料來源，進行</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n8v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>資訊處-資料工程師</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>永豐商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中山區 </t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自我學習研究能力，且對資料技術具備敏感度
+具良好的溝通與協作能力，樂於與團隊分享想法與知識，推動團隊成長。
+</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/909yb</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>【台北】資料庫工程師(MS SQL)</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>宏益科技服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Azure SQL Database管理經驗者尤佳。
+工作類型：
+- 開發專案包括銀行、人壽、產險、證券、公部門、電商、電信等產業。
+- 依個人能力、生涯規劃擔任系統分析師(SA)、系統設計師(SD)以及軟體工程師(PG)等角色
+- 依個人意願配</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ywmf</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>20260506</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>【台北】數據工程師Data Engineer — "Data Infrastructure Architect"</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>創智動能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>台北市中正區 八德路1段23號9樓</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>至數據倉儲或資料湖。 
+   確保數據準確性與一致性，並優化數據處理效能。
+Data Transformation and Integration
+Design and implement data transformation processes</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8kgsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>軟體產品工程師</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>永聚資科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>新北市板橋區 四川路2段16巷10號1樓</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+‧ 寫過 RESTful API、處理過實際業務邏輯
+‧ 看過、用過、改過別人的程式碼（不是只會寫新東西）
+‧ 重視程式碼品質：會寫測試、會 review、會重構
+‧ 對「打造產品」有熱情，不只想當外包工程師
+公司會提供的支援】
+‧ 每月 1,</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qb3t</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ETL 資料工程師/大數據工程師</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>歐立威科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>台北市大同區 鄭州路87號11樓之1</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Pentaho PDI、Talend、Informatica、Microsoft SSIS 等）進行數據抽取、轉換與載入，確保資料正確性與完整性。
+3.熟悉 Python 或 Java 等程式語言，能撰寫 ETL 腳本與自動化流程。
+4.設計並維護 Data</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ugrj</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>北部 環境工程師</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>偉創綠技術股份有限公司</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>環境衛生及污染防治服務業</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>新北市汐止區 新台五路99號28樓之11 室(iFG遠雄廣場 A棟)</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>月薪 43,000元以上</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>1.執行水質監測相關儀器操作、保養、校正與表單紀錄
+2.現場重點檢查、儀器損壞紀錄
+3.例行性報告作業與交辦事項
+4.庶務性一般文書資料及歸檔
+5.作業謹慎
+6.有環化相關教育養成背景或相近職場經驗者為佳</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/86il0</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>電機設計工程師 (20260115BD800001)</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>中鼎集團_中鼎工程股份有限公司</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>建築及工程技術服務業</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>台北市士林區 中山北路六段89號</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>國內外大型知名工程的電⼒系統設計、動⼒與接地系統設計、照明系統設
+計、弱電與消防系統設計、陰極防蝕和電熱保溫設計、建造與試⾞。</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Digital Twin工程師、資料工程師、後端工程師_14874</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>和碩集團_和碩聯合科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>電腦及其週邊設備製造業</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>台北市北投區 立功街76號</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>碩士</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 模型、data engineering和simulation environment集成到企業工作流程中。
+4.與產品經理、資料科學家和工程師合作，將業務需求轉化為技術解決方案。
+5.確保數位孿生系統應用程序的高性能、可擴展性和安全性，滿足企業級需</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vzq3</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>【外商】[RC-Data] (Sr.) Data Engineer-Streaming／數據工程師-Streaming</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路捷運中山站六號出口共構大樓</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>資料與 AI 相關領域人才
+【關於該職位】 
+我們正在尋找一位 Streaming Data Engineer（即時資料工程師），負責設計並建置可擴展的即時資料處理管線（Real-time Data Pipelines）與串流資料平台。
+此職位將</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wpc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>允和科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>高雄市前鎮區 建基街9號5樓</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>月薪 35,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1、自動化數據採集：設計與維護高效能 ETL 爬蟲程式，定期抓取氣象署 (CWA)、環境部等國內外開放資料 (Open Data) 及傳感器數據。
+2、依據專案需求，進行系統功能開發、優化與維護。
+3、與產品經理、專案經理協作，理解</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yb0h</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>【外商】[FIN] Sr. Data Engineer／資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號20樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>年薪 1,200,000 ~ 1,400,000元</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>實務開發經驗。
+4. 具備 Data Pipeline (資料流) 的設計、搭建與優化能力，熟悉 Dagster 或 Airflow 等排程工具。
+5. 5 年以上資深資料工程師或相關經驗，並具備獨立主導專案的能力。
+6. 卓越的需求訪談與業務邏輯</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dq30</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>【凱基證券/數位創新部】數據工程師</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>凱基證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>台北市中正區 重慶南路一段</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>1. 資料倉儲等系統或機器學習建模之資料收集、開發處理與管理維護
+2. 業務單位數據需求開發</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7jogm</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>澧曜數據有限公司</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>台中市西區 忠明南路497號2樓</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 開發/維護/設計處理數據架構與服務以及部署服務。
+2. 負責ETL（數據提取、轉換、加載）流程設計，包括數據清洗、預處理及自訂程式開發。
+3. 擁有CI/CD經驗，熟悉Jenkins、GitLab、Airflow等CI/CD工具和流程。
+</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dclx</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>果實夥伴股份有限公司</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路610號2樓</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>【工作內容 】
+-  ETL 之開發、處理(資料清理、儲存、分析)與監測
+- 開發與設計專案所需 API 服務並與後端工程師合作，完成系統產品化程序
+- 依據不同業務需求，完成建置/維運/更新各式 Data infra 的需求
+- 與數據產品管理</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7dpwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>20260512</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>GIS資料工程師</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>九福科技顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>台北市大同區 重慶北路二段48號2</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>1.具有主動積極負責精神，擁有團隊工作意識亦能獨立作業，學習能力強，善溝通
+2.具備熟悉ArcGIS、影像分析及資料分析處理
+3.工作內容：檢核、搜集、彙整、分析比對資料，GIS圖資處理及製程文件彙整，品管檢核，進行資料收集、彙整及交辦工作事項</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78nq1</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>網頁系統工程師</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>捷斯克科技有限公司</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>台中市西區 台灣大道二段181號12樓之3</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>月薪 36,000元以上</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>1.Laravel 後端工程師，加入我們的核心團隊負責 CRM SCM 等系統的開發與功能擴展。
+2.此職位專注於商業邏輯的實作、資料庫架構設計（SQL）與 API 串接。
+3.我們需要習慣使用 AI 工具（如 ChatGPT Claude）來輔</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8o1xt</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>臺北市立萬芳醫院-委託臺北醫學大學辦理</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>醫院</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>月薪 43,700 ~ 45,900元</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。 
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8z3ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>20260505</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>資訊處_數據工程師</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>美而快國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>鞋類／布類／服飾品零售業</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>台北市南港區 重陽路203巷29號</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Analytics 4（GA4）
+Matomo
+數據處理與資料工程
+Databricks、Azure Blob Storage
+parquet 資料格式處理
+Dagster、Talend
+資料庫與後端處理
+Microsoft SQL</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90ruo</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>20260311</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>【資訊板塊】金融數據工程師(企業資料倉儲整合｜核心系統現代化｜數據架構轉型)_I00024956</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>國泰世華商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>打造金融數據新未來，從你開始！
+你相信數據不只是冰冷的數字，而是能驅動決策、創造價值的力量嗎？
+在這裡，你不只是寫程式，而是參與一場金融數據革命！
+加入我們，打造穩定、高效、可擴展的資料平台，讓每一筆數據都能說故事，讓你的技術真正改變企業未來。</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8whwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>立視科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>多媒體傳播相關業</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>台北市松山區 八德路四段760號6樓</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位熱情且富有才華的資料工程師，加入我們的團隊，協助解決廣告投遞的資料內容。在這裡有大量的數據供你發揮所長，將學過的知識及方法應用到實務的工作上。
+我們希望你具備以下三大特質：
+對資料工程領域有強烈興趣和熱情 。
+重視團隊合作，具備</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zz6u</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>資料工程師 || 資料倉儲 × ETL流程建置</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>三陽工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>汽車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>新竹縣湖口鄉 中華路3號</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>月薪 38,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>將參與公司資料平台與資料倉儲建置，
+從資料蒐集、整合到ETL流程設計，
+逐步建立穩定且可持續運作的資料流架構。
+透過內外部資料匯集與整理，
+包含 API、Excel、爬蟲及非結構化資料處理，
+讓分散資訊能有效串接、清理與整合，提升資料可用性與品</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91fva</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>數據工程師｜打造零售界的神級Data Build</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>統一資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路155號8F~10F</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>你是資料界的打怪高手嗎？
+我們正在尋找一位能將數據煉金的工程師，一起升級零售產業的數據系統，從地端到雲端，穩定輸出、精準命中！
+這份工作不只是 coding，更是策略規劃、技術架構與商業價值的 combo 技。
+如果你喜歡優化效能、挑戰架構、解任</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4bma8</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>資深資料工程師｜Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>街口電子支付股份有限公司</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號8樓(C棟)</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>◆THE ROLE &amp; THE TEAM 
+As a Data Engineer in JKOPay, you will be responsible for processing JKOPay’s online transaction data and offline data analysis with your experience in data engineering. JKOPay serves +6 million users in Taiwan, as well as partners and stakeholders that integrate with our payment service, which handles 3-billion transaction amounts every month. 
+With the rapid growth of JKOPay’s business, Data Engineer is the key to designing systems for collecting, storing, and analyzing data at scale, as well as convert raw data into usable information for business analysis to interpret. 
+This is an opportunity to help shape and expand JKOPay’s ETL data pipeline. If you are interested in handling multiple-terabyte data and improving engineering efficiency, in a great team that keeps growing, this role is for you. 
+◆WHY YOU SHOULD BE INTERESTED 
+-Translate business requirements &amp; end to end designs into technical implementations and responsible for building batch data warehouse. 
+-Manage data modeling design, writing, and optimizing ETL jobs. 
+-Collaborate with the business team to build data metrics and data visualization based on data warehouse. 
+-Responsible for building and maintaining data products. 
+-Involvement in rollouts, upgrades, implementation, and release of data system changes as required for streamlining of internal practices. 
+◆WE'D LOVE TO MEET YOU IF 
+-At least 2 years of relevant experience in data engineering. 
+-Proficient in creating and maintaining complex ETL pipeline end-toend while maintaining high reliability and security.
+-Familiar with backend engineering and practical knowledge of shell, SQL, and one more programming language (e.g. Python, Scala, etc.). 
+-Familiar with the common distributed computing engine or platform (e.g. ClickHouse, Spark, Kafka, BigQuery, Airflow, etc). 
+-Familiar with at least 1 data exploration and visualization platform (e.g. Superset, Tableau). 
+-Familiar with data lake, data warehouse, and data mart concept, and have production experience in modeling design. 
+-Familiar with at least 1 Cloud data flow solution (e.g. AWS Data Pipelines, GCP Dataflow, etc.) is a plus. 
+-Experience with Data Catalog is a plus. 
+-Excellent interpersonal and communication skills with the ability to engage and managing internal and external stakeholders across all levels of seniority.</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7jw2n</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>可樂旅遊旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段90號12樓</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>資料運用並創造商業價值，並積極探索 AI 技術，提升整體營運效率與決策品質。
+【工作內容】
+1. 設計、開發與維護數據流程，打造穩定且高效的數據基礎架構
+2. 使用 Python 進行數據清理、轉換與處理
+3. 將數據處理流程自動化，並協助部署至雲</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/853np</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Senior AI Agent Engineer 資深 AI Agent 工程師</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>奧藝數位行銷有限公司</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路192號5樓之1</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>年薪 2,000,000 ~ 2,000,000元</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 協作創新，解鎖更多 AI 應用可能
+-串接前沿 AI 研究與實際產品落地之間的橋樑
+-協助企業自動化工作流程、進行智慧資料分析並提升營運效率
+-參與打造下一世代 AI 驅動的企業應用與解決方案
+資格條件（Qualifications）
+-資訊工程</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91sva</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>A6000 廣告平台資料工程師</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>富邦媒體科技股份有限公司(富邦momo)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>並協助開發滿足廣告業務發展相關的需求
+2.優化系統 Data Pipeline 處理海量用戶與廣告事件，提供即時且高效率的 OLAP 系統
+3.與演算法工程師與資料分析師協作開發廣告引擎模型與競價引擎
+4.關聯式與非關聯式資料庫的 DB</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dbr3</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>20260427</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Integration Engineer 系統整合工程師</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>荷蘭商范德蘭德工業有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>儲配／運輸物流業</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段129號5樓</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>援客戶的營運流程。
+作為一名 整合工程師（Integration Engineer），你將參與將各種元件與（子）系統整合為完整解決方案的工作。這在大型且複雜的機場與包裹處理系統中尤其具有挑戰性，這些系統包含單件輸送系統、自動倉儲系統（ASRS）、自</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90xoc</t>
         </is>
       </c>
     </row>

--- a/z_RequestData/jobsearch_data104.xlsx
+++ b/z_RequestData/jobsearch_data104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J331"/>
+  <dimension ref="A1:J441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12306,10 +12306,8 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>20260522</t>
-        </is>
+      <c r="A222" t="n">
+        <v>20260522</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -12364,10 +12362,8 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>20260517</t>
-        </is>
+      <c r="A223" t="n">
+        <v>20260517</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -12420,10 +12416,8 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>20260427</t>
-        </is>
+      <c r="A224" t="n">
+        <v>20260427</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -12472,10 +12466,8 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>20260514</t>
-        </is>
+      <c r="A225" t="n">
+        <v>20260514</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -12526,10 +12518,8 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A226" t="n">
+        <v>20260521</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -12616,10 +12606,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A227" t="n">
+        <v>20260518</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -12671,10 +12659,8 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A228" t="n">
+        <v>20260520</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -12726,10 +12712,8 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>20260522</t>
-        </is>
+      <c r="A229" t="n">
+        <v>20260522</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -12799,10 +12783,8 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A230" t="n">
+        <v>20260519</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -12854,10 +12836,8 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A231" t="n">
+        <v>20260518</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -12909,10 +12889,8 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>20260517</t>
-        </is>
+      <c r="A232" t="n">
+        <v>20260517</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -12964,10 +12942,8 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A233" t="n">
+        <v>20260515</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -13021,10 +12997,8 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A234" t="n">
+        <v>20260520</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -13073,10 +13047,8 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A235" t="n">
+        <v>20260519</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -13128,10 +13100,8 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A236" t="n">
+        <v>20260519</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -13182,10 +13152,8 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A237" t="n">
+        <v>20260518</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -13237,10 +13205,8 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A238" t="n">
+        <v>20260519</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -13294,10 +13260,8 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A239" t="n">
+        <v>20260518</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -13349,10 +13313,8 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>20260413</t>
-        </is>
+      <c r="A240" t="n">
+        <v>20260413</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -13403,10 +13365,8 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A241" t="n">
+        <v>20260519</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -13458,10 +13418,8 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>20260423</t>
-        </is>
+      <c r="A242" t="n">
+        <v>20260423</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -13513,10 +13471,8 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A243" t="n">
+        <v>20260520</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -13568,10 +13524,8 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A244" t="n">
+        <v>20260515</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -13624,10 +13578,8 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A245" t="n">
+        <v>20260520</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -13682,10 +13634,8 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A246" t="n">
+        <v>20260520</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -13739,10 +13689,8 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>20260508</t>
-        </is>
+      <c r="A247" t="n">
+        <v>20260508</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -13795,10 +13743,8 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A248" t="n">
+        <v>20260519</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -13852,10 +13798,8 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A249" t="n">
+        <v>20260520</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -13909,10 +13853,8 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>20260514</t>
-        </is>
+      <c r="A250" t="n">
+        <v>20260514</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -13963,10 +13905,8 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A251" t="n">
+        <v>20260521</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -14016,10 +13956,8 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A252" t="n">
+        <v>20260515</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -14071,10 +14009,8 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>20260510</t>
-        </is>
+      <c r="A253" t="n">
+        <v>20260510</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -14125,10 +14061,8 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A254" t="n">
+        <v>20260520</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -14178,10 +14112,8 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A255" t="n">
+        <v>20260520</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -14233,10 +14165,8 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A256" t="n">
+        <v>20260518</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -14289,10 +14219,8 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A257" t="n">
+        <v>20260518</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -14343,10 +14271,8 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>20260511</t>
-        </is>
+      <c r="A258" t="n">
+        <v>20260511</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -14400,10 +14326,8 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A259" t="n">
+        <v>20260520</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -14454,10 +14378,8 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A260" t="n">
+        <v>20260520</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -14507,10 +14429,8 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A261" t="n">
+        <v>20260521</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -14561,10 +14481,8 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A262" t="n">
+        <v>20260521</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -14616,10 +14534,8 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A263" t="n">
+        <v>20260521</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -14669,10 +14585,8 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A264" t="n">
+        <v>20260521</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -14725,10 +14639,8 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A265" t="n">
+        <v>20260515</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -14778,10 +14690,8 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A266" t="n">
+        <v>20260515</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -14846,10 +14756,8 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A267" t="n">
+        <v>20260521</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -14938,10 +14846,8 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>20260409</t>
-        </is>
+      <c r="A268" t="n">
+        <v>20260409</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -14994,10 +14900,8 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>20260512</t>
-        </is>
+      <c r="A269" t="n">
+        <v>20260512</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -15048,10 +14952,8 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A270" t="n">
+        <v>20260518</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -15102,10 +15004,8 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>20260511</t>
-        </is>
+      <c r="A271" t="n">
+        <v>20260511</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -15191,10 +15091,8 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A272" t="n">
+        <v>20260515</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -15246,10 +15144,8 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>20260522</t>
-        </is>
+      <c r="A273" t="n">
+        <v>20260522</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -15300,10 +15196,8 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A274" t="n">
+        <v>20260519</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -15356,10 +15250,8 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A275" t="n">
+        <v>20260520</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -15411,10 +15303,8 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>20260514</t>
-        </is>
+      <c r="A276" t="n">
+        <v>20260514</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -15466,10 +15356,8 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A277" t="n">
+        <v>20260515</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -15520,10 +15408,8 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A278" t="n">
+        <v>20260519</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -15577,10 +15463,8 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A279" t="n">
+        <v>20260521</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -15630,10 +15514,8 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A280" t="n">
+        <v>20260521</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -15687,10 +15569,8 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A281" t="n">
+        <v>20260519</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -15743,10 +15623,8 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A282" t="n">
+        <v>20260520</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -15798,10 +15676,8 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A283" t="n">
+        <v>20260515</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -15852,10 +15728,8 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A284" t="n">
+        <v>20260519</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -15911,10 +15785,8 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A285" t="n">
+        <v>20260519</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -15966,10 +15838,8 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A286" t="n">
+        <v>20260521</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -16023,10 +15893,8 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A287" t="n">
+        <v>20260520</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -16078,10 +15946,8 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A288" t="n">
+        <v>20260521</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -16136,10 +16002,8 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A289" t="n">
+        <v>20260521</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -16242,10 +16106,8 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>20260125</t>
-        </is>
+      <c r="A290" t="n">
+        <v>20260125</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -16297,10 +16159,8 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>20260424</t>
-        </is>
+      <c r="A291" t="n">
+        <v>20260424</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -16353,10 +16213,8 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A292" t="n">
+        <v>20260515</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -16407,10 +16265,8 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A293" t="n">
+        <v>20260518</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -16461,10 +16317,8 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A294" t="n">
+        <v>20260519</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -16516,10 +16370,8 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>20260321</t>
-        </is>
+      <c r="A295" t="n">
+        <v>20260321</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -16569,10 +16421,8 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>20260510</t>
-        </is>
+      <c r="A296" t="n">
+        <v>20260510</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -16626,10 +16476,8 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A297" t="n">
+        <v>20260331</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -16685,10 +16533,8 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A298" t="n">
+        <v>20260519</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -16737,10 +16583,8 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>20260407</t>
-        </is>
+      <c r="A299" t="n">
+        <v>20260407</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -16790,10 +16634,8 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A300" t="n">
+        <v>20260520</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -16846,10 +16688,8 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A301" t="n">
+        <v>20260518</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -16903,10 +16743,8 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>20260522</t>
-        </is>
+      <c r="A302" t="n">
+        <v>20260522</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -16959,10 +16797,8 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A303" t="n">
+        <v>20260519</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -17014,10 +16850,8 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A304" t="n">
+        <v>20260518</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -17072,10 +16906,8 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A305" t="n">
+        <v>20260519</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -17126,10 +16958,8 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A306" t="n">
+        <v>20260520</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -17182,10 +17012,8 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>20260506</t>
-        </is>
+      <c r="A307" t="n">
+        <v>20260506</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -17237,10 +17065,8 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A308" t="n">
+        <v>20260518</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -17295,10 +17121,8 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A309" t="n">
+        <v>20260518</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -17349,10 +17173,8 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A310" t="n">
+        <v>20260519</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -17406,10 +17228,8 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A311" t="n">
+        <v>20260518</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -17459,10 +17279,8 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A312" t="n">
+        <v>20260519</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -17513,10 +17331,8 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A313" t="n">
+        <v>20260519</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -17568,10 +17384,8 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A314" t="n">
+        <v>20260519</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -17623,10 +17437,8 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A315" t="n">
+        <v>20260519</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -17678,10 +17490,8 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A316" t="n">
+        <v>20260521</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -17731,10 +17541,8 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A317" t="n">
+        <v>20260520</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -17786,10 +17594,8 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A318" t="n">
+        <v>20260519</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -17842,10 +17648,8 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>20260512</t>
-        </is>
+      <c r="A319" t="n">
+        <v>20260512</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -17896,10 +17700,8 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A320" t="n">
+        <v>20260519</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -17950,10 +17752,8 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>20260520</t>
-        </is>
+      <c r="A321" t="n">
+        <v>20260520</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -18005,10 +17805,8 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>20260505</t>
-        </is>
+      <c r="A322" t="n">
+        <v>20260505</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -18064,10 +17862,8 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A323" t="n">
+        <v>20260311</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -18119,10 +17915,8 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A324" t="n">
+        <v>20260521</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -18174,10 +17968,8 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A325" t="n">
+        <v>20260518</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -18231,10 +18023,8 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A326" t="n">
+        <v>20260518</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -18286,10 +18076,8 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A327" t="n">
+        <v>20260521</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -18357,10 +18145,8 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A328" t="n">
+        <v>20260519</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -18413,10 +18199,8 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A329" t="n">
+        <v>20260521</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -18470,10 +18254,8 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>20260518</t>
-        </is>
+      <c r="A330" t="n">
+        <v>20260518</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -18525,10 +18307,8 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>20260427</t>
-        </is>
+      <c r="A331" t="n">
+        <v>20260427</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -18574,6 +18354,6170 @@
       <c r="J331" t="inlineStr">
         <is>
           <t>https://www.104.com.tw/job/90xoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>20260527</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>數位發展策略暨平台整合主管</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>香港商天圓文化諮詢顧問有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>台北市中正區 重慶南路一段11-1號2樓</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>決問題
+5. 數位行銷經驗（含B2B經驗佳）
+6. WordPress規劃及使用經驗尤佳
+7. 可面對諮詢與工程端開發溝通，能與IT工程師有效溝通（了解基本前後端概念）
+8.熟悉SEO與內容行銷策略
+9.熟悉Google Analytics,</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ykhh</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>機構工程師</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>泓鈞國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>桃園市蘆竹區 長興里南崁路二段66-6號8樓</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>月薪 45,000元以上</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程技術文件、BOM及相關開發資料。 
+7.	需短期出差
+8.	配合主管交辦事項，協助跨部門溝通與專案執行。 
+</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85z7z</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>資料工程師 / Data Engineer</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>奕界科技有限公司</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>台北市中正區 仁愛路二段99號8樓</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>月薪 65,000元以上</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>We are an iGaming software company building live casino and slot games, integrated with third-party operators. We process high volumes of transactions and are scaling our data platform to power financial reporting, regulatory needs, and business intelligence. We're looking for a Data Engineer to help design, build, and own our end-to-end ETL pipeline — from transactional databases through to our data warehouse and analytics layer.
+===What You'll Do===
+* Design and maintain ETL/ELT pipelines moving transactional data from PostgreSQL (AWS Aurora) into Redshift via zero-ETL, and onward into our lakehouse layer.
+* Build and operate our Apache Iceberg + Parquet on S3 data warehousing layer, including table design, partitioning, compaction, and schema evolution.
+* Develop and orchestrate data workflows in Apache Airflow to generate financial reports and feed downstream dashboards.
+* Model data to support backoffice financial reporting (bets, settlements, wallet movements, operator reconciliation) with accuracy and auditability.
+* Partner with BI stakeholders to deliver clean, reliable datasets in Tableau for metrics such as retention, player activity, and revenue.
+* Write and maintain Python-based automation for ingestion, transformation, data quality checks, and monitoring.
+* Ensure data integrity, reconciliation, and lineage across the pipeline, with attention to the financial and compliance sensitivities of iGaming.
+* Optimize for performance, cost, and reliability across AWS infrastructure.
+===What We're Looking For===
+* Strong SQL and hands-on experience with data warehousing (Redshift or comparable MPP/columnar systems).
+* Production experience building and orchestrating pipelines with Apache Airflow.
+* Proficiency in Python for data engineering and automation.
+* Experience with the AWS data stack (Aurora/PostgreSQL, Redshift, S3, IAM).
+* Solid understanding of data modeling (dimensional modeling, slowly changing dimensions, reconciliation patterns).
+* Familiarity with table formats / lakehouse concepts (Apache Iceberg, Parquet) — or strong appetite to learn.
+* Comfort working with BI tools (Tableau or similar) and collaborating with analysts.
+===Nice to Have===
+* Experience in iGaming, fintech, payments, or other high-volume transactional/financial domains.
+* Exposure to zero-ETL or CDC-based replication.
+* Familiarity with NodeJS-based services (our application servers are built in Node).
+* Understanding of regulatory/compliance and audit requirements in regulated industries.
+* Experience with cost optimization on AWS and data observability/quality frameworks.
+===Why Join Us===
+* Own a greenfield lakehouse migration (Iceberg/Parquet) from the ground up.
+* Work on data that directly drives financial decisions and product strategy.
+* Modern AWS-based stack with room to shape architecture and tooling.</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/928hw</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>美商電腦 - 資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>TechTalent_天合科技顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市南港區 </t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>具備資料平台建置與資料整合經驗的資料工程師，負責開發及維護企業資料平台、資料管線與雲端資料架構，支援數據分析、營運系統及 AI 應用發展。
+您將與軟體開發、資料分析及產品團隊合作，打造穩定且高效的資料基礎設施。
+工作職責
+● 建置、維護及優化</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/929qr</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer / 資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Zerologix_零輯台灣科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路333號9樓</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>月薪 1,200,000元以上</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>▍Technical capabilities
+－Enterprise Architecture: Design end-to-end data architectures to fit with overarching enterprise architecture. Define data taxonomies and data dictionaries. Curate strategic datasets, and optimize the design of data integrations, processing, and storage for data consumption patterns. Apply data correlation, denormalization, tagging, and validations at strategic points across data pipelines being executed across a common data platform. 
+－Solution Design: design fit-for-purpose solutions by objectively weighing considerations from resource skillsets, time pressures, costs, and operational complexity. Build simple yet scalable and extensible solutions with low operational upkeep. Solution design experience across big data, application development, automation, and infrastructure 
+－Customer Centricity: Engage internal customers and stakeholders to develop initial requests and ideas into real-world solutions and implementations. Focused on ascertaining the true underlying need and problem parameters. Iterate through solution options and communicate trade-offs in business and end-user terms such as experience, quality, resiliency, timelines, and cost. Develop quick proofs as an effective tool to demonstrate solution concepts and feasibility. 
+▍Knowledge and Experiences
+－Experience in building and maintaining reliable and scalable ETL on big data platforms as well as experience working with varied forms of data infrastructure inclusive of AWS S3, Apache Hive on S3 or Databricks on S3. 
+－Experience working with cloud big data platforms such as AWS and relevant services such as Glue, Lake Formation, Lambda, Sagemaker, EMR, etc. 
+－Experience with Data Lake / Data Lakehouse Infrastructure, such as Delta Lake, Databricks, Snowflake, etc. 
+－Experience and deep knowledge of data modelling techniques, and relational and nonrelational databases, such as MySQL, MongoDB, etc. 
+－Expert knowledge of SQL, Python and Spark, Strong programming background for data exploration/analysis, and solution prototyping capabilities. 
+－Experience of using Data ETL solutions, such as Fivetran, Stitch, etc. 
+－Expertise in data modelling principles/methods including conceptual, logical &amp; physical Data Models. 
+－Experience with code version control is requried, such as Gitlab, Github, Bitbucket, etc. 
+－Background with any of these are highly desired. 
+－Machine Learning, Mathematics, Statistics, Algorithm Design 
+－Finance or Trading Industry 
+－Backend Development / Restful API 
+▍Non-Technical capabilities
+－Ownership and Leadership, and needs to mentoring Junior as Team Lead or Senior Professional 
+－Exceptional written, verbal, and interpersonal communication skills to be able to bridge the gap between business and technical teams. 
+－Ability to work within complex and challenging data environments o Proven experience in collaborating with internal, analytics, reporting and data teams. 
+－Ability to work independently and multi-task to meet critical deadlines in a rapidly changing environment. 
+－Agile Project Management Skill is highly desired.</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/864mn</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>核桃運算股份有限公司</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路一段9號4樓</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備 3-5 年經驗的資料工程師，加入我們的數據團隊。您將負責設計、構建並優化高效率的 Data Pipeline，確保資料從來源端到分析端的準確性與即時性。 此職位不僅需要強大的 Python 與 ETL 開發能力，更需要您對</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8waxf</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>20260525</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>【台北 / 彈性遠端】Sr. Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>布魯斯人事顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中正區 </t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>月薪 1,400,000元以上</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1. 負責大規模資料的雲端基礎架構設計與演進，涵蓋資料流、整合處理、儲存分析與事件偵測等核心能力。
+2. 與相關團隊協作，提出並實作資料架構的優化與轉移計畫，打造具高可用性、可擴展性與韌性的基礎設施。
+3. 兼顧業務成長與工程實作</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wrnj</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>三竹資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>台北市中山區 新生北路二段39號11F</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Airflow 排程管理經驗、DB 帳號權限控管經驗，或有處理高併發金融資料流之經驗。
+職務內容：
+1. 本職務屬於產品任務，配合研發團隊發展金融科技應用之日常資料工程，並負責穩定性維護與效能優化。
+2. 參與設計高可靠性（High</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mtc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>【外商】[RC-Data] Data Engineer / 資料工程師</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路捷運中山站六號出口共構大樓</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>【職位亮點】
+1. 數據規模化：處理全球跨時區、千萬級日活躍用戶產生的金融級即時交易數據流。
+2. 技術主權：參與從 0 到 1 的架構重構與技術選型，我們鼓勵工程師定義數據標準。
+3. 前沿技術棧：深度實踐三層式資料湖架構（Medallion</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wyu9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>20260415</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>數據工程師(Data Engineer) - Python/API開發/ETL</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>果友科技有限公司</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備後端思維的數據工程師，打造數據產品與並與分析客戶團隊合作，建置高品質的數據供應與自動化環境。
+你的主要任務是確保數據能穩定流動、被正確處理與自動化運作，成為支撐企業決策與AI應用的堅實基礎。
+【工作內容】
+1. 設計、開發與</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8thk7</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>【台北】數據工程師Data Engineer — "Data Infrastructure Architect"</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>創智動能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>台北市中正區 八德路1段23號9樓</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>至數據倉儲或資料湖。 
+   確保數據準確性與一致性，並優化數據處理效能。
+Data Transformation and Integration
+Design and implement data transformation processes</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8kgsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>RD-數據工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>順立智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>台北市內湖區 內湖路一段360巷8號7樓</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>板（命名、開發流程、文件）
+【Must Have】
+－2+ 年資料工程/資料管線相關經驗
+－熟悉 SQL + Python
+－熟悉任一資料倉儲
+－有資料品質/監控/回溯經驗
+－具產品數據概念</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7njt5</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SWRD_Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Position Impact：
+資料工程師的核心價值在於設計、建置並維護整體的數據解決方案，確保全公司的數據具備高可用性、可靠性及可擴充性。在此職位中，您將處理大規模數據庫，主動識別潛在風險，並開發能提升數據效能與品質的解決方案。您將與後端工程師</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ti6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>立視科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>多媒體傳播相關業</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>台北市松山區 八德路四段760號6樓</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位熱情且富有才華的資料工程師，加入我們的團隊，協助解決廣告投遞的資料內容。在這裡有大量的數據供你發揮所長，將學過的知識及方法應用到實務的工作上。
+我們希望你具備以下三大特質：
+對資料工程領域有強烈興趣和熱情 。
+重視團隊合作，具備</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zz6u</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>20260530</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>GIS資料工程師</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>九福科技顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>台北市大同區 重慶北路二段48號2</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>1.具備熟悉QGIS、ArcGIS、影像分析及資料分析處理能力
+2.有資料庫與SQL語句應用經驗者優先錄取
+3.數據處理能力、Python、資料搜集、彙整、分析能力、文件撰寫能力者佳
+4.檢核、搜集、彙整、分析比對資料，GIS圖資處理及製程文件彙</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78nq1</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>英屬開曼群島商萬里雲互聯股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段333號33樓</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>【職務說明】
+       我們正在尋找一位具備高度專業技能的資深資料工程師，加入我們快速成長的資料與AI解決方案團隊。此角色將負責設計並交付可擴展的資料平台、建置資料管道，並推動雲端/地端環境下的資料搬遷，以銜接AI分析應用落地。</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p7ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師 (台中)</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>微碧愛普科技有限公司</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道二段659號8樓</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>需此職位與產品團隊和前後端工程團隊緊密合作，負責資料基礎建設的穩定性與資料品質，並推動新一代 AI 資料應用的落地。
+【工作內容】
+1. Data Infrastructure 建置與維護：負責 Airflow 的部署、調優與日常維護，確保排程</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xujh</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Tableau資料工程師</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>緯德科技股份有限公司 (TechLink Corporation)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號8F-13</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>- 熟悉數據分析和Tableau報表開發實務經驗1年以上。
+- 熟悉資料庫安裝、設定及操作實務經驗1年以上。(Oracle、MS SQL Server、MySQL至少一種)
+- 可獨立或與團隊合作，工作態度積極、負責，能配合公司規定。
+- 依不同</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>侍達遊戲藝術有限公司</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>台北市信義區 東興路41號5樓</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>1. 根據分析需求進行資料建模，並提供視覺化的資料呈現。
+2. 提供分析數據及報表。
+3. 設計與開發資料分析所需要的工具。
+[能力需求]
+1. 具備程式開發經驗 (Python/Golang等)。
+2. 具備 SQL/NoSQL 使用經驗</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85yiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>I3901 資深雲端數據工程師(Senior Cloud Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>遠傳電信股份有限公司</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>電信相關業</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>新北市板橋區 遠東路68號 (需視客戶需求於雙北移動)</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>10年以上</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>本職位主要負責建置並最佳化數據管線 (Data Pipeline)架構，為跨部門團隊提供資料收集與處理流程設計。需具備從零開始建立並持續優化資料系統的能力，經驗豐富的數據管線設計師與ETL開發人員的角色。將協助軟體開發人員、資料庫架構師、數據分析</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91pzc</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>科技部_Data Engineer 數據工程師 (Data &amp; AI Product)</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>美好證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路三段２號4樓</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>】
+我們正在打造新一代的 DATA/AI 智能化運轉體系，以先進的數據工程、資料平台與 AI 技術，推動投資研究、產品創新與顧問服務的核心能力全面升級。
+此角色將負責設計、建置與維運公司的核心數據基礎設施 (Data &amp; AI Platform)</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7b6bq</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>久浪智醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 新竹縣竹北市生醫路2段150號</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 生醫與影像數據統計分析
+2. 數據庫建立與維護
+3. AI/ML 模型建立
+4. 自動化及優化工作及數據流程
+5. 具備AI Agent &amp; MCP protocol專案經驗
+</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8idjr</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>天線研發工程師</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>連騰科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>其他相關製造業</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>新北市新店區 北新路三段225號5樓(台北矽谷)</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 調適與優化NB天線，天線頻段包含WWAN , WLAN , MIMO
+2. 製作天線測試報告、資料匯整、PPT簡報
+3. 研發天線創新項目
+4. 電磁模擬軟體操作
+5.提供顧客專業問題上的解決之道
+6.協助完成其他工程師的專案與主管交辦事項
+</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/89rmh</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>維運工程師 (Operations Engineer)</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>愛訊電網科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>電信相關業</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>台北市中正區 衡陽路51號11樓之4</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>令與基本維護能力。
+2. 基礎 MySQL 資料庫操作與安裝能力。
+3. 基礎 Apache / Nginx 設定與安裝能力。
+4. 能夠使用任一程式語言撰寫簡易 Script 。
+5. TCP/IP 基礎網路概念與基礎網路架構概念。
+● 即使</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/923uq</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師(錦州街)</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>山富國際旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>台北市中山區 錦州街46號10樓</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>月薪 48,000元以上</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">與效能調校。
+與後端工程師協作，確保數據收集與儲存的效率與規範。
+探索並導入新興的數據技術與工具，持續提升團隊的數據處理能力。
+</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/73ifb</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>數據工程師 / Data Engineer (Data Infrastructure)</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>富華創新股份有限公司台中分公司</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>建築及工程技術服務業</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>台中市北屯區 太原路三段1315號</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士、博士</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>協助各業務單位理解數據價值，推動企業從「經驗法則」逐步邁向「數據驅動」的決策模式。
+▍我們期待你具備
+・3 年以上資料工程、後端開發或資料庫管理經驗，精通 SQL 與 Python。
+・熟悉 GCP 雲端數據與 AI 生態系：具備</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zban</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>20260415</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>數據工程師(Data Engineer) - Python/ETL/MongoDB</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>果友科技有限公司</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段333號</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備後端架構思維的「數據工程師」，能與企業客戶的數據分析、工程團隊協作，打造穩定且可擴展的數據處理流程。
+這份職缺主要任務是設計並維運高可靠性的 ETL 與 Airflow 數據流程，確保資料能自動化運行、正確轉換，成為企業決策與</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8urkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>云智資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市松山區 </t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>1.具有資料分析經驗1年以上
+2.資料庫語法開發2年以上經驗並熟悉SQL（MS Sql 尤佳）
+3.ETL 開發經驗1年以上（Trinity ETL尤佳）</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7ihuk</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資深資料工程師(Python)</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>宇利峯有限公司</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>台中市西屯區 市政路386號</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>職位概要:
+我們正在尋找一位專精於資料整理和Python開發的Python資料工程師，主要負責資料的清洗、標準化和品質控制工作。
+1. 數據清洗和標準化:
+- 處理原始資料，識別和處理異常值。
+- 統一資料格式和編碼標準。
+- 補齊缺失值和修正</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>資深資料工程師｜Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>街口電子支付股份有限公司</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號8樓(C棟)</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>◆THE ROLE &amp; THE TEAM 
+As a Data Engineer in JKOPay, you will be responsible for processing JKOPay’s online transaction data and offline data analysis with your experience in data engineering. JKOPay serves +6 million users in Taiwan, as well as partners and stakeholders that integrate with our payment service, which handles 3-billion transaction amounts every month. 
+With the rapid growth of JKOPay’s business, Data Engineer is the key to designing systems for collecting, storing, and analyzing data at scale, as well as convert raw data into usable information for business analysis to interpret. 
+This is an opportunity to help shape and expand JKOPay’s ETL data pipeline. If you are interested in handling multiple-terabyte data and improving engineering efficiency, in a great team that keeps growing, this role is for you. 
+◆WHY YOU SHOULD BE INTERESTED 
+-Translate business requirements &amp; end to end designs into technical implementations and responsible for building batch data warehouse. 
+-Manage data modeling design, writing, and optimizing ETL jobs. 
+-Collaborate with the business team to build data metrics and data visualization based on data warehouse. 
+-Responsible for building and maintaining data products. 
+-Involvement in rollouts, upgrades, implementation, and release of data system changes as required for streamlining of internal practices. 
+◆WE'D LOVE TO MEET YOU IF 
+-At least 2 years of relevant experience in data engineering. 
+-Proficient in creating and maintaining complex ETL pipeline end-toend while maintaining high reliability and security.
+-Familiar with backend engineering and practical knowledge of shell, SQL, and one more programming language (e.g. Python, Scala, etc.). 
+-Familiar with the common distributed computing engine or platform (e.g. ClickHouse, Spark, Kafka, BigQuery, Airflow, etc). 
+-Familiar with at least 1 data exploration and visualization platform (e.g. Superset, Tableau). 
+-Familiar with data lake, data warehouse, and data mart concept, and have production experience in modeling design. 
+-Familiar with at least 1 Cloud data flow solution (e.g. AWS Data Pipelines, GCP Dataflow, etc.) is a plus. 
+-Experience with Data Catalog is a plus. 
+-Excellent interpersonal and communication skills with the ability to engage and managing internal and external stakeholders across all levels of seniority.</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7jw2n</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>成強科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>新北市林口區 仁愛路二段502號1808A</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>月薪 32,000 ~ 40,000元</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>公司目前正著手跨領域製作新型遊戲  (運動相關)，
+詳見官網:https://jacfit.com.tw/
+主要工作內容:
+1.對現有資料分析算法進行維護。
+2.與研發團隊針對設備軟體數據資料，進行採集及分析。
+3.根據產品開發要求，與團隊協作</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8e1v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>20260527</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>AI資料工程師</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>力新國際科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>台北市內湖區 新湖一路128巷15號6樓</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> schema設計、KG-RAG整合。
+七、設計多租戶資料隔離（Multi-tenant Collection/ Namespace），防止跨租戶資料污染。
+八、實作增量同步機制：文件變更偵測、CDC、增量索引，避免每次全量重建。
+九、建構Data</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/9188l</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據架構工程師) – (數數發中心, DDT)</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>【關於我們】
+我們是國泰產險的資料科學（DS）團隊，使命在於持續進化數據應用，創造並釋放數據價值。目前正在藉由數據上雲、數據治理與 AI 技術應用，推動由底層架構到業務應用的全端數據生態建構與 AI 轉型準備。
+我們尋找認同以下團隊文化的夥伴：</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8opms</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>徵  數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>臺北醫學大學</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用之</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xi1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>資料工程師 (電商專案)</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>碩誠國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路170號14樓D室</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+3.跨部門協作: 訪談需求單位，配合業務目標，應用AI智能模型與數據技術規劃落地於業務場景之方案。
+4.數據處理與特徵工程: 從零開始進行數據清洗、特徵工程及分析，確保數據質量與模型效能最佳化。
+5.資料建模分析: 透過訓練機器學習模型及數據分析，</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/915ue</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>文境資科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>專門設計相關業</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師
+1.資料稽核(Data Auditing)、收集(Data Collection)、整合作業(Data Integration) 等資料分析前處理作業
+2.有MS SQL server、SSIS、SSRS</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7g1tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>重高科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段162號12樓之2</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Technical Skills)--
+我們希望候選人在以下多數領域具備實作經驗：
+1. Python：精通 Python，特別是在資料工程與自動化流程的應用（而不僅僅是撰寫簡單腳本或 ML 模型）。
+2. SQL：專家級別，具備 BigQuery 或類似雲端資料</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvez</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>可樂旅遊旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段90號12樓</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>資料運用並創造商業價值，並積極探索 AI 技術，提升整體營運效率與決策品質。
+【工作內容】
+1. 設計、開發與維護數據流程，打造穩定且高效的數據基礎架構
+2. 使用 Python 進行數據清理、轉換與處理
+3. 將數據處理流程自動化，並協助部署至雲</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/853np</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>20260512</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>東海大學智慧永續循環經濟研究中心誠徵資料工程師</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>東海大學</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>其他教育服務業</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道四段1727號</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具環境工程背景、能將專業知識轉化為結構化資料與知識模型的人才，加入智慧永續循環研究中心，共同建構以環工知識為核心的 AI 與知識圖譜系統。
+本職位的核心任務不是單純做資料清洗或模型訓練，而是：
+把環境工程的「機制、概念與流程」</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y8zy</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>產品三部 | 資料工程師(高雄)</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>騰雲科技服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中華四路45號2樓</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>✅ 工作內容｜你會負責的任務
+1.數據建模：負責設計與維護 MDP 平台的資料模型，確保能有效支撐財務、銷售、行為等多維度主題數據。
+2.ETL 流程開發：配合使用 ETL 工具，撰寫高效能的 T-SQL 邏輯進行數據清洗、轉換與載入。
+3.效能</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xvzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>大江生醫股份有限公司(TCI CO., Ltd)</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>台北市內湖區 港墘路187號8樓</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Lake。
+．   與資料科學團隊合作，提供模型所需的資料集與特徵工程支援（如 LightGBM、XGBoost）。
+．   透過Power BI進行資料串接與報表資料結構設計，確保分析資料即時、準確。
+．   撰寫技術文件，維護資料流程運作紀錄</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/69p6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>資料科學工程師 (Data Engineer) -- 資料科學實驗室 (數數發中心,DDT)_I00018190</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[工作內容]
+職務包含但不限於以下內容
+- 基於 Python 語言之產品開發，推廣及後續維護
+- Docker/Kubernetes 相關技術應用研發
+- 雲端技術應用及研究
+- 創新資料科學工程架構研究及開發
+- 大數據專案開發實作
+</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8hztb</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>聯想感行銷科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>台北市松山區 民生東路三段135號3樓</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>月薪 900,000元以上</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>協作定義與完成團隊/客戶資料流開發，協助梳理與排除運作中的 data pipeline 產生的各種突發程式狀況，並完成記錄與建檔，您應可獨立開發系統串接、大資料清整。在工作過程中，您會與工程團隊、設計團隊、產品團隊溝通協作，完成規劃之項目與習慣自</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8t66i</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>製程資料工程師</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>聯亞光電工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>台南市善化區 西善一路9號</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>1、了解產線流程，協助將製程與生產資料系統化
+2、規劃並建置製造相關資料庫，確保資料可追溯、可查詢
+3、開發或維護內部系統，降低人工紀錄與 Excel 作業
+4、建立基本報表與視覺化畫面，呈現產線狀態與歷史趨勢
+5、與製程、工程、設備單位合作，支</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x7cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>20260523</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>商業智慧系統開發工程師</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>碩益科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>台北市大安區 光復南路102號9樓</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>1.	負責報表、儀表板及分析應用需求開發與維護，支援營運管理與決策分析需求。
+2.	依業務需求進行資料整理、欄位定義、邏輯設計及報表呈現規劃。
+3.	使用 Power BI、SAP Analytics Cloud（SAC）或 SAP BW 等工具</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90mor</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>南部 水電工程師</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>偉創綠技術股份有限公司</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>環境衛生及污染防治服務業</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>台南市新市區 樹谷園區管理中心</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 45,000元</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>01.有環工、電機相關工作經驗或觀念者佳
+02.設備維護保養紀錄
+03.執行工程監工相關行事(非勞務操作員)
+04.一般設備操作、保養
+05.庶務性行政與一般文書資料歸檔
+06.其它公司交辦事項
+07.作業謹慎負責、具溝通協調能力
+08.具勞工安</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8859d</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>【國泰投信】資深資料工程師 Senior Data Engineer_I00022193</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>國泰證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號6樓</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>定 ETL 資料處理流程（資料存取、蒐集、處理和儲存）的開發標準與最佳實踐，確保系統的高效、穩定與可擴展性。
+4. 負責數據架構的效能優化，指導並帶領團隊解決技術難題。
+【必要條件】
+1. 5 年以上資料工程經驗，具備分散式系統與容器化經驗。
+2</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qbnl</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>20260125</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1.在Hadoop架構的資料倉儲(Data Warehouse)上建立具備擴充性與高可靠性的資料產品，為數據科學家與業務團隊提供穩健的資料基礎。
+2.與數據科學家和業務分析團隊合作，理解需求並提供適用的資料解決方案。
+3.設計並構建</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n58n</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>(C6) 資深數據工程師Senior Data Engineer（內湖）</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>【職位說明】
+參與智慧城市 AI 賦能產品開發，負責建置企業級數據平台(Data as a Service, DaaS)，處理各種形式的資料，並進行完善的資料治理、血緣追蹤與監控。最終將整合生成式 AI（Generative AI）功能，提供智慧</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p0av</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>英屬維京群島商嘉碼科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>台中市西屯區 工業三十八路210號3樓之6</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位數據工程師，不僅具備扎實的技術底子，更擁有主動積極、樂於挑戰的特質。
+加入我們後，您將在這個充滿活力、尊重多元的環境中扮演關鍵角色，透過打造穩健的數據基礎與管道，協助團隊從資料中萃取價值、加速產品與業務的創新。
+如果您對資料領域充</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vvrv</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>資深資料科學工程師 Sr. Data R&amp;D Engineer (Backend) - 台中 數據技術發展 (數數發中心, DDT)_I00020704</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>台中市烏日區 台中市烏日區高鐵一路299號</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>[工作內容]
+資深後端工程師職務可能包含但不限如下相關內容：
+- 開發與維護現有應用服務
+- 與前端人員合作設計 API 接口
+- 熟悉資料與 AI 模型應用服務開發，與資料科學家合作解決商業命題
+- 具有 Open Source 研究與使用經驗</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n5io</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>20260525</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>D02-資料工程師(DE)_旅遊科技部_數據營運組</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>雄獅資訊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路151號</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>我們正在尋找對科技趨勢敏銳、樂於實驗的技術創新人才。你將成為旅遊科技部的技術推進引擎，結合 AI、前沿工具與跨領域思維，探索下一個改變旅遊產業的數位可能。
+1. 介接並整合內外部資料來源，確保資料的高可用性與一致性
+2. 設計、開發、測試與維護</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ppdw</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市萬華區 </t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>【職務需求】
+1. 以 Data Engineering 為主，包含 hands-on data pipeline、ETL、data modeling、以及上游系統整合經驗。
+2. 需具備資料整合、資料品質與資料模型設計能力。
+3. 熟悉</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Data Engineer (Mid Level)  資料工程師（中階）</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>極酷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路2段26號2樓</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✨加入 KICKS CREW，與我們一起成長！CAN'T STOP WON'T STOP✨
+We are a rapidly growing global e-commerce platform specializing in sneakers and apparel. Our engineering team is committed to building cutting-edge technologies that continuously transform how customers discover, shop, and engage with our platform.
+We are looking for a Data Engineer with 3+ years of experience building and optimizing data infrastructure. This role will focus on BigQuery warehouse optimization, event tracking quality, and scalable data pipeline design.
+✨Key Responsibilities
+Data Warehouse Optimization
+• Optimize and refactor BigQuery data models for performance and cost efficiency
+• Improve table structure, partitioning, clustering, and query performance
+• Maintain and enhance ELT pipelines
+• Enforce data quality checks and documentation standards
+Event Tracking Quality
+• Audit and redesign Mixpanel and GA4 tracking architecture
+• Validate GTM, SDK, and server-side event implementation (QA Process)
+• Standardize event naming and tracking schema
+• Identify and close tracking gaps
+Data Pipeline &amp; Integration
+• Build and maintain scalable data pipelines into BigQuery
+• Handle structured and semi-structured data
+• Support cross-domain data integration
+BAU &amp; Collaboration
+• Support BI team on optimization-related data requests
+• Troubleshoot discrepancies across warehouse and tracking tools
+• Document data lineage and ownership
+✨Requirements
+Experience
+• Minimum 3 years of experience as Data Engineer or similar role
+• Strong hands-on experience with cloud warehouse.
+• Experience with event tracking architecture and debugging (QA)
+Technical Skills
+• SQL/Programming Proficiency
+• Workflow Orchestration (e.g Apache/Airflow/Dagster, etc)
+• Experience with ETL or ELT pipeline design
+• Familiar with event-based tracking models
+• Understanding of data modeling and warehouse best practices
+Nice to Have
+• Experience with the modern data stack (e.g., dbt, Airbyte, Datahub)
+• Familiarity with Docker and Kubernetes
+• Experience integrating and managing Mixpanel and GA4 data
+</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90m7j</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>20260409</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>遊戲資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>吉恩立數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段106號5樓</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>我們找的就是你：善於溝通、邏輯清晰及執行力的工程師 !
+負責一款遊戲，
+從資料庫初期的建置發佈以及遊戲整體環境建置，到後續服務的長久運行管理。
+在這裡你不會感到孤單，會有同仁一起參與合作與營運，當然，熟悉後也有需要獨自運作的時刻。
+【工作任務</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tymj</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Data Engineer (Mid Level)  資料工程師（中階）</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>極酷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路2段26號2樓</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> optimize scalable data infrastructure.
+此角色將支援公司整體資料工程專案，包括 BigQuery 數據倉儲優化、事件追蹤品質與資料管線建置。
+ This role will support company-wide</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvll</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>【擴編】資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>聖文森商瑞德克斯科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>台中市西屯區 朝富路213號19樓</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+※ 工作專業需求：
+1. 具資料視覺化工具（Tableau / PowerBI / Metabase）經驗</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xdrn</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>20260525</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>康統醫學科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>台北市中正區 北平東路16號8樓</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>熟悉至少一種關聯式資料庫：PostgreSQL / MySQL / SQL Server 其一或多種。會設計 schema（正規化）、index、view、stored procedure。
+扎實 SQL 能力：複雜 JOIN、視圖、</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x02n</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>BI 數據工程師  (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>神來也麻將_慧邦科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>台北市中正區 羅斯福路二段100號10樓</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>1. 建置與維運遊戲數據 ETL / ELT 排程。
+2. 與分析、PM、營運合作，提供即時數據查找並建置固定排程或後台功能。
+3. 進行資料品質檢查、異常偵測與基礎探索分析。
+4. 開發與維護數據後台、API 與資料平台相關功能。
+【專業條</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/6u7bu</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>量化投資金融大數據工程師</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>沛然資訊有限公司</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街150號7樓</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>年薪 800,000 ~ 1,500,000元</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>控與跨市場操作等關鍵場景中。我們開發可用於決策的高互動行動應用，誠摯邀請對產品品質與金融邏輯有熱情的夥伴加入我們的團隊。
+【工作內容】
+1. 台清交成資工系學碩士優先。
+2. 優秀IT科技理工且對量化投資有興趣者。
+3. 量化交易相關資料庫的維運</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7mnu3</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>ETL 資料工程師/大數據工程師</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>歐立威科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>台北市大同區 鄭州路87號11樓之1</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Pentaho PDI、Talend、Informatica、Microsoft SSIS 等）進行數據抽取、轉換與載入，確保資料正確性與完整性。
+3.熟悉 Python 或 Java 等程式語言，能撰寫 ETL 腳本與自動化流程。
+4.設計並維護 Data</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ugrj</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>AI數據工程師</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>建準電機工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>專用生產機械製造修配業</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中正一路120號12樓(近捷運-苓雅運動園區站)</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>1. 建立、維護與優化企業數據中台，整合內部各系統資料，確保資料一致性與可用性。
+2. 設計 ETL 流程與資料庫架構，提供 AI 模型與報表系統所需資料。
+3. 監控資料質量，定期進行資料清洗與效能優化，確保數據中台穩定運作。
+4. 報表開發</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xjwv</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>20260530</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>臺北市立萬芳醫院-委託臺北醫學大學辦理</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>醫院</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>月薪 43,700 ~ 45,900元</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。 
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8z3ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>億力資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中山區 </t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>效
+3. 跨部門協作: 訪談需求單位，配合業務目標，應用AI智能模型與數據技術規劃落地於業務場景之方案。
+4. 數據處理與特徵工程: 從零開始進行數據清洗、特徵工程及分析，確保數據質量與模型效能最佳化。 
+5. 資料建模分析: 透過訓練機器學習模型</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90e1j</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>20260511</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>像素數科技術有限公司</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>台北市大同區 承德路一段 2 號</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>年薪 1,000,000 ~ 1,800,000元</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+- 監控數據流程和數據質量，及時發現和解決數據品質問題；
+- 維護和更新工程處理中的文件與資料字典；
+- 編寫清晰的程式碼文件和註釋，以確保團隊成員能夠理解和使用你的程式碼；
+- 持續關注數據技術的發展趨勢，不斷學習和探索新的數據技術和工具。
+</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7rkad</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>20260419</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>[台北]資料工程師實習生（AI &amp; BI）</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>台灣新蛋股份有限公司</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路513巷31號10樓</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>月薪 24,000元以上</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+    •  對數據分析、BI 或資料工程有興趣
+    •  願意學習新技術，具備良好邏輯思考能力
+【加分項】
+    • 有簡單資料分析 / BI / ETL project 經驗（課程或 side project 皆可）
+    • 有使用</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90be7</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>(台北市 文山區)物料管理員/物料管控員/採購專員/採發專員</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>華富水電工程有限公司</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>空調水機電工程業</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>台北市文山區 忠順街二段12號1樓</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>#曾有機電工程相關經驗尤佳
+#熟悉機電工程 水電材料/管線/五金另件尤佳
+1.標單和在建工程物料規格及數量控管。
+2.與工地及廠商聯繫每日進料事宜.追蹤。
+3.設備材料處理訂貨、退換貨...等相關聯繫及追蹤。
+4.其他主管辦事交項。</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d4e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>視覺AOI工程師</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>驊鋒國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>其他半導體相關業</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 光明六路東一段247號9樓</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>月薪 70,000 ~ 85,000元</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-開發與維護 AOI 影像處理與缺陷檢測模組
+-實作影像前處理、特徵萃取與缺陷分類演算法
+-與硬體、光學、運動控制工程師合作完成系統整合
+-協助機台測試、資料分析與效能調校
+-2以上年影像處理或機器視覺相關開發經驗
+-熟悉 C++ 或</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/9292u</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>20260321</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>【凱基證券/數位創新部】數據工程師</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>凱基金融控股股份有限公司|凱基證券|凱基銀行|中華開發資本|凱基投信</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>台北市中正區 重慶南路一段</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>1. 資料倉儲等系統或機器學習建模之資料收集、開發處理與管理維護
+2. 業務單位數據需求開發</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/89pxp</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>果實夥伴股份有限公司</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路610號2樓</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>【工作內容 】
+-  ETL 之開發、處理(資料清理、儲存、分析)與監測
+- 開發與設計專案所需 API 服務並與後端工程師合作，完成系統產品化程序
+- 依據不同業務需求，完成建置/維運/更新各式 Data infra 的需求
+- 與數據產品管理</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7dpwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>雲端數據工程師</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>君綺生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>美容／美體業</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>台北市信義區 松智路1號</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>部門介紹:
+我們是集團組織擴編成立的新部門, 在這工作你將會體驗全雲的工作環境, 包含AWS雲端服務及工具, 在工作中學習專案管理、資料庫管理、雲端服務等技術
+工作內容
+1. 參與雲端數據架構發展規劃，設計資料處理、儲存、分析架構，以符合數據</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mcsu</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>20260530</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Cloud &amp; Data Engineer 雲端與資料工程師</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>阿卡希亞股份有限公司</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>桃園市桃園區 中正路1125號7樓</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Job Summary:
+本職務 Cloud &amp; Data Engineer 將同時建構與維護雲端、資料、AI 與資安相關系統的設計與交付，協同技術團隊成員提供系統整合（System Integrator, SI）服務，服務跨國企業集團或上市櫃客</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yz82</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>行銷部-數據工程師 ( Data Engineer )</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>全聯福利中心_全聯實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>量販流通相關業</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>台北市中山區 敬業四路33號</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>動力，能適應快速變化的技術環境，持續精進技能 
+4. 勇於挑戰創新 - 保持開放心態，不設限自己的發展，樂於嘗試新技術與跨領域合作
+數據工程師的核心挑戰與工作內容：
+1. 數據處理與自動化 — 了解與整合異質數據來源（API、資料庫、CSV、</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7xcgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>開元食品工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>其他食品製造業</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>台北市內湖區 民善街</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士、博士</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具創新精神並熱衷於資料科學領域的 資料工程師 加入我們的團隊。您將負責建立及維護高效的資料處理架構，確保數據在多元系統間流暢流通，並能夠進行高效的數據存儲與分析。若您對資料技術充滿熱情，並擁有相關的技能與經驗，我們非常期待您的加入</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8lttn</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>20260331</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>職務目的：參與銀行級大型資料倉儲與雲端轉型專案。
+工作內容：
+1.維運數據倉儲 ODS 資料庫：
+•規劃與管理資料庫空間與使用者權限。
+•監控系統運作狀況，進行問題排查與修復。
+•確保資料庫效能與穩定性。
+2.資料導入流程管理：
+•設計與實作</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7p5ll</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>AI Data Engineer AI 資料工程師</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>摩速科技有限公司</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>台北市大安區 仁愛路三段17號3樓</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>性、可解釋性、結果正確性
+- 調查資料異常與不一致問題，找出根本原因，並建立可持續的預防與監控機制。
+- 與產品、商務與工程團隊合作，對齊資料定義並交付關鍵資料資產。
+- 建立或延伸 AI 產品功能，例如：Agent workflow、推薦邏輯、自</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91odq</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>軟體產品工程師</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>永聚資科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>新北市板橋區 四川路2段16巷10號1樓</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+‧ 寫過 RESTful API、處理過實際業務邏輯
+‧ 看過、用過、改過別人的程式碼（不是只會寫新東西）
+‧ 重視程式碼品質：會寫測試、會 review、會重構
+‧ 對「打造產品」有熱情，不只想當外包工程師
+公司會提供的支援】
+‧ 每月 1,</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qb3t</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>澧曜數據有限公司</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>台中市西區 忠明南路497號2樓</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 開發/維護/設計處理數據架構與服務以及部署服務。
+2. 負責ETL（數據提取、轉換、加載）流程設計，包括數據清洗、預處理及自訂程式開發。
+3. 擁有CI/CD經驗，熟悉Jenkins、GitLab、Airflow等CI/CD工具和流程。
+</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dclx</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>【凱基證券/數位創新部】數據工程師</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>凱基證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>台北市中正區 重慶南路一段</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>1. 資料倉儲等系統或機器學習建模之資料收集、開發處理與管理維護
+2. 業務單位數據需求開發</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7jogm</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>20260514</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>【Data Engineer】 資料工程師</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>新加坡商昇新科技股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞湖街58號5樓</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>我們正處於數據架構升級的關鍵階段。尋找一位數據工程專家與我們共同重新定義數據流。
+你將負責冷熱數據分離架構的落地，並優化我們的 Data Warehouse 架構，確保在海量數據環境下，數據依然能兼具查詢效能與成本。
+【你將面臨的核心技術挑戰】</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x352</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>【研究發展處】Big Data Engineer 資料工程師 / Senior Big Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>現觀科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段42號2樓</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Dashboard Visualization，並與產品開發團隊進行資料探勘及研究。
+[工作內容]
+1.開發大數據系統資料處理平台
+2.串流資料平行處理程序開發,熟悉分散式運算,平行運算
+3.解決大量資料處理時所衍生的效能,擴充與維護維運資料庫</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7bdqr</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Regional Data Engineer 數據工程師(台北工作)</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>香港商麥迪康亞太有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路1段163號4樓之3(市府站1號出口)</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>1.設計、開發和維護可擴展的數據管道和ETL流程。
+2.與數據科學家、分析師和利益相關者合作，了解數據需求並提供解決方案。
+3.優化和改進現有數據系統，以提高性能和可靠性。
+4.實施數據質量檢查，確保各類數據源的數據完整性。
+5.開發和維護數據工程</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8m4mk</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>資訊處-資料工程師 Information Technology Division – Data Engineer</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>永豐商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中山區 </t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>自我學習研究能力，且對資料技術具備敏感度
+具良好的溝通與協作能力，樂於與團隊分享想法與知識，推動團隊成長。
+Job Responsibilities:
+1.	Develop, maintain, refactor, and optimize</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/909yb</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>全端資料工程師（資料平台）  Full Stack Engineer (Data Platform)(台南優先,台中)</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>葳誠科技有限公司</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>台南市善化區 環東路二段33號</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>月薪 70,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>【職務說明 Position Summary】
+中文：
+我們正在尋找一位以資料平台為核心的全端工程師駐點在外商客戶端，負責開發與維運雲端資料平台及相關Web服務。此職位著重於 Databricks、SCM資料倉儲、資料分析/探勘與系統整合，同時</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90phw</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據應用工程師) – (數數發中心, DDT)_I00020717</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+* 目標成果導向：重視成果並具合作互助精神
+* 積極主動、持續進步：樂於學習與自我成長
+* 熱愛數據、對技術充滿熱忱：積極探索與應用新技術
+【工作內容】
+資料工程的世界千變萬化，以下是你的任務指南：
+1. 數據蒐集與處理，接觸各種資料來源，進行</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n8v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>資料工程師 / 數據服務架構師</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Phison Electronics Corp_群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>IC設計相關業</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>苗栗縣竹南鎮 群義路1號</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>算引擎（如 Trino）的維運與優化，透過 Infrastructure as Code (IaC) 與 GitOps 實現數據工程的自動化與標準化。
+【工作內容】
+    容器化平台管理：負責 Kubernetes 叢集的日常維運、資源調度與自動</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ve8x</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>AI 工程師</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>亞達科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台南市善化區 </t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>更上一層樓！
+- 有活力的團隊 ： 和一群熱血又有愛的夥伴一起工作，挑戰再大也不怕，因為我們一起扛！
+- 國際專案拓展機會：公司正積極佈局美國市場重點專案，優秀工程師有機會參與跨國技術合作，與國際團隊協作，累積海外專案經驗！
+現在就是加入 AI</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8lrdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>[DI]  資安數據工程師 Security Data Engineer</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>動力安全資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>做什麼｜What You'll Do】
+你將從基礎開始，逐步深入資安數據工程的核心：
+● 學習業界領先的資安數據平台：你將接受 Splunk 系統性培訓，學習如何管理與維運企業級的資安數據平台，包含 log 收集、資料與欄位前處理到查詢分析。</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4jnp8</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>軟體工程師</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>福盈科技化學股份有限公司</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>其他化學相關製造業</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>桃園市大園區 大園工業區民權路7號</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>1. 資料庫系統串接
+2. ERP應用與維護
+3. 平台程式開發
+4. 雲端環境維運
+5. 企業MIS維運
+6. 企業戰情儀表板開發與維護</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90df9</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>20260530</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>軟體測試工程師  | Manual / Automation Tester</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>一通數位有限公司</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路288號七樓 (距捷運港墘站約500公尺)</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>月薪 50,000 ~ 70,000元</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>【職務說明】
+歡迎熱愛挑戰與學習的你加入我們，一起打造高品質的國際金融科技證券應用系統！
+本職缺開放給具備手動或自動化測試經驗的軟體測試工程師。
+你將參與產品從需求到上線的整個測試流程，確保系統穩定、高效與易用，並與跨部門團隊緊密合作，為最終用戶</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7zzwy</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>SW_資料庫工程師 DBA Engineer</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>蓋亞汽車股份有限公司</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>汽車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>台中市烏日區 高鐵一路299號7樓</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>蓋亞汽車【研發部】擴大招募！
+走向零碳未來，我們期待您的加入。
+我們正在尋找一位熱愛資料庫效能優化、系統架構設計與跨部門協作的【資料庫工程師】，協助我們打造高效穩定的資料架構，支援智慧車輛系統與資料分析應用。
+｜您在蓋亞汽車的工作職掌｜
+✔</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dt2w</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>20260409</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>數據工程師實習生｜AI應用開發｜新創｜雲端大數據實作</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>睿思智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>新北市板橋區 中山路2段443巷77號10樓</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>月薪 200 ~ 200元</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>作的核心內容 Responsibilities】
+1. 協助客戶整合、設計與部署大數據流程及平台。
+2. 設計 Data Pipeline 並整合多類資料來源。
+3. ETL流程開發與自動化、數據處理流程優化。
+4. Data Schema 設計</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xq4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>【新擴編】Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>愛酷智能科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化南路一段2號5樓</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>步汰換舊有的 Digdag 流程。
+2. ETL/ELT 流程開發： 串接 PostgreSQL 與 MongoDB 以及外部資料 等多源數據，清洗並導入 BigQuery。
+3. 數據倉儲模型設計： 使用 dbt 開發與維護數據模型，優化 SQL</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wccg</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Tableau資料工程師(TU001)</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>祐安資訊有限公司</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>台北市松山區 復興北路191號5F-1</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>+ 具備 數據分析和Tableau報表開發 實務經驗
++ 具備 Oracle、MS SQL Server、MySQL 等資料庫(任一即可)安裝、設定、維護及障礙排除實務經驗 
++ 工作態度積極、負責，重視團隊溝通合作 
++ 不當獨行俠，行有餘力時</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>聯想感行銷科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>台北市松山區 民生東路三段135號3樓</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>月薪 1,100,000元以上</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>獨立掌握與釐清客戶資料處理需求、定義資料流規格、定義資料模型，確認運行規格。
+需面對企業客戶並給予資料流與資料 schema 上的回應。
+【專案管理能力】
+熟悉資料流開發、資料流驗証等流程。
+熟悉編寫資料流規格書。
+評估議定工作時程表（WBS</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8t673</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>D4000 資料工程師(推薦/搜尋)</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>富邦媒體科技股份有限公司(富邦momo)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街96號4樓</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1. 負責推薦、搜尋平台系統的資料流設計，並協助開發滿足相關數據產品發展的需求，協助業務團隊發揮數據商業價值
+2. 與資料科學家、演算法工程師、資料分析師等，協作開發推薦、搜尋引擎模型，進行機器學習、深度學習之模型自動化、模型服務架</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8lxd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer【數位數據發展本部】</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>東南旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段60號</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>統性整合資料支撐分析與AI應用的發展
+●	建置優化Data Pipeline，並建立資料品質監控管理機制，確保資料品質和效率
+●	與DA / DS 協作，開發實作數據 / AI產品，參與模型的部署上線與維運
+●	協作工程師設計大規模資料遷移，參與</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tbys</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>【外商】[FIN] Sr. Data Engineer／資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號20樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Dagster 或 Airflow 等排程工具。
+5. 5 年以上資深資料工程師或相關經驗，並具備獨立主導專案的能力。熟練運用大語言模型（LLM）等工具進行需求分析、代碼重構、或自動化編寫重複性 ETL 腳本
+6. 卓越的需求訪談與業務邏輯理解能力，能將複</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dq30</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>20260525</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>資訊處_數據工程師</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>美而快國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>鞋類／布類／服飾品零售業</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>台北市南港區 重陽路203巷29號</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Analytics 4（GA4）
+Matomo
+數據處理與資料工程
+Databricks、Azure Blob Storage
+parquet 資料格式處理
+Dagster、Talend
+資料庫與後端處理
+Microsoft SQL</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90ruo</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>數據工程師（Data Engineer）</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>創代科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路101號10樓</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>定性。
+- 運用 Airflow、dbt 等工具，設計並優化高效、可觀測（Observable）的現代化資料管線。
+- 與機器學習工程師合作，建置穩定可靠的機器學習資料管線（ML Pipeline），支援模型訓練、部署與推論流程。
+- 參與資料湖倉</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ys29</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>AI 工程師</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>巨獸科技有限公司</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>高雄市三民區 鼎泰街</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>程式語言
+Python（必備，AI、資料處理、建模核心）
+JavaScript/TypeScript（Web AI、前端整合）
+軟體工程
+Git / GitHub / GitLab（版本控制）
+Linux 系統操作（伺服器、部署）
+Docker</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8u86z</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>20260427</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Integration Engineer 系統整合工程師</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>荷蘭商范德蘭德工業有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>儲配／運輸物流業</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段129號5樓</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>援客戶的營運流程。
+作為一名 整合工程師（Integration Engineer），你將參與將各種元件與（子）系統整合為完整解決方案的工作。這在大型且複雜的機場與包裹處理系統中尤其具有挑戰性，這些系統包含單件輸送系統、自動倉儲系統（ASRS）、自</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90xoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>20260527</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>【台中】資料工程師</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>敦謙國際智能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>台中市西區 國泰金融大樓(台中市西區英才路 530 號) 24 樓</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 90,000元</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>職務工作內容：
+營運策略系統 (RMS)
+透過資料分析、資料探勘和數據處理技術，為旅宿提供精準的營運決策依據。
+建模預測，根據歷史銷售資料，建立銷售量、住宿率等預測模型，為旅宿決策的制定提供參考。
+協助開發專為旅宿設計的智能客服機器人。
+職務需</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/75oc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>20260505</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>[台北]資料工程師(BI)</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>台灣新蛋股份有限公司</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路513巷31號10樓</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>BI 或資料工程有興趣
+    •  願意學習新技術，具備良好邏輯思考能力
+【加分項】
+    • 有簡單資料分析 / BI / ETL project 經驗（課程或 side project 皆可）
+    • 有使用 Python（pandas</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/917z1</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>〔資訊〕數據工程師</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>台新新光金控_台新國際商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>台北市內湖區 舊宗路二段207號</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>工作內容：
+1.資料數據進行ETL開發、測試與維護ETL資料轉換工作
+2.具備 T-SQL 語法及Stored Procedure開發經驗
+3.分析系統之開發(含批次、介面及報表)
+4. Hadoop Eco System(Spark、Hive、</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8s444</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>AI 提示工程師（Prompt Engineer）</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>台灣骨王生技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>台中市大雅區 科雅路41號2樓</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>AI 提示工程師（Prompt Engineer）
+地點：台中市／台中科學園區
+部門：研發部
+職位性質：全職
+職務說明
+我們正在尋找一位具有 語言模型理解與應用能力、同時能結合提示工程（Prompt Engineering）與 Python</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8r08j</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>【金融科技】資料工程師 Data Engineer(經驗行員)</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>玉山銀行_玉山商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>台北市松山區 民生東路三段115號</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>1.負責設計和維護高效且可擴展的雲地混合數據架構
+2.設計及開發巨量資料 data pipeline，包含結構化資料、半結構化資料及非結構化資料，並建立自動化監控機制
+3.評估與導入 modern data stack，用以解決以下問題：data</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7tqhz</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>【前瞻研究籌獲中心】資料工程師(台南)</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>國家資通安全研究院</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>其他專業／科學及技術業</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台南市歸仁區 </t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>1.協助概念驗證程式開發、後端服務建置及產品功能落地，支援不實資訊、網路詐騙、深偽影音等相關應用系統之開發與維運。
+2.建構高效、可擴展且穩定之後端服務，開發與串接 API、AI 模型推論服務及資料處理流程，並與前端、資料及產品團隊協作完成系統整</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8rkm9</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>20260311</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>【資訊板塊】金融數據工程師(企業資料倉儲整合｜核心系統現代化｜數據架構轉型)_I00024956</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>國泰世華商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>打造金融數據新未來，從你開始！
+你相信數據不只是冰冷的數字，而是能驅動決策、創造價值的力量嗎？
+在這裡，你不只是寫程式，而是參與一場金融數據革命！
+加入我們，打造穩定、高效、可擴展的資料平台，讓每一筆數據都能說故事，讓你的技術真正改變企業未來。</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8whwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>統一超商資深資料工程師(uniopen客戶資料平台CDP)</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>統一超商股份有限公司</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路163號5樓</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>月薪 50,000 ~ 120,000元</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1. 設計資料模型與數據建模轉化 (Data Modeling)：主導 數據架構規劃與 Medallion 模型設計，定義企業級 Golden Table 規範，確保模型具備高度擴展性以支援 AI/ML 應用。
+2. BI 報表與儀</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p2a1</t>
         </is>
       </c>
     </row>

--- a/z_RequestData/jobsearch_data104.xlsx
+++ b/z_RequestData/jobsearch_data104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J441"/>
+  <dimension ref="A1:J551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18358,10 +18358,8 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>20260527</t>
-        </is>
+      <c r="A332" t="n">
+        <v>20260527</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -18415,10 +18413,8 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A333" t="n">
+        <v>20260601</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -18470,10 +18466,8 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A334" t="n">
+        <v>20260602</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -18549,10 +18543,8 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A335" t="n">
+        <v>20260603</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -18604,10 +18596,8 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A336" t="n">
+        <v>20260602</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -18678,10 +18668,8 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A337" t="n">
+        <v>20260603</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -18730,10 +18718,8 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>20260525</t>
-        </is>
+      <c r="A338" t="n">
+        <v>20260525</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -18785,10 +18771,8 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A339" t="n">
+        <v>20260604</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -18840,10 +18824,8 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A340" t="n">
+        <v>20260604</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -18895,10 +18877,8 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>20260415</t>
-        </is>
+      <c r="A341" t="n">
+        <v>20260415</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -18950,10 +18930,8 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A342" t="n">
+        <v>20260529</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -19005,10 +18983,8 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A343" t="n">
+        <v>20260603</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -19063,10 +19039,8 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A344" t="n">
+        <v>20260604</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -19116,10 +19090,8 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>20260528</t>
-        </is>
+      <c r="A345" t="n">
+        <v>20260528</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -19171,10 +19143,8 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>20260530</t>
-        </is>
+      <c r="A346" t="n">
+        <v>20260530</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -19226,10 +19196,8 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A347" t="n">
+        <v>20260603</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -19279,10 +19247,8 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>20260528</t>
-        </is>
+      <c r="A348" t="n">
+        <v>20260528</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -19333,10 +19299,8 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A349" t="n">
+        <v>20260601</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -19388,10 +19352,8 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A350" t="n">
+        <v>20260604</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -19445,10 +19407,8 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A351" t="n">
+        <v>20260602</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -19497,10 +19457,8 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A352" t="n">
+        <v>20260602</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -19551,10 +19509,8 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A353" t="n">
+        <v>20260602</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -19608,10 +19564,8 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A354" t="n">
+        <v>20260602</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -19666,10 +19620,8 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A355" t="n">
+        <v>20260601</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -19723,10 +19675,8 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A356" t="n">
+        <v>20260601</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -19778,10 +19728,8 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A357" t="n">
+        <v>20260601</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -19833,10 +19781,8 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>20260415</t>
-        </is>
+      <c r="A358" t="n">
+        <v>20260415</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -19886,10 +19832,8 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A359" t="n">
+        <v>20260601</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -19940,10 +19884,8 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A360" t="n">
+        <v>20260603</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -19997,10 +19939,8 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>20260521</t>
-        </is>
+      <c r="A361" t="n">
+        <v>20260521</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -20068,10 +20008,8 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A362" t="n">
+        <v>20260603</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -20125,10 +20063,8 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>20260527</t>
-        </is>
+      <c r="A363" t="n">
+        <v>20260527</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -20180,10 +20116,8 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A364" t="n">
+        <v>20260601</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -20234,10 +20168,8 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A365" t="n">
+        <v>20260529</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -20289,10 +20221,8 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A366" t="n">
+        <v>20260601</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -20344,10 +20274,8 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>20260531</t>
-        </is>
+      <c r="A367" t="n">
+        <v>20260531</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -20398,10 +20326,8 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A368" t="n">
+        <v>20260603</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -20453,10 +20379,8 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A369" t="n">
+        <v>20260602</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -20509,10 +20433,8 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>20260512</t>
-        </is>
+      <c r="A370" t="n">
+        <v>20260512</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -20563,10 +20485,8 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A371" t="n">
+        <v>20260603</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -20618,10 +20538,8 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>20260519</t>
-        </is>
+      <c r="A372" t="n">
+        <v>20260519</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -20673,10 +20591,8 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A373" t="n">
+        <v>20260529</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -20732,10 +20648,8 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A374" t="n">
+        <v>20260601</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -20784,10 +20698,8 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A375" t="n">
+        <v>20260603</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -20840,10 +20752,8 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>20260523</t>
-        </is>
+      <c r="A376" t="n">
+        <v>20260523</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -20894,10 +20804,8 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A377" t="n">
+        <v>20260603</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -20953,10 +20861,8 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>20260508</t>
-        </is>
+      <c r="A378" t="n">
+        <v>20260508</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -21009,10 +20915,8 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>20260125</t>
-        </is>
+      <c r="A379" t="n">
+        <v>20260125</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -21064,10 +20968,8 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A380" t="n">
+        <v>20260604</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -21117,10 +21019,8 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A381" t="n">
+        <v>20260604</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -21171,10 +21071,8 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A382" t="n">
+        <v>20260529</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -21228,10 +21126,8 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>20260525</t>
-        </is>
+      <c r="A383" t="n">
+        <v>20260525</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -21282,10 +21178,8 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A384" t="n">
+        <v>20260603</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -21337,10 +21231,8 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A385" t="n">
+        <v>20260602</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -21426,10 +21318,8 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>20260409</t>
-        </is>
+      <c r="A386" t="n">
+        <v>20260409</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -21482,10 +21372,8 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A387" t="n">
+        <v>20260602</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -21536,10 +21424,8 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A388" t="n">
+        <v>20260603</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -21590,10 +21476,8 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>20260525</t>
-        </is>
+      <c r="A389" t="n">
+        <v>20260525</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -21643,10 +21527,8 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A390" t="n">
+        <v>20260602</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -21699,10 +21581,8 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A391" t="n">
+        <v>20260529</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -21755,10 +21635,8 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A392" t="n">
+        <v>20260602</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -21809,10 +21687,8 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A393" t="n">
+        <v>20260602</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -21864,10 +21740,8 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>20260530</t>
-        </is>
+      <c r="A394" t="n">
+        <v>20260530</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -21919,10 +21793,8 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A395" t="n">
+        <v>20260601</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -21974,10 +21846,8 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>20260511</t>
-        </is>
+      <c r="A396" t="n">
+        <v>20260511</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -22031,10 +21901,8 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>20260419</t>
-        </is>
+      <c r="A397" t="n">
+        <v>20260419</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -22088,10 +21956,8 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A398" t="n">
+        <v>20260603</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -22145,10 +22011,8 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A399" t="n">
+        <v>20260603</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -22202,10 +22066,8 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>20260321</t>
-        </is>
+      <c r="A400" t="n">
+        <v>20260321</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -22255,10 +22117,8 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>20260528</t>
-        </is>
+      <c r="A401" t="n">
+        <v>20260528</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -22311,10 +22171,8 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A402" t="n">
+        <v>20260601</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -22366,10 +22224,8 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>20260530</t>
-        </is>
+      <c r="A403" t="n">
+        <v>20260530</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -22419,10 +22275,8 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A404" t="n">
+        <v>20260601</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -22474,10 +22328,8 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A405" t="n">
+        <v>20260603</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -22526,10 +22378,8 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>20260331</t>
-        </is>
+      <c r="A406" t="n">
+        <v>20260331</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -22585,10 +22435,8 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A407" t="n">
+        <v>20260602</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -22640,10 +22488,8 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A408" t="n">
+        <v>20260602</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -22698,10 +22544,8 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A409" t="n">
+        <v>20260602</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -22753,10 +22597,8 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A410" t="n">
+        <v>20260529</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -22806,10 +22648,8 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>20260514</t>
-        </is>
+      <c r="A411" t="n">
+        <v>20260514</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -22860,10 +22700,8 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A412" t="n">
+        <v>20260529</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -22916,10 +22754,8 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A413" t="n">
+        <v>20260601</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -22972,10 +22808,8 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A414" t="n">
+        <v>20260604</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -23027,10 +22861,8 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>20260531</t>
-        </is>
+      <c r="A415" t="n">
+        <v>20260531</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -23081,10 +22913,8 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A416" t="n">
+        <v>20260601</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -23139,10 +22969,8 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A417" t="n">
+        <v>20260602</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -23193,10 +23021,8 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A418" t="n">
+        <v>20260603</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -23248,10 +23074,8 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A419" t="n">
+        <v>20260602</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -23302,10 +23126,8 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A420" t="n">
+        <v>20260602</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -23359,10 +23181,8 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>20260530</t>
-        </is>
+      <c r="A421" t="n">
+        <v>20260530</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -23414,10 +23234,8 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>20260528</t>
-        </is>
+      <c r="A422" t="n">
+        <v>20260528</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -23470,10 +23288,8 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>20260409</t>
-        </is>
+      <c r="A423" t="n">
+        <v>20260409</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -23526,10 +23342,8 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A424" t="n">
+        <v>20260515</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -23580,10 +23394,8 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A425" t="n">
+        <v>20260601</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -23635,10 +23447,8 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A426" t="n">
+        <v>20260601</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -23692,10 +23502,8 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A427" t="n">
+        <v>20260604</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -23746,10 +23554,8 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A428" t="n">
+        <v>20260602</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -23801,10 +23607,8 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A429" t="n">
+        <v>20260602</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -23855,10 +23659,8 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>20260525</t>
-        </is>
+      <c r="A430" t="n">
+        <v>20260525</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -23914,10 +23716,8 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A431" t="n">
+        <v>20260601</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -23969,10 +23769,8 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A432" t="n">
+        <v>20260603</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -24027,10 +23825,8 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>20260427</t>
-        </is>
+      <c r="A433" t="n">
+        <v>20260427</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -24080,10 +23876,8 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>20260527</t>
-        </is>
+      <c r="A434" t="n">
+        <v>20260527</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -24137,10 +23931,8 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>20260505</t>
-        </is>
+      <c r="A435" t="n">
+        <v>20260505</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -24193,10 +23985,8 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A436" t="n">
+        <v>20260601</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -24249,10 +24039,8 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A437" t="n">
+        <v>20260603</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -24306,10 +24094,8 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>20260602</t>
-        </is>
+      <c r="A438" t="n">
+        <v>20260602</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -24360,10 +24146,8 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>20260603</t>
-        </is>
+      <c r="A439" t="n">
+        <v>20260603</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -24413,10 +24197,8 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>20260311</t>
-        </is>
+      <c r="A440" t="n">
+        <v>20260311</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -24468,10 +24250,8 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>20260601</t>
-        </is>
+      <c r="A441" t="n">
+        <v>20260601</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -24518,6 +24298,6095 @@
       <c r="J441" t="inlineStr">
         <is>
           <t>https://www.104.com.tw/job/8p2a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>20260614</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>品管工務助理(水上牛稠埔工務所)（無相關工作經驗可）</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>陸福營造有限公司</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>嘉義縣中埔鄉 中庄工務所（忠和國小附近）</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>月薪 33,000 ~ 42,000元</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>高中職以下、高中職</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+| 工作說明|
+1. 協助品管人員現場查驗.查驗表單製作.實驗室會驗。
+2. 配合工程預算，製作發包標單及圖說整理。
+3. 協助丈量尺寸，繪圖，核對圖面資料，並負責圖檔管理。
+4. 負責各項行政庶務工作（如：合約製作、檔案管理、報價、請款與預算</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91zqn</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>React前端工程師</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>樂菓資訊有限公司</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>台中市西區 臺灣大道二段2號6樓之5</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>師合作還原設計稿；與後端工程師協作進行 API 串接與資料整合。
+4.架構與元件維護：撰寫高可重用性的 Custom Hooks 與元件，維護並提升前端代碼品質。
+[必要條件]
+- 核心技術：熟練 TypeScript / JavaScript</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8r9vf</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市萬華區 </t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>【職務需求】
+1. 以 Data Engineering 為主，包含 hands-on data pipeline、ETL、data modeling、以及上游系統整合經驗。
+2. 需具備資料整合、資料品質與資料模型設計能力。
+3. 熟悉</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Regional Data Engineer 數據工程師(台北工作)</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>香港商麥迪康亞太有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路1段163號4樓之3(市府站1號出口)</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>1.設計、開發和維護可擴展的數據管道和ETL流程。
+2.與數據科學家、分析師和利益相關者合作，了解數據需求並提供解決方案。
+3.優化和改進現有數據系統，以提高性能和可靠性。
+4.實施數據質量檢查，確保各類數據源的數據完整性。
+5.開發和維護數據工程</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8m4mk</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>核桃運算股份有限公司</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路一段9號4樓</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備 3-5 年經驗的資料工程師，加入我們的數據團隊。您將負責設計、構建並優化高效率的 Data Pipeline，確保資料從來源端到分析端的準確性與即時性。 此職位不僅需要強大的 Python 與 ETL 開發能力，更需要您對</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8waxf</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師 (台中)</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>微碧愛普科技有限公司</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道二段659號8樓</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>需此職位與產品團隊和前後端工程團隊緊密合作，負責資料基礎建設的穩定性與資料品質，並推動新一代 AI 資料應用的落地。
+【工作內容】
+1. Data Infrastructure 建置與維護：負責 Airflow 的部署、調優與日常維護，確保排程</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xujh</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>資料工程師/爬蟲工程師</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>貝伯盈智慧運營有限公司</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>台中市南區 福順里平順街200號1樓</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>月薪 32,000 ~ 38,000元</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 輪換策略(住宅代理、動態 IP 池)
+4. 設計資料清洗與格式標準化 pipeline，將原始資料結構化後寫入 OpenSearch
+5. 監控爬蟲健康狀態，快速處理因各平台改版導致的失效問題
+6. 與 NLP 工程師協作，確認資料欄位結構滿足後續</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92ier</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資深資料工程師(Python)</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>宇利峯有限公司</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>台中市西屯區 市政路386號</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>職位概要:
+我們正在尋找一位專精於資料整理和Python開發的Python資料工程師，主要負責資料的清洗、標準化和品質控制工作。
+1. 數據清洗和標準化:
+- 處理原始資料，識別和處理異常值。
+- 統一資料格式和編碼標準。
+- 補齊缺失值和修正</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>RD-數據工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>順立智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>台北市內湖區 內湖路一段360巷8號7樓</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>板（命名、開發流程、文件）
+【Must Have】
+－2+ 年資料工程/資料管線相關經驗
+－熟悉 SQL + Python
+－熟悉任一資料倉儲
+－有資料品質/監控/回溯經驗
+－具產品數據概念</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7njt5</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>20260531</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>文境資科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>專門設計相關業</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師
+1.資料稽核(Data Auditing)、收集(Data Collection)、整合作業(Data Integration) 等資料分析前處理作業
+2.有MS SQL server、SSIS、SSRS</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7g1tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>【台北 / 彈性遠端】Sr. Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>布魯斯人事顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中正區 </t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>月薪 1,400,000元以上</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1. 負責大規模資料的雲端基礎架構設計與演進，涵蓋資料流、整合處理、儲存分析與事件偵測等核心能力。
+2. 與相關團隊協作，提出並實作資料架構的優化與轉移計畫，打造具高可用性、可擴展性與韌性的基礎設施。
+3. 兼顧業務成長與工程實作</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wrnj</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>數解人意科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路三段 195 號 7 樓</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>【 資料工程師 ( Data Engineer) 】
+在 QSearch，數據是我們最核心的資產。此角色的核心目標是建構公司大數據生態系的「源頭引擎」。您將負責設計、開發與維運可擴展的高速分散式爬蟲系統，與各平台反爬蟲機制正面對決，並優化高併發</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92847</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>圖靈數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>台北市中正區 中山北路一段2號11樓</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>行銷判讀，運營，轉化方面的戰略支持與技術方法。成員大多是技術工程師組成，協助客戶收集有用的數據，了解數據，利用數據。
+目前是 Google Marketing Platform、Mixpanel、AB Tasty 認證合作夥伴。
+公司福利：
+・</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7v0e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>20260415</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>數據工程師(Data Engineer) - Python/ETL/MongoDB</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>果友科技有限公司</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段333號</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備後端架構思維的「數據工程師」，能與企業客戶的數據分析、工程團隊協作，打造穩定且可擴展的數據處理流程。
+這份職缺主要任務是設計並維運高可靠性的 ETL 與 Airflow 數據流程，確保資料能自動化運行、正確轉換，成為企業決策與</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8urkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>侍達遊戲藝術有限公司</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>台北市信義區 東興路41號5樓</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>1. 根據分析需求進行資料建模，並提供視覺化的資料呈現。
+2. 提供分析數據及報表。
+3. 設計與開發資料分析所需要的工具。
+[能力需求]
+1. 具備程式開發經驗 (Python/Golang等)。
+2. 具備 SQL/NoSQL 使用經驗</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85yiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Position Impact：
+資料工程師的核心價值在於設計、建置並維護整體的數據解決方案，確保全公司的數據具備高可用性、可靠性及可擴充性。在此職位中，您將處理大規模數據庫，主動識別潛在風險，並開發能提升數據效能與品質的解決方案。您將與後端工程師</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ti6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>數據工程師 / Data Engineer (Data Infrastructure)</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>富華創新股份有限公司台中分公司</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>建築及工程技術服務業</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>台中市北屯區 太原路三段1315號</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士、博士</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>協助各業務單位理解數據價值，推動企業從「經驗法則」逐步邁向「數據驅動」的決策模式。
+▍我們期待你具備
+・3 年以上資料工程、後端開發或資料庫管理經驗，精通 SQL 與 Python。
+・熟悉 GCP 雲端數據與 AI 生態系：具備</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zban</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>久浪智醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 新竹縣竹北市生醫路2段150號</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 生醫與影像數據統計分析
+2. 數據庫建立與維護
+3. AI/ML 模型建立
+4. 自動化及優化工作及數據流程
+5. 具備AI Agent &amp; MCP protocol專案經驗
+</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8idjr</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>旺旺中時媒體集團_(CT) Data Engineer（資料工程師）</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>旺旺中時媒體集團_工商財經數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>電視業</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>台北市萬華區 艋舺大道303號</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>本職位為Data Engineer（資料工程師）
+（依資歷可掛 Senior Data Engineer）
+工作內容 :
+● 設計與實作跨平台資料收集流程（API 與後台匯出並行）
+● 串接並維運以下類型資料來源（依實際情況）：
+YouTube</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wttd</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>徵  數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>臺北醫學大學</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用之</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xi1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>20260613</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>數據工程師 data engineer</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>台灣創博識有限公司</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>台北市中正區 南海路1號13樓</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>data governance, data quality, MLOps
+4. 優化開發者體驗，解決資料科學家開發與部署會遇到的問題
+資料工程師在數位轉型的浪潮下扮演重要的角色，本職位將有機會參與公司數位轉型計畫，並協助建立可靠的數據基礎架構，提供客</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wl9k</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>英屬維京群島商嘉碼科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>台中市西屯區 工業三十八路210號3樓之6</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位數據工程師，不僅具備扎實的技術底子，更擁有主動積極、樂於挑戰的特質。
+加入我們後，您將在這個充滿活力、尊重多元的環境中扮演關鍵角色，透過打造穩健的數據基礎與管道，協助團隊從資料中萃取價值、加速產品與業務的創新。
+如果您對資料領域充</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vvrv</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>監造工程師</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>城域建築師事務所</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>建築設計業</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>高雄市左營區 自由三路266-1號</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 48,000元</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+5. 預先檢查分包廠商施工前之準備工作。
+6. 確實填寫監工日報表，以留下詳實工程進行的記錄資料。
+7. 進行進場材料品質之點收、存放、使用查驗及結算。
+8. 依據施工狀況向分包廠商協商提出各項建議。
+9. 視狀況採取各項措施，以因應分包廠商之不</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91dru</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>20260614</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>乙級職業安全衛生管理人員</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>承鉌營造工程有限公司</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>土木工程業</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台中市烏日區 </t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>1. 熟悉土木工程相關法規及施工規範，負責監督建築工地現場安全規定執行情形。
+2. 熟悉工地安全管理，執行現場風險評估及安全計劃制定。
+3. 具備工程圖紙閱讀與解釋能力，並協助執行現場勘察與數據收集。
+4. 使用AutoCAD進行工地設計圖修改與</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8sibo</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>太陽能量測/資料分析工程師(竹北)</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>艾思特能源股份有限公司</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>精密儀器相關製造業</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新竹縣竹北市 </t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>1. 協助執行太陽能電站之現場檢測與量測作業(台灣及東南亞地區)
+2. 蒐集並整理現場檢測資料，撰寫相關測試與檢測紀錄
+3. 進行數據分析與報告撰寫，需熟悉 Word 文件排版 與 Excel 樞紐分析
+4. 協助撰寫及優化 檢測SOP 與 測試</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8uri5</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>云智資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市松山區 </t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>1.具有資料分析經驗1年以上
+2.資料庫語法開發2年以上經驗並熟悉SQL（MS Sql 尤佳）
+3.ETL 開發經驗1年以上（Trinity ETL尤佳）</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7ihuk</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>20260530</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>臺北市立萬芳醫院-委託臺北醫學大學辦理</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>醫院</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>月薪 43,700 ~ 45,900元</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。 
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8z3ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>聯樂數位行銷股份有限公司</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段285號4樓</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1. 負責資料的雲端基礎架構設計與演進，涵蓋資料流、整合處理、監控狀態等。
+2. 開發和串接API，提供穩定、可重複使用的資料服務。。
+3. 兼顧業務成長與工程實作需求，將資料相關能力平台化，提供穩定、可重複使用的基礎服務。
+4.</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92g11</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>行銷部-數據工程師 ( Data Engineer )</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>全聯福利中心_全聯實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>量販流通相關業</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>台北市中山區 敬業四路33號</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>動力，能適應快速變化的技術環境，持續精進技能 
+4. 勇於挑戰創新 - 保持開放心態，不設限自己的發展，樂於嘗試新技術與跨領域合作
+數據工程師的核心挑戰與工作內容：
+1. 數據處理與自動化 — 了解與整合異質數據來源（API、資料庫、CSV、</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7xcgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>果實夥伴股份有限公司</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路610號2樓</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>【工作內容 】
+-  ETL 之開發、處理(資料清理、儲存、分析)與監測
+- 開發與設計專案所需 API 服務並與後端工程師合作，完成系統產品化程序
+- 依據不同業務需求，完成建置/維運/更新各式 Data infra 的需求
+- 與數據產品管理</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7dpwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>資料工程師 (電商專案)</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>碩誠國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路170號14樓D室</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+3.跨部門協作: 訪談需求單位，配合業務目標，應用AI智能模型與數據技術規劃落地於業務場景之方案。
+4.數據處理與特徵工程: 從零開始進行數據清洗、特徵工程及分析，確保數據質量與模型效能最佳化。
+5.資料建模分析: 透過訓練機器學習模型及數據分析，</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/915ue</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Tableau資料工程師</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>緯德科技股份有限公司 (TechLink Corporation)</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號8F-13</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>- 熟悉數據分析和Tableau報表開發實務經驗1年以上。
+- 熟悉資料庫安裝、設定及操作實務經驗1年以上。(Oracle、MS SQL Server、MySQL至少一種)
+- 可獨立或與團隊合作，工作態度積極、負責，能配合公司規定。
+- 依不同</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師(錦州街)</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>山富國際旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>台北市中山區 錦州街46號10樓</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>月薪 48,000元以上</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">與效能調校。
+與後端工程師協作，確保數據收集與儲存的效率與規範。
+探索並導入新興的數據技術與工具，持續提升團隊的數據處理能力。
+</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/73ifb</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>產品三部 | 資料工程師(高雄)</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>騰雲科技服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中華四路45號2樓</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>✅ 工作內容｜你會負責的任務
+1.數據建模：負責設計與維護 MDP 平台的資料模型，確保能有效支撐財務、銷售、行為等多維度主題數據。
+2.ETL 流程開發：配合使用 ETL 工具，撰寫高效能的 T-SQL 邏輯進行數據清洗、轉換與載入。
+3.效能</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xvzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>資料工程師 || 資料倉儲 × ETL流程建置</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>三陽工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>汽車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>新竹縣湖口鄉 中華路3號</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>月薪 38,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>將參與公司資料平台與資料倉儲建置，
+從資料蒐集、整合到ETL流程設計，
+逐步建立穩定且可持續運作的資料流架構。
+透過內外部資料匯集與整理，
+包含 API、Excel、爬蟲及非結構化資料處理，
+讓分散資訊能有效串接、清理與整合，提升資料可用性與品</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91fva</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>立視科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>多媒體傳播相關業</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>台北市松山區 八德路四段760號6樓</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位熱情且富有才華的資料工程師，加入我們的團隊，協助解決廣告投遞的資料內容。在這裡有大量的數據供你發揮所長，將學過的知識及方法應用到實務的工作上。
+我們希望你具備以下三大特質：
+對資料工程領域有強烈興趣和熱情 。
+重視團隊合作，具備</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zz6u</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>【台北】數據工程師Data Engineer — "Data Infrastructure Architect"</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>創智動能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>台北市中正區 八德路1段23號9樓</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>至數據倉儲或資料湖。 
+   確保數據準確性與一致性，並優化數據處理效能。
+Data Transformation and Integration
+Design and implement data transformation processes</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8kgsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>量化投資金融大數據工程師</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>沛然資訊有限公司</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街150號7樓</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>年薪 800,000 ~ 1,500,000元</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>控與跨市場操作等關鍵場景中。我們開發可用於決策的高互動行動應用，誠摯邀請對產品品質與金融邏輯有熱情的夥伴加入我們的團隊。
+【工作內容】
+1. 台清交成資工系學碩士優先。
+2. 優秀IT科技理工且對量化投資有興趣者。
+3. 量化交易相關資料庫的維運</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7mnu3</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>AI資料工程師</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>力新國際科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>台北市內湖區 新湖一路128巷15號6樓</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> schema設計、KG-RAG整合。
+七、設計多租戶資料隔離（Multi-tenant Collection/ Namespace），防止跨租戶資料污染。
+八、實作增量同步機制：文件變更偵測、CDC、增量索引，避免每次全量重建。
+九、建構Data</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/9188l</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>AI醫療資料工程師（Medical AI Data Engineer）</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>杏創生物科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>藥品／化妝品及清潔用品零售業</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>台北市中山區 新生北路一段66號4樓</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>月薪 48,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+工作內容
+1. 協助整理細胞檢測資料與臨床資料
+2. 建立細胞檢測資料庫與管理系統
+3. 協助將Flow Cytometry數據自動化匯入系統
+4. 協助建立AI細胞檢測知識庫
+5. 串接AI工具，協助自動產生檢測報告
+6. 協助開發醫療數據</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/88ifz</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>可樂旅遊旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段90號12樓</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>資料運用並創造商業價值，並積極探索 AI 技術，提升整體營運效率與決策品質。
+【工作內容】
+1. 設計、開發與維護數據流程，打造穩定且高效的數據基礎架構
+2. 使用 Python 進行數據清理、轉換與處理
+3. 將數據處理流程自動化，並協助部署至雲</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/853np</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>AI數據工程師</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>建準電機工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>專用生產機械製造修配業</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中正一路120號12樓(近捷運-苓雅運動園區站)</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>1. 建立、維護與優化企業數據中台，整合內部各系統資料，確保資料一致性與可用性。
+2. 設計 ETL 流程與資料庫架構，提供 AI 模型與報表系統所需資料。
+3. 監控資料質量，定期進行資料清洗與效能優化，確保數據中台穩定運作。
+4. 報表開發</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xjwv</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>20260415</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>數據工程師(Data Engineer) - Python/API開發/ETL</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>果友科技有限公司</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備後端思維的數據工程師，打造數據產品與並與分析客戶團隊合作，建置高品質的數據供應與自動化環境。
+你的主要任務是確保數據能穩定流動、被正確處理與自動化運作，成為支撐企業決策與AI應用的堅實基礎。
+【工作內容】
+1. 設計、開發與</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8thk7</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>科技金融_資料工程師</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>中國信託商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>台北市南港區 經貿二路168號 (中國信託總部)</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>1. 負責需求分析與流程規劃，洞察潛在關鍵應用或數據，並運用內外部數據進行前期探索分析及策略建議。
+2. 負責梳理並規劃機器學習研發資料庫架構，建立數據品質流程管理與維護計畫，掌握數據產品策略及生命週期。
+3. 能將數據應用產品轉化為需求文件、系</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/73am4</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>監造工程師</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>力匠工程顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>建築及工程技術服務業</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>高雄市三民區 大昌一路303-1號2樓</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>月薪 45,000元以上</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>工程施工監造及表報作業。
+年薪14~15月
+配置專用監造外出四輪傳動車一部</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/2tkf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>20260614</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>現場工安/助理</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>千祥科技工程有限公司</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>空調水機電工程業</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>新竹縣寶山鄉 三峰路二段433巷11-26號</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>1. 執行現場安全檢查及記錄維護。
+2. 執行公司內、外部安全衛生業務。
+3. 處理突發之勞工安全相關事宜。
+4. 執行安全衛生教育訓練。
+5.負責工地勞安查核、職災害預防及改善。
+6.其他行政事項(工程師彙整文件、整理相關資料、物料管理)及主管</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8lk1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>【台中】資料工程師</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>敦謙國際智能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>台中市西區 國泰金融大樓(台中市西區英才路 530 號) 24 樓</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 90,000元</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>職務工作內容：
+營運策略系統 (RMS)
+透過資料分析、資料探勘和數據處理技術，為旅宿提供精準的營運決策依據。
+建模預測，根據歷史銷售資料，建立銷售量、住宿率等預測模型，為旅宿決策的制定提供參考。
+協助開發專為旅宿設計的智能客服機器人。
+職務需</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/75oc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>資料工程師 ETL / Data Engineer | 半導體 | 工作地點: 新北市</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Tezerakt_美商立方體有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新北市板橋區 </t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>[請提供英文簡歷]
+[本職缺] 
+為 Data Infrastructure Support Engineer(資料工程)，主要負責半導體製造產業 ／雲端資料基礎建設的功能開發與強化。工作範疇包含新data pipeline 的 parsing</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yq4u</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>數據工程師(電商專案)</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>碩誠國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路170號14樓D室</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>我們正在尋找對數據、AI 應用充滿熱情的夥伴，與我們一起挑戰應用技術極限、共同學習成長，並將數據價值轉化為實際影響商業影響力！ 如果你願意接受快速回應開發調整的數據工作，同時讓你的數據能力能落地，歡迎加入我們！
+數據工程師的核心挑戰與工作內容：</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/915u7</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>ETL 資料工程師/大數據工程師</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>歐立威科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>台北市大同區 鄭州路87號11樓之1</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Pentaho PDI、Talend、Informatica、Microsoft SSIS 等）進行數據抽取、轉換與載入，確保資料正確性與完整性。
+3.熟悉 Python 或 Java 等程式語言，能撰寫 ETL 腳本與自動化流程。
+4.設計並維護 Data</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ugrj</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>20260512</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>東海大學智慧永續循環經濟研究中心誠徵資料工程師</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>東海大學</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>其他教育服務業</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道四段1727號</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具環境工程背景、能將專業知識轉化為結構化資料與知識模型的人才，加入智慧永續循環研究中心，共同建構以環工知識為核心的 AI 與知識圖譜系統。
+本職位的核心任務不是單純做資料清洗或模型訓練，而是：
+把環境工程的「機制、概念與流程」</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y8zy</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>GIS資料工程師</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>九福科技顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>台北市大同區 重慶北路二段48號2</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>1.具備熟悉QGIS、ArcGIS、影像分析及資料分析處理能力
+2.有資料庫與SQL語句應用經驗者優先錄取
+3.數據處理能力、Python、資料搜集、彙整、分析能力、文件撰寫能力者佳
+4.檢核、搜集、彙整、分析比對資料，GIS圖資處理及製程文件彙</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78nq1</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>永慶房產集團_永慶房屋仲介股份有限公司</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段77號12樓</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>永慶房產集團為房仲產業龍頭，用科技創新引領創新變革，歡迎IT領域的優秀夥伴加入!
+工作內容如下：
+1.規劃集團資料流程，達成資料整合綜效。
+2.建置企業數據中台，管控集團資料倉儲品質與正確性。
+3.與資料分析師協同合作，進行資料分析前處理，提供</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78pf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>重高科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段162號12樓之2</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Technical Skills)--
+我們希望候選人在以下多數領域具備實作經驗：
+1. Python：精通 Python，特別是在資料工程與自動化流程的應用（而不僅僅是撰寫簡單腳本或 ML 模型）。
+2. SQL：專家級別，具備 BigQuery 或類似雲端資料</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvez</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>【擴編】資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>聖文森商瑞德克斯科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>台中市西屯區 朝富路213號19樓</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+※ 工作專業需求：
+1. 具資料視覺化工具（Tableau / PowerBI / Metabase）經驗</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xdrn</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>【研究發展處】Big Data Engineer 資料工程師 / Senior Big Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>現觀科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段42號2樓</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Dashboard Visualization，並與產品開發團隊進行資料探勘及研究。
+[工作內容]
+1.開發大數據系統資料處理平台
+2.串流資料平行處理程序開發,熟悉分散式運算,平行運算
+3.解決大量資料處理時所衍生的效能,擴充與維護維運資料庫</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7bdqr</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>成強科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>新北市林口區 仁愛路二段502號1808A</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>月薪 32,000 ~ 40,000元</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>公司目前正著手跨領域製作新型遊戲  (運動相關)，
+詳見官網:https://jacfit.com.tw/
+主要工作內容:
+1.對現有資料分析算法進行維護。
+2.與研發團隊針對設備軟體數據資料，進行採集及分析。
+3.根據產品開發要求，與團隊協作</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8e1v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>資深資料工程師｜Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>街口電子支付股份有限公司</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號8樓(C棟)</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>◆THE ROLE &amp; THE TEAM 
+As a Data Engineer in JKOPay, you will be responsible for processing JKOPay’s online transaction data and offline data analysis with your experience in data engineering. JKOPay serves +6 million users in Taiwan, as well as partners and stakeholders that integrate with our payment service, which handles 3-billion transaction amounts every month. 
+With the rapid growth of JKOPay’s business, Data Engineer is the key to designing systems for collecting, storing, and analyzing data at scale, as well as convert raw data into usable information for business analysis to interpret. 
+This is an opportunity to help shape and expand JKOPay’s ETL data pipeline. If you are interested in handling multiple-terabyte data and improving engineering efficiency, in a great team that keeps growing, this role is for you. 
+◆WHY YOU SHOULD BE INTERESTED 
+-Translate business requirements &amp; end to end designs into technical implementations and responsible for building batch data warehouse. 
+-Manage data modeling design, writing, and optimizing ETL jobs. 
+-Collaborate with the business team to build data metrics and data visualization based on data warehouse. 
+-Responsible for building and maintaining data products. 
+-Involvement in rollouts, upgrades, implementation, and release of data system changes as required for streamlining of internal practices. 
+◆WE'D LOVE TO MEET YOU IF 
+-At least 2 years of relevant experience in data engineering. 
+-Proficient in creating and maintaining complex ETL pipeline end-toend while maintaining high reliability and security.
+-Familiar with backend engineering and practical knowledge of shell, SQL, and one more programming language (e.g. Python, Scala, etc.). 
+-Familiar with the common distributed computing engine or platform (e.g. ClickHouse, Spark, Kafka, BigQuery, Airflow, etc). 
+-Familiar with at least 1 data exploration and visualization platform (e.g. Superset, Tableau). 
+-Familiar with data lake, data warehouse, and data mart concept, and have production experience in modeling design. 
+-Familiar with at least 1 Cloud data flow solution (e.g. AWS Data Pipelines, GCP Dataflow, etc.) is a plus. 
+-Experience with Data Catalog is a plus. 
+-Excellent interpersonal and communication skills with the ability to engage and managing internal and external stakeholders across all levels of seniority.</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7jw2n</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>20260409</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>遊戲資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>吉恩立數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段106號5樓</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>我們找的就是你：善於溝通、邏輯清晰及執行力的工程師 !
+負責一款遊戲，
+從資料庫初期的建置發佈以及遊戲整體環境建置，到後續服務的長久運行管理。
+在這裡你不會感到孤單，會有同仁一起參與合作與營運，當然，熟悉後也有需要獨自運作的時刻。
+【工作任務</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tymj</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據應用工程師) – (數數發中心, DDT)_I00020717</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+* 目標成果導向：重視成果並具合作互助精神
+* 積極主動、持續進步：樂於學習與自我成長
+* 熱愛數據、對技術充滿熱忱：積極探索與應用新技術
+【工作內容】
+資料工程的世界千變萬化，以下是你的任務指南：
+1. 數據蒐集與處理，接觸各種資料來源，進行</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n8v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>【國泰投信】資料工程師 Data Engineer_I00022210</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>國泰證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號6樓</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Kubernetes）。
+5. 實現湖倉一體（Lakehouse）與存算分離架構。
+【必要條件】
+1. 1 年以上資料工程或資料分析經驗，具備資料處理或資料分析的程式開發能力。
+2. 具備 Python 軟體開發或資料處理經驗。
+3. 具備 Linux 系</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qbni</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>資訊部-應用系統課-工程師/資深工程師(Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>華立捷科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 台元街30號3樓之3</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>【讓數據驅動決策的核心角色】
+你將從資料整合與平台開發出發，串聯各部門系統與資料流，讓資訊能即時反映在業務與產線決策中。
+這不只是資料工程，而是打造整個組織「資料大腦」的關鍵工作。
+適合希望累積資料平台實務經驗，並參與企業決策支援的工程師。
+1</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7vbwa</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>[台北]資料工程師實習生（AI &amp; BI）</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>台灣新蛋股份有限公司</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路513巷31號10樓</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>月薪 24,000元以上</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+    •  對數據分析、BI 或資料工程有興趣
+    •  願意學習新技術，具備良好邏輯思考能力
+【加分項】
+    • 有簡單資料分析 / BI / ETL project 經驗（課程或 side project 皆可）
+    • 有使用</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90be7</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>資深資料工程師 Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>宏碁資訊服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市南港區 </t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>【職務說明】
+我們正在尋找具備企業級 Data Engineering 與 BI Solution 經驗的 Senior Data Engineer，協助企業客戶建構可維運、可擴充、可分析的資料平台與數據應用架構
+此角色將參與企業資料平台、</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y1vy</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>評鑑組專任計畫助理(資料工程師)</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>東吳大學</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>台北市士林區 臨溪路70號</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>月薪 36,300 ~ 41,500元</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.校務資料庫定期更新、維護與管理。
+2. 協助校務研究專案申請、資料分析與成果彙整。
+3. 協助辦理校務研究計畫與專案申請。
+4. 中心相關活動辦理及行政支援。
+5. 其他主管交辦事項。	</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92136</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>【外商】[RC-Data] Data Engineer / 資料工程師</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路捷運中山站六號出口共構大樓</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>【職位亮點】
+1. 數據規模化：處理全球跨時區、千萬級日活躍用戶產生的金融級即時交易數據流。
+2. 技術主權：參與從 0 到 1 的架構重構與技術選型，我們鼓勵工程師定義數據標準。
+3. 前沿技術棧：深度實踐三層式資料湖架構（Medallion</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wyu9</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>20260614</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>工務工程師</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>普生地室內裝修工程有限公司</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>建物裝修及裝潢業</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高雄市楠梓區 </t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>的重要溝通橋樑，讓資訊傳遞更有效率。
+3. 管理工程材料與現場資源
+• 協助材料進場安排、數量核對與現場管理。
+• 支援工程估價、發包詢價與相關資料整理。
+4. 建立更高效率的工程流程
+• 協助整理工程紀錄、施工照片與驗收資料。
+• 我們也期待你能</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ll8u</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>20260424</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>技術工程類 - 廠務工程師－新建廠工程（擴廠/系統設計/審圖）【高雄】</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>日月光半導體製造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>半導體製造業</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>高雄市楠梓區 經三路26號</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>月薪 38,000元以上</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>電、空調、水務等系統之設計資料檢視、審圖及規格確認。
+協助工程發包、施工管理、監造、驗收及系統移轉。
+進行工程進度、品質、成本及風險控管。
+建立與維護系統設計規範、技術文件及標準流程。
+導入新技術、新設備或節能方案，支援廠務系統升級。
+與內部單位、</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ji9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>(C6) 資深數據工程師Senior Data Engineer（內湖）</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>【職位說明】
+參與智慧城市 AI 賦能產品開發，負責建置企業級數據平台(Data as a Service, DaaS)，處理各種形式的資料，並進行完善的資料治理、血緣追蹤與監控。最終將整合生成式 AI（Generative AI）功能，提供智慧</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p0av</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>資料工程師/後端工程師</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>銓鍇國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>新北市中和區 中正路700號五樓</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>1. 開發和優化數據處理流程: 使用 Python 和 Apache Spark 進行數據清洗、轉換和建模，提升處理大規模數據集的效率。
+2. 設計和維護與優化data pipelines。
+3. 管理和維護 MongoDB 和 Data Lake。
+4. 分析，挖掘和解釋數據含義。
+5. 協助編寫技術開發相關文件。</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8e74p</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>科技部_Data Engineer 數據工程師 (Data &amp; AI Product)</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>美好證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路三段２號4樓</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>】
+我們正在打造新一代的 DATA/AI 智能化運轉體系，以先進的數據工程、資料平台與 AI 技術，推動投資研究、產品創新與顧問服務的核心能力全面升級。
+此角色將負責設計、建置與維運公司的核心數據基礎設施 (Data &amp; AI Platform)</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7b6bq</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>AI 應用工程師</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>鶴卜製研股份有限公司</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 縣政二路187號2樓</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>職缺名稱: 
+AI 應用工程師 
+工作內容:
+1. 開發與維護 MCP（Model Context Protocol）伺服器，串接 Claude／LLM 與內外部工具、資料源。
+2. 串接各類 LLM／GenAI API（Anthropic</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92naq</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Data Engineer (Mid Level)  資料工程師（中階）</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>極酷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路2段26號2樓</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> optimize scalable data infrastructure.
+此角色將支援公司整體資料工程專案，包括 BigQuery 數據倉儲優化、事件追蹤品質與資料管線建置。
+ This role will support company-wide</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvll</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>115年-資料工程師-(資深專員／專員) - 行政管理部／資訊組</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>國家住宅及都市更新中心</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路一段21號</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>上線與後續維護
+•與廠商合作進行各業務系統平台資料整合與介接
+【必要條件】
+•三年以上資料工程相關工作經驗，具備獨立完成資料工程項目的能力
+•精通 Python 程式語言，具備良好的程式設計能力與程式碼品質意識，熟悉常用的資料處理函式庫
+•熟悉</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/918a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據架構工程師) – (數數發中心, DDT)</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>【關於我們】
+我們是國泰產險的資料科學（DS）團隊，使命在於持續進化數據應用，創造並釋放數據價值。目前正在藉由數據上雲、數據治理與 AI 技術應用，推動由底層架構到業務應用的全端數據生態建構與 AI 轉型準備。
+我們尋找認同以下團隊文化的夥伴：</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8opms</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>三竹資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>台北市中山區 新生北路二段39號11F</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Airflow 排程管理經驗、DB 帳號權限控管經驗，或有處理高併發金融資料流之經驗。
+職務內容：
+1. 本職務屬於產品任務，配合研發團隊發展金融科技應用之日常資料工程，並負責穩定性維護與效能優化。
+2. 參與設計高可靠性（High</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mtc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>軟體產品工程師</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>永聚資科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>新北市板橋區 四川路2段16巷10號1樓</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+‧ 寫過 RESTful API、處理過實際業務邏輯
+‧ 看過、用過、改過別人的程式碼（不是只會寫新東西）
+‧ 重視程式碼品質：會寫測試、會 review、會重構
+‧ 對「打造產品」有熱情，不只想當外包工程師
+公司會提供的支援】
+‧ 每月 1,</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qb3t</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>20260125</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1.在Hadoop架構的資料倉儲(Data Warehouse)上建立具備擴充性與高可靠性的資料產品，為數據科學家與業務團隊提供穩健的資料基礎。
+2.與數據科學家和業務分析團隊合作，理解需求並提供適用的資料解決方案。
+3.設計並構建</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n58n</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>英屬開曼群島商萬里雲互聯股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段333號33樓</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>【職務說明】
+       我們正在尋找一位具備高度專業技能的資深資料工程師，加入我們快速成長的資料與AI解決方案團隊。此角色將負責設計並交付可擴展的資料平台、建置資料管道，並推動雲端/地端環境下的資料搬遷，以銜接AI分析應用落地。</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p7ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>製程資料工程師</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>聯亞光電工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>台南市善化區 西善一路9號</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>1、了解產線流程，協助將製程與生產資料系統化
+2、規劃並建置製造相關資料庫，確保資料可追溯、可查詢
+3、開發或維護內部系統，降低人工紀錄與 Excel 作業
+4、建立基本報表與視覺化畫面，呈現產線狀態與歷史趨勢
+5、與製程、工程、設備單位合作，支</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x7cl</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>AI工程師</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>汎海科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>新北市三重區 光復路一段61巷27號9樓之3</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Python 後端工程師 / 技術合夥人（SaaS 平台）
+我們不是找員工，而是找一起打造產業平台的夥伴。
+SaaS 後端架構設計
+設計 Multi-tenant 架構
+API 設計與版本控管
+JWT 認證與權限系統
+製程邏輯設計
+可擴充架構規劃</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8molp</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>大江生醫股份有限公司(TCI CO., Ltd)</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>台北市內湖區 港墘路187號8樓</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Lake。
+．   與資料科學團隊合作，提供模型所需的資料集與特徵工程支援（如 LightGBM、XGBoost）。
+．   透過Power BI進行資料串接與報表資料結構設計，確保分析資料即時、準確。
+．   撰寫技術文件，維護資料流程運作紀錄</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/69p6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>D02-資料工程師(DE)_旅遊科技部_數據營運組</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>雄獅資訊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路151號</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>生產效率與可靠性。
+我們期待一位具備深厚工程能力、能主導平台設計並推動技術標準的資料工程師，設計穩定、高效能、可擴展的資料基礎設施，讓分析師與資料科學家能在正確、可信的資料之上快速產出洞察與 AI 應用，打造資料平台的技術基石：
+•	設計並建置可擴</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ppdw</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>眾匯智能健康股份有限公司</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>其他醫療保健服務業</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>台北市南港區 三重路19-13號E棟5樓(南港軟體園區)</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>數位健康產業是台灣的另一座護國神山，歡迎有志於探索數位健康創新事業模式發展之夥伴，加入我們的團隊!
+1.健康數據庫之清理、彙整及運用管理
+2.參與開發【AI分身健康管理】服務
+3.支援營運團隊各種AI專案之數據運用
+4.協助管理階層決策所需數據分析運用
+5.其他AI或數據技術創新服務開發</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5wvxj</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>20260428</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>AI 全端工程師(豐原、中壢)</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>吉翔樂_旻新科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>資料儲存媒體製造及複製業</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">桃園市蘆竹區 </t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>關於我們
+我們是賽鴿產業的科技創新者，專注於開發 GPS 即時追蹤系統與數據分析平台。隨著 AI 技術快速發展，我們正積極將 AI Agent 導入產品與內部流程，尋找能夠擁抱這波浪潮、用新方法解決問題的工程師加入團隊。
+職位概述
+我們正在尋找</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wo3z</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Cloud &amp; Data Engineer 雲端與資料工程師</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>阿卡希亞股份有限公司</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>桃園市桃園區 中正路1125號7樓</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Job Summary:
+本職務 Cloud &amp; Data Engineer 將同時建構與維護雲端、資料、AI 與資安相關系統的設計與交付，協同技術團隊成員提供系統整合（System Integrator, SI）服務，服務跨國企業集團或上市櫃客</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yz82</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>20260407</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>資料工程師-情報系統二team【全家便利商店關係企業】</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>精藤股份有限公司</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段61號11樓</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>護），更有完善的公司治理與開發標準，可做為所有資訊人員執行專案時的後盾。
+除此之外，精藤近年來亦不斷追求更多新領域的發展，例如：雲端科技應用、大數據資料分析以及行動裝置管理技術等等，誠摯的歡迎所有對於零售流通有興趣的伙伴一同加入精藤的大家庭。</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/84xyg</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Python 工程師</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>亞洲指標數位行銷顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路214號3樓</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>月薪 38,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Playwright）。
+本職位的核心著重於「資料處理與應用」，非常適合熟悉 Python 資料處理、並渴望進一步跨足後端開發的工程師。在 API 開發方面，團隊將由資深同仁提供完整的技術指導，協助您將扎實的資料處理能力，順利延伸至後端開發領域。誠摯歡迎對</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92090</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>20260613</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>職業安全衛生管理人員/主任</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>普生地室內裝修工程有限公司</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>建物裝修及裝潢業</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高雄市楠梓區 </t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>月薪 43,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> EHS 的專業接口： 負責一線廠區開工前的工安/資安送審資料準備，現場對接廠方環安衛（EHS）工程師，建立良好、專業的信任關係。
+2 現場危害預判與防護： 每日巡視裝修案場，精準識別動火作業、高架作業、化學品管理（油漆、有機溶劑）之風險，在違規發生前</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92oe1</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>20260614</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>弱電系統工務工程師</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>皓眾國際有限公司</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>通訊機械器材相關業</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>台南市東區 崇善一街113號</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>月薪 30,000 ~ 45,000元</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>(高架作業)
+5、現場監工、人員調派、施工協調與簡易文書紀錄。(俱業務能力者尤佳)
+6、弱電系統工程識圖及繪圖。(可學習)
+7、設備保養與維修服務。
+8、其它主管交辦事項。
+9、試用期三個月。
+10、有相關經驗者薪資可談。
+11、試用</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78mqw</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>【新擴編】Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>愛酷智能科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化南路一段2號5樓</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>步汰換舊有的 Digdag 流程。
+2. ETL/ELT 流程開發： 串接 PostgreSQL 與 MongoDB 以及外部資料 等多源數據，清洗並導入 BigQuery。
+3. 數據倉儲模型設計： 使用 dbt 開發與維護數據模型，優化 SQL</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wccg</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>網頁系統工程師</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>捷斯克科技有限公司</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>台中市西區 台灣大道二段181號12樓之3</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>月薪 36,000元以上</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>1.Laravel 後端工程師，加入我們的核心團隊負責 CRM SCM 等系統的開發與功能擴展。
+2.此職位專注於商業邏輯的實作、資料庫架構設計（SQL）與 API 串接。
+3.我們需要習慣使用 AI 工具（如 ChatGPT Claude）來輔</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8o1xt</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>【前瞻研究籌獲中心】資料工程師(台南)</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>國家資通安全研究院</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>其他專業／科學及技術業</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台南市歸仁區 </t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>1.協助概念驗證程式開發、後端服務建置及產品功能落地，支援不實資訊、網路詐騙、深偽影音等相關應用系統之開發與維運。
+2.建構高效、可擴展且穩定之後端服務，開發與串接 API、AI 模型推論服務及資料處理流程，並與前端、資料及產品團隊協作完成系統整</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8rkm9</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>P7-Python資料工程師</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>意藍資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號12樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>月薪 35,000 ~ 45,000元</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>本公司是國內搜尋及語意分析市占率最高的廠商，專注研發非結構資料之數據處理，尋找熟悉Python及物件導向設計的人才加入。工作主要為開發與維運資料產線，搜集語料、資料儲存處理，並提供API服務供下游服務使用。
+工作內容如下：
+- 資料搜集程式開發</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7csnw</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>雲端數據工程師</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>君綺生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>美容／美體業</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>台北市信義區 松智路1號</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>部門介紹:
+我們是集團組織擴編成立的新部門, 在這工作你將會體驗全雲的工作環境, 包含AWS雲端服務及工具, 在工作中學習專案管理、資料庫管理、雲端服務等技術
+工作內容
+1. 參與雲端數據架構發展規劃，設計資料處理、儲存、分析架構，以符合數據</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mcsu</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>20260409</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>數據工程師｜AI產業｜新創｜Python｜歡迎新鮮人與資深開發者</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>睿思智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>新北市板橋區 中山路2段443巷77號10樓</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 120,000元</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>最佳夥伴。未來也將持續擴展Neuro家族，讓AI應用更親民、更普及。
+如果你喜歡學習、願意動手做事，歡迎加入我們，一起努力成長，創造更多可能！
+【主要任務】
+1. 與資料科學家、雲端架構師、資料分析師及專案經理密切合作，提供高品質的雲端數據服務給</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xq4h</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>資料與物聯網基礎架構 IT 軟體工程師</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>扇港先進台灣股份有限公司</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>通訊機械器材相關業</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>新北市中和區 建八路218號9樓</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>資料與物聯網基礎架構 IT 軟體工程師
+薪資：極具競爭力的薪資 + 績效獎金
+[關於 SENKO]
+SENKO 先進元件是高性能光纖互連解決方案的全球領導者，為資料中心、5G/6G、矽光子學、量子連接和人工智慧基礎設施提供動力。我們在美國、日</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90umh</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>AIR SPACE_新地國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>鞋類／布類／服飾品批發業</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>台北市士林區 中山北路五段(近士林捷運站210公尺)</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>AIR SPACE為台灣第一女裝品牌，
+我們提供安心的工作環境、人才培育訓練課程，
+願您能成為永續經營的共同夥伴，歡迎加入AIR SPACE團隊！
+【我們在找什麼樣的你】
+熟悉資料庫、ETL 流程與數據建模，能有效整理、清理與分析大量數據，</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8fvcr</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>軟體工程師</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>奇翼醫電股份有限公司</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 文興路257號11樓</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 進行效能分析、記憶體與 CPU 優化（含多線程、SIMD、定點數實作等）、並規劃壓力測試場景。
+6. 與 iOS/Android/嵌入式工程師共同將演算法移植或包裝（例如 C/C++ / Rust library 或 WASM），或作為雲端</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tjo6</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>20260424</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>數據應用工程師</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>聯經數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>新北市汐止區 大同路一段369號3樓</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>效提供部門技術支援，透過專業技術或工具進行資料清理、結構化、分析，及呈現，友善各需求單位取得數據加以應用。
+4.隨時掌握數據系統工程之產業最新知識、技術、應用及趨勢。
+5.其它主管交辦事項。
+【必要條件】
+1.熟悉基礎 SQL 語法與</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8nf2t</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>【外商】[FIN] Sr. Data Engineer／資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號20樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Dagster 或 Airflow 等排程工具。
+5. 5 年以上資深資料工程師或相關經驗，並具備獨立主導專案的能力。熟練運用大語言模型（LLM）等工具進行需求分析、代碼重構、或自動化編寫重複性 ETL 腳本
+6. 卓越的需求訪談與業務邏輯理解能力，能將複</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dq30</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>統一超商資深資料工程師(uniopen客戶資料平台CDP)</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>統一超商股份有限公司</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路163號5樓</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>月薪 50,000 ~ 120,000元</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>【工作內容】
+1. 設計資料模型與數據建模轉化 (Data Modeling)：主導 數據架構規劃與 Medallion 模型設計，定義企業級 Golden Table 規範，確保模型具備高度擴展性以支援 AI/ML 應用。
+2. BI 報表與儀</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p2a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>AI 工程師</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>碩益科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>台北市大安區 光復南路102號9樓</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位對 AI 技術充滿熱情、後端基本功扎實的 Junior AI / 後端工程師。
+你將加入我們的 AI 研發團隊，在資深架構師的帶領下，協助開發與維護企業級的 AI Agent 系統與高精度知識檢索（RAG）應用。
+這是一個能讓你深</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92lpv</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>澧曜數據有限公司</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>台中市西區 忠明南路497號2樓</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 開發/維護/設計處理數據架構與服務以及部署服務。
+2. 負責ETL（數據提取、轉換、加載）流程設計，包括數據清洗、預處理及自訂程式開發。
+3. 擁有CI/CD經驗，熟悉Jenkins、GitLab、Airflow等CI/CD工具和流程。
+</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dclx</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Data Engineering Intern 實習資料工程師</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>類神經網路股份有限公司</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>台北市松山區 復興北路369號14樓之2</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>月薪 196 ~ 250元</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>「為什麼要做」、「真正要解決的問題是什麼」。
+無論是資料處理、AI 應用開發、系統優化或日常維運，我們都期待每位成員能理解自己所負責工作的目的與影響，主動發現問題、提出想法，並持續尋找更好的解決方式。
+如果你喜歡探索新技術與新工具；
+如果你具備</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7n5ln</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>資料工程師 / 數據服務架構師</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Phison Electronics Corp_群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>IC設計相關業</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>苗栗縣竹南鎮 群義路1號</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>算引擎（如 Trino）的維運與優化，透過 Infrastructure as Code (IaC) 與 GitOps 實現數據工程的自動化與標準化。
+【工作內容】
+    容器化平台管理：負責 Kubernetes 叢集的日常維運、資源調度與自動</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ve8x</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>資深資料科學工程師 Sr. Data R&amp;D Engineer (Backend) - 台中 數據技術發展 (數數發中心, DDT)_I00020704</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>台中市烏日區 台中市烏日區高鐵一路299號</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>[工作內容]
+資深後端工程師職務可能包含但不限如下相關內容：
+- 開發與維護現有應用服務
+- 與前端人員合作設計 API 接口
+- 熟悉資料與 AI 模型應用服務開發，與資料科學家合作解決商業命題
+- 具有 Open Source 研究與使用經驗</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n5io</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>【金融科技】資料工程師 Data Engineer(經驗行員)</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>玉山銀行_玉山商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>台北市松山區 民生東路三段115號</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>1.負責設計和維護高效且可擴展的雲地混合數據架構
+2.設計及開發巨量資料 data pipeline，包含結構化資料、半結構化資料及非結構化資料，並建立自動化監控機制
+3.評估與導入 modern data stack，用以解決以下問題：data</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7tqhz</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>20260311</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>【數位驅動】資料科學工程師 (數數發中心,DDT)_I00021770</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>國泰世華商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>1.數據介接、清洗、處理與數據模型的程式開發
+2.數據工程 API 程式撰寫
+3.與數據分析師合作，進行機器學習、深度學習與統計分析模型的維運化程式開發
+4.ETL Pipline 的工具開發與維護
+5.協助新系統上線
+6.數據工程的自動化、監控</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pi2u</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>SW_資料庫工程師 DBA Engineer</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>蓋亞汽車股份有限公司</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>汽車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>台中市烏日區 高鐵一路299號7樓</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>蓋亞汽車【研發部】擴大招募！
+走向零碳未來，我們期待您的加入。
+我們正在尋找一位熱愛資料庫效能優化、系統架構設計與跨部門協作的【資料庫工程師】，協助我們打造高效穩定的資料架構，支援智慧車輛系統與資料分析應用。
+｜您在蓋亞汽車的工作職掌｜
+✔</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dt2w</t>
         </is>
       </c>
     </row>

--- a/z_RequestData/jobsearch_data104.xlsx
+++ b/z_RequestData/jobsearch_data104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,10 +481,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A2" t="n">
+        <v>20260706</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -538,10 +536,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
+      <c r="A3" t="n">
+        <v>20260703</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -596,10 +592,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A4" t="n">
+        <v>20260706</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -648,10 +642,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
+      <c r="A5" t="n">
+        <v>20260701</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -703,10 +695,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A6" t="n">
+        <v>20260706</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -756,10 +746,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A7" t="n">
+        <v>20260707</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -811,10 +799,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A8" t="n">
+        <v>20260702</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -868,10 +854,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A9" t="n">
+        <v>20260706</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -921,10 +905,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A10" t="n">
+        <v>20260702</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -975,10 +957,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A11" t="n">
+        <v>20260707</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1031,10 +1011,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20260625</t>
-        </is>
+      <c r="A12" t="n">
+        <v>20260625</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1086,10 +1064,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20260515</t>
-        </is>
+      <c r="A13" t="n">
+        <v>20260515</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1140,10 +1116,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>20260621</t>
-        </is>
+      <c r="A14" t="n">
+        <v>20260621</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1196,10 +1170,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A15" t="n">
+        <v>20260529</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1251,10 +1223,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>20260508</t>
-        </is>
+      <c r="A16" t="n">
+        <v>20260508</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1308,10 +1278,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
+      <c r="A17" t="n">
+        <v>20260629</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1363,10 +1331,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20260702</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1420,10 +1386,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>20260618</t>
-        </is>
+      <c r="A19" t="n">
+        <v>20260618</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1474,10 +1438,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
+      <c r="A20" t="n">
+        <v>20260703</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1529,10 +1491,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
+      <c r="A21" t="n">
+        <v>20260701</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1603,10 +1563,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A22" t="n">
+        <v>20260702</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1657,10 +1615,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A23" t="n">
+        <v>20260702</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1710,10 +1666,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20260630</t>
-        </is>
+      <c r="A24" t="n">
+        <v>20260630</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1772,10 +1726,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A25" t="n">
+        <v>20260707</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1828,10 +1780,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
+      <c r="A26" t="n">
+        <v>20260701</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1885,10 +1835,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20260630</t>
-        </is>
+      <c r="A27" t="n">
+        <v>20260630</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1940,10 +1888,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A28" t="n">
+        <v>20260707</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1993,10 +1939,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A29" t="n">
+        <v>20260707</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2046,10 +1990,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20260630</t>
-        </is>
+      <c r="A30" t="n">
+        <v>20260630</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2102,10 +2044,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A31" t="n">
+        <v>20260706</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -2157,10 +2097,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A32" t="n">
+        <v>20260706</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2213,10 +2151,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>20260511</t>
-        </is>
+      <c r="A33" t="n">
+        <v>20260511</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2270,10 +2206,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20260630</t>
-        </is>
+      <c r="A34" t="n">
+        <v>20260630</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2343,10 +2277,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>20260616</t>
-        </is>
+      <c r="A35" t="n">
+        <v>20260616</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2396,10 +2328,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
+      <c r="A36" t="n">
+        <v>20260701</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2451,10 +2381,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>20260616</t>
-        </is>
+      <c r="A37" t="n">
+        <v>20260616</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2507,10 +2435,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>20260415</t>
-        </is>
+      <c r="A38" t="n">
+        <v>20260415</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2562,10 +2488,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A39" t="n">
+        <v>20260706</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2616,10 +2540,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A40" t="n">
+        <v>20260707</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2669,10 +2591,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A41" t="n">
+        <v>20260707</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2723,10 +2643,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A42" t="n">
+        <v>20260702</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2780,10 +2698,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A43" t="n">
+        <v>20260707</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2835,10 +2751,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A44" t="n">
+        <v>20260707</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2894,10 +2808,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>20260626</t>
-        </is>
+      <c r="A45" t="n">
+        <v>20260626</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2948,10 +2860,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A46" t="n">
+        <v>20260702</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -3005,10 +2915,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>20260704</t>
-        </is>
+      <c r="A47" t="n">
+        <v>20260704</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -3063,10 +2971,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A48" t="n">
+        <v>20260706</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -3118,10 +3024,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A49" t="n">
+        <v>20260702</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -3173,10 +3077,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A50" t="n">
+        <v>20260706</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -3228,10 +3130,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A51" t="n">
+        <v>20260702</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -3283,10 +3183,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>20260625</t>
-        </is>
+      <c r="A52" t="n">
+        <v>20260625</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -3338,10 +3236,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A53" t="n">
+        <v>20260707</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3392,10 +3288,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A54" t="n">
+        <v>20260707</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3447,10 +3341,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A55" t="n">
+        <v>20260706</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3500,10 +3392,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A56" t="n">
+        <v>20260706</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3557,10 +3447,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A57" t="n">
+        <v>20260702</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3611,10 +3499,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>20260616</t>
-        </is>
+      <c r="A58" t="n">
+        <v>20260616</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3665,10 +3551,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A59" t="n">
+        <v>20260706</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3719,10 +3603,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A60" t="n">
+        <v>20260706</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3776,10 +3658,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>20260704</t>
-        </is>
+      <c r="A61" t="n">
+        <v>20260704</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3830,10 +3710,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A62" t="n">
+        <v>20260706</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3886,10 +3764,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A63" t="n">
+        <v>20260707</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3939,10 +3815,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>20260624</t>
-        </is>
+      <c r="A64" t="n">
+        <v>20260624</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3996,10 +3870,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>20260618</t>
-        </is>
+      <c r="A65" t="n">
+        <v>20260618</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -4051,10 +3923,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A66" t="n">
+        <v>20260706</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -4106,10 +3976,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A67" t="n">
+        <v>20260707</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -4159,10 +4027,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>20260630</t>
-        </is>
+      <c r="A68" t="n">
+        <v>20260630</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -4211,10 +4077,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
+      <c r="A69" t="n">
+        <v>20260701</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -4269,10 +4133,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A70" t="n">
+        <v>20260706</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -4322,10 +4184,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>20260409</t>
-        </is>
+      <c r="A71" t="n">
+        <v>20260409</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -4378,10 +4238,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A72" t="n">
+        <v>20260702</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -4432,10 +4290,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>20260624</t>
-        </is>
+      <c r="A73" t="n">
+        <v>20260624</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -4489,10 +4345,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A74" t="n">
+        <v>20260707</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4545,10 +4399,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
+      <c r="A75" t="n">
+        <v>20260703</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4600,10 +4452,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A76" t="n">
+        <v>20260707</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4656,10 +4506,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A77" t="n">
+        <v>20260702</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4713,10 +4561,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>20260622</t>
-        </is>
+      <c r="A78" t="n">
+        <v>20260622</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4767,10 +4613,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
+      <c r="A79" t="n">
+        <v>20260701</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4823,10 +4667,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
+      <c r="A80" t="n">
+        <v>20260703</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4878,10 +4720,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
+      <c r="A81" t="n">
+        <v>20260701</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4932,10 +4772,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A82" t="n">
+        <v>20260706</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -4988,10 +4826,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>20260615</t>
-        </is>
+      <c r="A83" t="n">
+        <v>20260615</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -5043,10 +4879,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A84" t="n">
+        <v>20260707</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -5101,10 +4935,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A85" t="n">
+        <v>20260702</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -5155,10 +4987,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>20260630</t>
-        </is>
+      <c r="A86" t="n">
+        <v>20260630</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -5210,10 +5040,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A87" t="n">
+        <v>20260706</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -5295,10 +5123,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A88" t="n">
+        <v>20260707</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -5350,10 +5176,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A89" t="n">
+        <v>20260707</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -5406,10 +5230,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
+      <c r="A90" t="n">
+        <v>20260703</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -5463,10 +5285,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>20260628</t>
-        </is>
+      <c r="A91" t="n">
+        <v>20260628</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -5520,10 +5340,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>20260623</t>
-        </is>
+      <c r="A92" t="n">
+        <v>20260623</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5574,10 +5392,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A93" t="n">
+        <v>20260707</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5627,10 +5443,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A94" t="n">
+        <v>20260707</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5686,10 +5500,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A95" t="n">
+        <v>20260706</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -5741,10 +5553,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A96" t="n">
+        <v>20260707</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -5796,10 +5606,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
+      <c r="A97" t="n">
+        <v>20260703</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5854,10 +5662,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>20260703</t>
-        </is>
+      <c r="A98" t="n">
+        <v>20260703</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5912,10 +5718,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>20260508</t>
-        </is>
+      <c r="A99" t="n">
+        <v>20260508</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -5971,10 +5775,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>20260427</t>
-        </is>
+      <c r="A100" t="n">
+        <v>20260427</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -6024,10 +5826,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>20260705</t>
-        </is>
+      <c r="A101" t="n">
+        <v>20260705</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -6078,10 +5878,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>20260604</t>
-        </is>
+      <c r="A102" t="n">
+        <v>20260604</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -6131,10 +5929,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>20260630</t>
-        </is>
+      <c r="A103" t="n">
+        <v>20260630</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -6210,10 +6006,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A104" t="n">
+        <v>20260702</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -6263,10 +6057,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A105" t="n">
+        <v>20260702</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -6316,10 +6108,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A106" t="n">
+        <v>20260702</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -6372,10 +6162,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A107" t="n">
+        <v>20260707</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -6428,10 +6216,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>20260706</t>
-        </is>
+      <c r="A108" t="n">
+        <v>20260706</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -6486,10 +6272,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A109" t="n">
+        <v>20260707</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -6539,10 +6323,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>20260629</t>
-        </is>
+      <c r="A110" t="n">
+        <v>20260629</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -6594,10 +6376,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>20260702</t>
-        </is>
+      <c r="A111" t="n">
+        <v>20260702</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -6665,6 +6445,6137 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>資訊部-銷售系統專業人員</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>台北101_台北金融大樓股份有限公司</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段7號59樓</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 
+專業能力條件
+1.	具資訊管理、資訊工程等相關科系背景。 
+2.	具POS、ERP、CRM、會員系統或商場營運系統相關經驗尤佳。 
+3.	熟悉資料庫管理及SQL查詢語法。 
+4.	具系統分析、需求訪談及專案管理能力。 
+5.	熟悉系統測試、問</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zf5v</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>化妝品研發助理</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>研一實業有限公司</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>化妝品製造業</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高雄市左營區 </t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>月薪 30,000 ~ 38,000元</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1.化妝品配方打樣製作。
+2.進行配方物性、安定性等相關測試之料體製作。
+3.協助執行研發工程師需求之各項測試項目。
+4.可獨立操作配方打樣所需使用之儀器設備。
+5.其他相關文書資料整理。
+6.完成主管交辦事項。</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90nmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>資料/數據工程師 Data engineer</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>智星網路科技有限公司</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>台北市信義區 松仁路89號4樓</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>【關於本職缺｜About the Role】
+Data Engineer 是公司資料基礎建設的核心角色，負責建置、維護與優化資料管線、資料倉儲與數據工程架構，確保來自 GTM、RevOps 與各商務系統的資料能被穩定整合、清洗、轉換並提供給分析與</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94l9i</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>果實夥伴股份有限公司</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路610號2樓</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>【工作內容 】
+-  ETL 之開發、處理(資料清理、儲存、分析)與監測
+- 開發與設計專案所需 API 服務並與後端工程師合作，完成系統產品化程序
+- 依據不同業務需求，完成建置/維運/更新各式 Data infra 的需求
+- 與數據產品管理</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7dpwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>20260720</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>核桃運算股份有限公司</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路一段9號4樓</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備 3-5 年經驗的資料工程師，加入我們的數據團隊。您將負責設計、構建並優化高效率的 Data Pipeline，確保資料從來源端到分析端的準確性與即時性。 此職位不僅需要強大的 Python 與 ETL 開發能力，更需要您對</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8waxf</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>【外商】[DPI] Data Engineer-Streaming／數據工程師-Streaming</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>台北市大同區 南京西路捷運中山站六號出口共構大樓</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>資料與 AI 相關領域人才
+【關於該職位】 
+我們正在尋找一位 Streaming Data Engineer（即時資料工程師），負責設計並建置可擴展的即時資料處理管線（Real-time Data Pipelines）與串流資料平台。
+此職位將</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wpc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>資料工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>立視科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>多媒體傳播相關業</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>台北市松山區 八德路四段760號6樓</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 75,000元</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位熱情且富有才華的資料工程師，加入我們的團隊，協助解決廣告投遞的資料內容。在這裡有大量的數據供你發揮所長，將學過的知識及方法應用到實務的工作上。
+我們希望你具備以下三大特質：
+對資料工程領域有強烈興趣和熱情 。
+重視團隊合作，具備</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zz6u</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IT-Data Engineer數據工程師(後端開發)_新北土城</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>鴻佰科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>電腦及其週邊設備製造業</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新北市土城區 </t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1.ETL的數據接入、清洗與匯入
+2.數據倉庫的建模與標準化
+3.後端API對接
+4.系統自動化代碼持續整合/持續部署
+5.系統效能調校/監控
+6.支援IT專案任務及主管交辦事項。</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pnyc</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>資料工程師/BI工程師</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>揚明光學股份有限公司_YoungOptics Inc.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>光學器材製造業</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>新竹市 科學園區新安路7號</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1. ETL / 資料整合開發：
+     ￭ 設計並開發資料清洗、轉換、整併流程（SAP DS / ETL Pipeline）
+     ￭ 維護批次程序、提升執行效能、確保資料品質與正確性
+2. SAP BW / 資料倉儲管理：</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8q2xn</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>嘉德高分子應用材料股份有限公司</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>橡膠製品製造業</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>新竹縣湖口鄉 鳳工路45號2樓</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>月薪 38,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>數據分析師及其他相關團隊合作
+6. 持續研究、學習新技術，提供更好的解決方案
+資料工程師在現今數位化時代扮演著重要的角色，負責設計、開發、建置企業級大數據平臺、資料倉儲及相關服務，為企業提供更好的資料分析與應用解決方案。這個職位有著廣闊的發展前景</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/946sd</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>[MDL-DE] 資料工程師 Data Engineer（Model Team）</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>亞太智能機器股份有限公司</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路266號2樓</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>麼是好資料」→ 產出訓練可用的資料集→ 配合訓練與評測驗證資料品質。
+你會和 Model Team 的工程師密切合作，理解每次訓練需要什麼樣的資料；也會配合 PjM，協助說明客戶該提供什麼格式與品質的資料。你也會參與資料管道（data</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/942tp</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ETL 資料工程師/大數據工程師</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>歐立威科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>台北市大同區 鄭州路87號11樓之1</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Pentaho PDI、Talend、Informatica、Microsoft SSIS 等）進行數據抽取、轉換與載入，確保資料正確性與完整性。
+3.熟悉 Python 或 Java 等程式語言，能撰寫 ETL 腳本與自動化流程。
+4.設計並維護 Data</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ugrj</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>英屬維京群島商嘉碼科技有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>台中市西屯區 工業三十八路210號3樓之6</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位數據工程師，不僅具備扎實的技術底子，更擁有主動積極、樂於挑戰的特質。
+加入我們後，您將在這個充滿活力、尊重多元的環境中扮演關鍵角色，透過打造穩健的數據基礎與管道，協助團隊從資料中萃取價值、加速產品與業務的創新。
+如果您對資料領域充</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8vvrv</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>圖靈數位股份有限公司</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>台北市中正區 中山北路一段2號11樓</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>行銷判讀，運營，轉化方面的戰略支持與技術方法。成員大多是技術工程師組成，協助客戶收集有用的數據，了解數據，利用數據。
+目前是 Google Marketing Platform、Mixpanel、AB Tasty 認證合作夥伴。
+公司福利：
+・</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7v0e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>資料工程師 ETL / Data Engineer | 半導體 | 工作地點: 新北市</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tezerakt_美商立方體有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新北市板橋區 </t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>[請提供英文簡歷]
+[本職缺] 
+為 Data Infrastructure Support Engineer(資料工程)，主要負責半導體製造產業 ／雲端資料基礎建設的功能開發與強化。工作範疇包含新data pipeline 的 parsing</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yq4u</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>【台北】數據工程師Data Engineer — "Data Infrastructure Architect"</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>創智動能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>台北市中正區 八德路1段23號9樓</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>至數據倉儲或資料湖。 
+   確保數據準確性與一致性，並優化數據處理效能。
+Data Transformation and Integration
+Design and implement data transformation processes</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8kgsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Position Impact：
+資料工程師的核心價值在於設計、建置並維護整體的數據解決方案，確保全公司的數據具備高可用性、可靠性及可擴充性。在此職位中，您將處理大規模數據庫，主動識別潛在風險，並開發能提升數據效能與品質的解決方案。您將與後端工程師</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ti6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>科技部_Data Engineer 數據工程師 (Data &amp; AI Product)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>美好證券股份有限公司</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路三段２號4樓</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>】
+我們正在打造新一代的 DATA/AI 智能化運轉體系，以先進的數據工程、資料平台與 AI 技術，推動投資研究、產品創新與顧問服務的核心能力全面升級。
+此角色將負責設計、建置與維運公司的核心數據基礎設施 (Data &amp; AI Platform)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7b6bq</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>【總公司】Data Engineer/數據工程師/資料工程師)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>味全食品工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>乳品製造業</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路125號10樓</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>本職務為台灣味全總部IT 職缺，隸屬數位部，負責集團數據平台之資料工程與維運：
+1. 維運既有資料倉儲與 ETL 排程：資料抽取、清洗、轉換、載入與失敗重跑。
+2. 與外部廠商（系統整合商）合作維運數據倉儲/數據平台：需求確認、交付驗收、上線後</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90av4</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>【AI Lab】資深數據工程師 Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>愛卡拉互動媒體股份有限公司</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中山區 </t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>【Responsibilities】
+- Design, build, and maintain scalable data pipelines that meet evolving product and analytics needs.
+- Identify, design, and implement internal process improvements: automating manual processes, optimizing data delivery, re-designing infrastructure for greater scalability, etc.
+- Create data tools that enable analytics and data scientist team members to build and ship faster.
+- Build and maintain the services that deliver our data to product, analytics, and external consumers.
+- Partner with data and analytics teams to evolve our data infrastructure.
+- Support cross functional, cross BU data integration tasks.
+【Must to Have】
+- Bachelor's degree in Computer Science, Engineering, or a related field, or equivalent practical experience; Master's is a plus
+- Strong proficiency in Python 3.10+ and shell scripting (Bash), with 5+ years of backend / data engineering experience and 3+ years owning production data pipelines
+- Experience with workflow orchestration tools, e.g. Argo Workflow, Airflow, Dagster
+- Experience with RDBMS, OLAP, and search databases, e.g. PostgreSQL, StarRocks (or BigQuery / ClickHouse / Snowflake / Druid), Elasticsearch
+- Experience with backend API development and deployment, e.g. gRPC, REST (FastAPI)
+- Experience deploying and operating services on Kubernetes with Docker
+- Comfortable developing, deploying, and debugging in Linux environments
+【Nice to Have】
+- Basic knowledge of machine learning algorithms
+- Basic knowledge of Data Lake and Data Warehouse Design
+- Experience with streaming processing systems, e.g. Kafka, Apache Flink, Cloud Dataflow, Apache Beam, Pub/Sub
+- Experience with Go programming language
+- Experience with gRPC and Protocol Buffers
+- Experience with production-grade operations — monitoring, debugging, and maintaining your own work after deployment</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91m1t</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資深資料工程師(Python)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>宇利峯有限公司</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>台中市西屯區 市政路386號</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>職位概要:
+我們正在尋找一位專精於資料整理和Python開發的Python資料工程師，主要負責資料的清洗、標準化和品質控制工作。
+1. 數據清洗和標準化:
+- 處理原始資料，識別和處理異常值。
+- 統一資料格式和編碼標準。
+- 補齊缺失值和修正</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>愛德萬互聯科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>桃園市蘆竹區 內溪路47號</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◎主要工作內容包括：
+Data Analytics &amp; Business Insights
+•	Analyze large and complex datasets from business and manufacturing systems to identify trends, patterns, exceptions, and improvement opportunities.
+•	Translate business challenges into data requirements, analytical approaches, and actionable recommendations.
+Data Solution Planning &amp; Project Delivery
+•	Conduct requirement analysis and assess data sources, dependencies, risks, and solution feasibility for assigned data initiatives.
+•	Define solution scope, data models, integration approaches, deliverables, and validation criteria for data projects.
+Data Architecture &amp; Engineering Collaboration
+•	Design scalable data models, Data Warehouse structures, Data Marts, and reusable datasets across enterprise and operational systems.
+Enterprise Applications &amp; Systems Integration
+•	Design cross-system data mappings, interface requirements, reconciliation controls, and exception-handling mechanisms.
+•	Support the development and maintenance of internal data applications, system interfaces, and lightweight services using C#/.NET technologies such as WinForms and ASP.NET Web Forms.
+•	Support Oracle ERP-related data integration and application services, including Oracle Database connectivity, SQL and PL/SQL development, data interfaces, and integration with internal systems.
+Visualization &amp; Reporting
+•	Develop interactive dashboards, management reports, and operational visualizations using Power BI and other analytics tools.
+◎需求條件：
+•	Bachelor's degree in Information Technology, Information Management, Software Engineering, or a related information systems field.
+•	Minimum 3 years of experience in data analytics, business intelligence, data engineering, database development, enterprise applications, or related disciplines.
+•	Hands-on experience with Oracle Database and PL/SQL, including database objects and stored procedures, as well as Microsoft SQL Server database development, performance tuning, and maintenance.
+•	Hands-on experience in data modeling and Data Warehouse or Data Mart design, with practical exposure to cross-system data integration.
+•	Experience developing dashboards, management reports, or analytical applications using Power BI, Tableau, or similar platforms.
+•	C# / ASP.NET Application Development
+</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94jv3</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>資訊維運專員（系統整合 / 快速建置專案）</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>財團法人祐生研究基金會</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>其他專業／科學及技術業</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>台北市中山區 長安東路一段4號2樓</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 55,000元</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>錄文件。
+徵求條件：
+1.大學畢業生。
+2.對 PHP / MySQL (或 MariaDB) 生態系有基礎認識，理解現代網頁運作基礎架構（前
+   端 HTML/CSS/JavaScript 與後端資料庫、API 的互動邏輯），並能運用 AI</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94234</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>程式設計師 Product Dev Programmer(產品團隊)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>神華商業系統股份有限公司</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路二段51號4樓之10</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>軟體開發本科系畢業
+● 大學學歷或以上
+●五年以上工作經驗加分
+【其他職缺參考】
+本職缺主要為"產品開發團隊"團隊的工程師,
+若對於"軟體專案維運導入"有興趣的,可參考以下職缺:
+"程式設計師 Programmer (專案團隊)"
+https:/</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/83lkq</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>行銷部-數據工程師 ( Data Engineer )</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>全聯福利中心_全聯實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>量販流通相關業</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>台北市中山區 敬業四路33號</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>動力，能適應快速變化的技術環境，持續精進技能 
+4. 勇於挑戰創新 - 保持開放心態，不設限自己的發展，樂於嘗試新技術與跨領域合作
+數據工程師的核心挑戰與工作內容：
+1. 數據處理與自動化 — 了解與整合異質數據來源（API、資料庫、CSV、</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7xcgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>文境資科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>專門設計相關業</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師
+1.資料稽核(Data Auditing)、收集(Data Collection)、整合作業(Data Integration) 等資料分析前處理作業
+2.有MS SQL server、SSIS、SSRS</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7g1tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>20260731</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Regional Data Engineer 數據工程師(台北工作)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>香港商麥迪康亞太有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路1段163號4樓之3(市府站1號出口)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1.設計、開發和維護可擴展的數據管道和ETL流程。
+2.與數據科學家、分析師和利益相關者合作，了解數據需求並提供解決方案。
+3.優化和改進現有數據系統，以提高性能和可靠性。
+4.實施數據質量檢查，確保各類數據源的數據完整性。
+5.開發和維護數據工程</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8m4mk</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SPC數據工程師</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>嘉晶電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>半導體製造業</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>新竹市 創新一路3號</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1.統計製程管制
+2.製程參數與品質監控
+3.協助建置製造資料庫，確保資料可追朔可查詢。
+4.協助將製程與生產資料系統化
+5.良率分析，異常偵測與改善追蹤。
+6.數據統計與系統維護
+7.協助產出定期報表（for 客戶、工廠）</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91zkc</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>【國泰投信】資料工程師 Data Engineer_I00022210</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>國泰證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號6樓</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Kubernetes）。
+5. 實現湖倉一體（Lakehouse）與存算分離架構。
+【必要條件】
+1. 1 年以上資料工程或資料分析經驗，具備資料處理或資料分析的程式開發能力。
+2. 具備 Python 軟體開發或資料處理經驗。
+3. 具備 Linux 系</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qbni</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>雲端數據工程師</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>君綺生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>美容／美體業</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>台北市信義區 松智路1號</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>部門介紹:
+我們是集團組織擴編成立的新部門, 在這工作你將會體驗全雲的工作環境, 包含AWS雲端服務及工具, 在工作中學習專案管理、資料庫管理、雲端服務等技術
+工作內容
+1. 參與雲端數據架構發展規劃，設計資料處理、儲存、分析架構，以符合數據</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mcsu</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>資料工程師-M115</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>精誠軟體服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路96號21樓</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>加入專案團隊，協助規劃、建置與優化企業資料處理與分析所需的資料基礎，主要任務包含：
+1. 設計、開發並維運資料整合流程，涵蓋 ETL／ELT 作業、資料清理、格式轉換與流程監控。
+2. 串接多元資料來源，進行資料模型、資料表結構與處理邏輯的設計與</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7mqfz</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>20260730</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>聯想感行銷科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>台北市松山區 民生東路三段135號3樓</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>月薪 1,100,000元以上</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>獨立掌握與釐清客戶資料處理需求、定義資料流規格、定義資料模型，確認運行規格。
+需面對企業客戶並給予資料流與資料 schema 上的回應。
+【專案管理能力】
+熟悉資料流開發、資料流驗証等流程。
+熟悉編寫資料流規格書。
+評估議定工作時程表（WBS</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8t673</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>數位醫療服務 -【資料分析 / 資料工程師】</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>采鋐健康整合集團_采照策略顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段5號M層</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>這不是一份只會「做報表」的工作。 我們正在尋找一位能夠把資料玩出火花的夥伴，讓數據真正變成影響決策的武器！
+你將會：
+1. 透過 Tableau、Looker、PowerBI 等 BI 工具，打造一眼就能看懂的超強報表，讓老闆和團隊秒懂數據價值。</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8te5p</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>數解人意科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路三段 195 號 7 樓</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>【 資料工程師 ( Data Engineer) 】
+在 QSearch，數據是我們最核心的資產。此角色的核心目標是建構公司大數據生態系的「源頭引擎」。您將負責設計、開發與維運可擴展的高速分散式爬蟲系統，與各平台反爬蟲機制正面對決，並優化高併發</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92847</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>(C6) 資深數據工程師Senior Data Engineer（內湖）</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>【職位說明】
+參與智慧城市 AI 賦能產品開發，負責建置企業級數據平台(Data as a Service, DaaS)，處理各種形式的資料，並進行完善的資料治理、血緣追蹤與監控。最終將整合生成式 AI（Generative AI）功能，提供智慧</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p0av</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>資料工程師 (IDS-DSS)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>宏燁資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>台北市中正區 北平東路30號7樓</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>專科</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>1.協助建置與維護 ETL數據管道。
+2.協助開發與建置 MongoDB 資料模型設計Data Modeling、Schema Design及Sharded Cluster
+3.使用 SQL、Python 進行資料擷取、轉換及清理作業。
+4.協助</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/93nrk</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>數位創發中心-專任職員2名(Power BI 資料分析工程師)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>臺北市立萬芳醫院-委託臺北醫學大學辦理</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>醫院</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>新北市中和區 圓通路301號</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>月薪 43,700 ~ 45,900元</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>【工作內容】
+(1)負責 Power BI 報表之設計、開發與維運，將複雜資料轉化為具洞察力的視覺化分析。 
+(2)進行資料庫資料擷取、清理與整合（Oracle、MS SQL 或其他關聯式資料庫）。
+(3)撰寫與優化 SQL 查詢，建立可重複使用</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8z3ma</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>20260731</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>全端資料工程師（資料平台）  Full Stack Engineer (Data Platform)(台南優先,台中)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>葳誠科技有限公司</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>台南市善化區 環東路二段33號</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>月薪 70,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>【職務說明 Position Summary】
+中文：
+我們正在尋找一位以資料平台為核心的全端工程師駐點在外商客戶端，負責開發與維運雲端資料平台及相關Web服務。此職位著重於 Databricks、SCM資料倉儲、資料分析/探勘與系統整合，同時</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90phw</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>東海大學智慧永續循環經濟研究中心誠徵資料工程師</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>東海大學</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>其他教育服務業</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>台中市西屯區 台灣大道四段1727號</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具環境工程背景、能將專業知識轉化為結構化資料與知識模型的人才，加入智慧永續循環研究中心，共同建構以環工知識為核心的 AI 與知識圖譜系統。
+本職位的核心任務不是單純做資料清洗或模型訓練，而是：
+把環境工程的「機制、概念與流程」</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8y8zy</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>重高科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段162號12樓之2</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Technical Skills)--
+我們希望候選人在以下多數領域具備實作經驗：
+1. Python：精通 Python，特別是在資料工程與自動化流程的應用（而不僅僅是撰寫簡單腳本或 ML 模型）。
+2. SQL：專家級別，具備 BigQuery 或類似雲端資料</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvez</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>數據工程師(Data Engineer) - Python/API開發/ETL</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>果友科技有限公司</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備後端思維的數據工程師，打造數據產品與並與分析客戶團隊合作，建置高品質的數據供應與自動化環境。
+你的主要任務是確保數據能穩定流動、被正確處理與自動化運作，成為支撐企業決策與AI應用的堅實基礎。
+【工作內容】
+1. 設計、開發與</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8thk7</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>前後端工程師/資料工程師</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>貝伯盈智慧運營有限公司</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>台中市南區 福順里平順街200號1樓</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 輪換策略(住宅代理、動態 IP 池)
+4. 設計資料清洗與格式標準化 pipeline，將原始資料結構化後寫入 OpenSearch
+5. 監控爬蟲健康狀態，快速處理因各平台改版導致的失效問題
+6. 與 NLP 工程師協作，確認資料欄位結構滿足後續</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92ier</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>數據工程師 - RPA流程自動化人員(IDS)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>宏燁資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>台北市中正區 北平東路30號7樓</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1. RPA軟體流程自動化(UiPath / Automation Anywhere)需求訪談、流程規劃、流程開發與維護。
+2. 設定軟體自動化流程、伺服器平台運用、流程開發。
+3. 個性主動積極，具程式開發相關經驗佳。  
+4. 有良好的溝通與表達能力，具團隊合作精神。
+5. 具有RPA經驗者佳。
+6. 依個人經驗與期望安排對應專案職務(駐點客戶端等)。
+7. 無RPA經驗可，歡迎想要學習與實作RPA機器人的夥伴加入。</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/874x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>20260729</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>HUA AO_香港商創金科技有限公司</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>台北市大同區 （近台北車站/京站廣場）</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Data Pipeline 等。
+•	研究並導入新技術，持續提升資料平台能力。
+《任職資格》
+•	大學以上，資訊工程、資訊管理、數學、統計、資料科學等相關科系。
+•	2–4 年資料工程、後端開發、Analytics Engineering 或 Data</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94a7g</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>【日商花王】.NET程式設計師 (歡迎應屆畢業生/不用on call/穩定成長)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>日商  花王(台灣)股份有限公司</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>清潔用品製造業</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>新北市新店區 北新路三段207號10樓</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1.使用S/4 Hana，並配合生產、採購、物流、業務等部門需求，開發適用之系統，以優化作業。
+2.從前端網頁到後端資料庫建置，管理與維護公司內部系統(帳務系統、業務系統...等)
+3.使用 VBA 開發各部門需求表單
+4.與日本母</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/3a5k8</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>.NET 後端工程師（Mid）- OP課</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>日本NEC集團_統智科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞湖街17號4樓</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>法皆可提出並且提出討論，方案確有改善幫助列入當年度績效加分項目。 
+5.專案內容與國內TOP品牌零售/餐飲合作，並使用AWS/AZURE等雲端平台，搭配NoSQL、海量資料等相關技術，有眾多技術領域接觸學習機會，拓展視野。 
+6.我們重視夥伴的才能</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yd1s</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>台北富邦商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1.在Hadoop架構的資料倉儲(Data Warehouse)上建立具備擴充性與高可靠性的資料產品，為數據科學家與業務團隊提供穩健的資料基礎。
+2.與數據科學家和業務分析團隊合作，理解需求並提供適用的資料解決方案。
+3.設計並構建</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n58n</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>新北市土城區 中山路3之2號</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>負責企業資料治理架構、數據品質與安全合規的系統開發、規則落實與日常維護，以提升數據資產的信任度、安全性與數據驅動的營運效率。</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92zyy</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>IT資料工程師(Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>GARMIN_台灣國際航電股份有限公司</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>電信相關業</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>新北市汐止區 新台五路一段97號37樓</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【Job Description】
+We are looking for a skilled and motivated IT Data Engineer to join our team in Taiwan. In this role, you will design, build, and maintain scalable data solutions that support reliable data processing, analytics, and business decision-making.
+You will work with modern data technologies such as Spark, Iceberg, Dremio, Kafka, Qlik, and Airflow to build scalable, reliable, and business-oriented data platforms.
+This role is ideal for someone who enjoys solving complex data problems, working across systems and teams, and turning data into practical business value.
+【Responsibilities】
+•	Design, build, and optimize scalable batch and real-time data pipelines. 
+•	Develop and maintain data models, data warehouses, and lakehouse solutions. 
+•	Build reliable data orchestration and workflow automation processes. 
+•	Work with business and IT teams to deliver data solutions, dashboards, and analytics use cases. 
+•	Support BI, reporting, and self-service analytics through tools such as Qlik. 
+•	Improve data platform reliability through monitoring, troubleshooting, scripting, and automation.
+【Skills】
+1. Essential
+•	Hands-on experience with Spark for large-scale data processing.
+•	Experience with Iceberg, Dremio, or similar lakehouse / modern data platform technologies.
+•	Experience with Kafka or other streaming data technologies.
+•	Strong SQL skills and experience with databases such as Oracle, MSSQL, or PostgreSQL.
+•	Proficiency in Python or Scala for data processing and automation.
+•	Experience with workflow orchestration tools such as Airflow or similar scheduling tools.
+•	Understanding of data modeling, data warehousing, and lakehouse architecture.
+•	Experience with BI or analytics tools such as Qlik, Tableau, or Power BI.
+•	Familiarity with Docker, Kubernetes, Linux, and shell scripting.
+2. Desirable / Nice to Have
+•	Experience with Hadoop or legacy big data platforms.
+•	Experience with S3-compatible object storage or large-scale data lake environments.
+•	Ability to develop and deploy REST APIs or web services.
+•	Familiarity with AI/ML pipelines and related data preparation processes.
+•	Experience or strong interest in GraphDB / Knowledge Graph concepts, including entity relationship modeling, relationship discovery, and graph-based analysis.
+3. Preferred Skills
+•	Strong analytical and problem-solving skills.
+•	Good communication and cross-functional collaboration abilities.
+•	Detail-oriented, proactive, and comfortable working in a fast-paced environment.
+•	Willingness to learn new technologies and continuously improve data solutions.
+</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7z55c</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AIR SPACE_新地國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>鞋類／布類／服飾品批發業</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>台北市士林區 中山北路五段(近士林捷運站210公尺)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>AIR SPACE為台灣第一女裝品牌，
+我們提供安心的工作環境、人才培育訓練課程，
+願您能成為永續經營的共同夥伴，歡迎加入AIR SPACE團隊！
+【我們在找什麼樣的你】
+熟悉資料庫、ETL 流程與數據建模，能有效整理、清理與分析大量數據，</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8fvcr</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>三竹資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>台北市中山區 新生北路二段39號11F</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Airflow 排程管理經驗、DB 帳號權限控管經驗，或有處理高併發金融資料流之經驗。
+職務內容：
+1. 本職務屬於產品任務，配合研發團隊發展金融科技應用之日常資料工程，並負責穩定性維護與效能優化。
+2. 參與設計高可靠性（High</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mtc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ETL資料工程師</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>欣創科技有限公司</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號9樓之4</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1. 熟悉執行ETL資料轉換作業(Informatica PowerCenter、IBM DataStage、Microsoft SSIS、Trinity等ETL工具)
+2. 資料庫安裝、設定及操作實務經驗
+3. 具備STORE</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/80lq4</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>A6000【momo Ads】資料工程師/Data Engineer(Java、Python、ETL)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>富邦媒體科技股份有限公司(富邦momo)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>台北市內湖區 洲子街96號4樓</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>負責廣告平台 Momo Ads 系統的資料流設計，並協助開發滿足廣告業務發展相關的需求
+2.優化系統 Data Pipeline 處理海量用戶與廣告事件，提供即時且高效率的 OLAP 系統
+3.與演算法工程師與資料分析師協作開發廣告引擎模型與競價引</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dbr3</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師(錦州街)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>山富國際旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>台北市中山區 錦州街46號10樓</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>月薪 48,000元以上</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">與效能調校。
+與後端工程師協作，確保數據收集與儲存的效率與規範。
+探索並導入新興的數據技術與工具，持續提升團隊的數據處理能力。
+</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/73ifb</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師 (大直)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中山區 </t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>【職務需求】
+1. 熟悉資料庫系統：MS SQL Server、Oracle等運作規劃。
+2. 熟悉ETL運作、資料倉儲(DW)、資料超市(DM)等運作規劃。
+3. 熟悉微軟雲端ETL解決方案：Azure Synapse Analytics、</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/93rcp</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>【外商】[FIN] Sr. Data Engineer／資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>烽泰科技有限公司</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>其他金融及輔助業</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號20樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Dagster 或 Airflow 等排程工具。
+5. 5 年以上資深資料工程師或相關經驗，並具備獨立主導專案的能力。熟練運用大語言模型（LLM）等工具進行需求分析、代碼重構、或自動化編寫重複性 ETL 腳本
+6. 卓越的需求訪談與業務邏輯理解能力，能將複</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dq30</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>數據工程師 data engineer</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>台灣創博識有限公司</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>台北市中正區 南海路1號13樓</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>data governance, data quality, MLOps
+4. 優化開發者體驗，解決資料科學家開發與部署會遇到的問題
+資料工程師在數位轉型的浪潮下扮演重要的角色，本職位將有機會參與公司數位轉型計畫，並協助建立可靠的數據基礎架構，提供客</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wl9k</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>【研究發展處】Big Data Engineer 資料工程師 / Senior Big Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>現觀科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段42號2樓</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Dashboard Visualization，並與產品開發團隊進行資料探勘及研究。
+[工作內容]
+1.開發大數據系統資料處理平台
+2.串流資料平行處理程序開發,熟悉分散式運算,平行運算
+3.解決大量資料處理時所衍生的效能,擴充與維護維運資料庫</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7bdqr</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>全電商營運部-數據工程師</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>全聯福利中心_全聯實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>量販流通相關業</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>台北市中山區 敬業四路33號</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>加入我們！
+數據工程師的核心挑戰與工作內容：
+1. 數據處理與自動化 — 了解與整合異質數據來源（API、DB資料庫、CSV、Parquet 等），建立高可靠度的 ETL／ELT 數據自動化處理流程、部署與監控機制，確保服務穩定性 
+2. CDP</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mp6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>[台北]資料工程師(BI)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>台灣新蛋股份有限公司</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路513巷31號10樓</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>BI 或資料工程有興趣
+    •  願意學習新技術，具備良好邏輯思考能力
+【加分項】
+    • 有簡單資料分析 / BI / ETL project 經驗（課程或 side project 皆可）
+    • 有使用 Python（pandas</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/917z1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>侍達遊戲藝術有限公司</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>台北市信義區 東興路41號5樓</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1. 根據分析需求進行資料建模，並提供視覺化的資料呈現。
+2. 提供分析數據及報表。
+3. 設計與開發資料分析所需要的工具。
+[能力需求]
+1. 具備程式開發經驗 (Python/Golang等)。
+2. 具備 SQL/NoSQL 使用經驗</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85yiu</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>遊戲資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>吉恩立數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段106號5樓</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>我們找的就是你：善於溝通、邏輯清晰及執行力的工程師 !
+負責一款遊戲，
+從資料庫初期的建置發佈以及遊戲整體環境建置，到後續服務的長久運行管理。
+在這裡你不會感到孤單，會有同仁一起參與合作與營運，當然，熟悉後也有需要獨自運作的時刻。
+【工作任務</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tymj</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>數據工程師(Data Engineer) - Python/ETL/MongoDB</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>果友科技有限公司</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段333號</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備後端架構思維的「數據工程師」，能與企業客戶的數據分析、工程團隊協作，打造穩定且可擴展的數據處理流程。
+這份職缺主要任務是設計並維運高可靠性的 ETL 與 Airflow 數據流程，確保資料能自動化運行、正確轉換，成為企業決策與</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8urkt</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>【前瞻研究籌獲中心】資料工程師(台南)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>國家資通安全研究院</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>其他專業／科學及技術業</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台南市歸仁區 </t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>1.協助概念驗證程式開發、後端服務建置及產品功能落地，支援不實資訊、網路詐騙、深偽影音等相關應用系統之開發與維運。
+2.建構高效、可擴展且穩定之後端服務，開發與串接 API、AI 模型推論服務及資料處理流程，並與前端、資料及產品團隊協作完成系統整</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8rkm9</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>資料工程師 / 數據服務架構師</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Phison Electronics Corp_群聯電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>IC設計相關業</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>苗栗縣竹南鎮 群義路1號</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>算引擎（如 Trino）的維運與優化，透過 Infrastructure as Code (IaC) 與 GitOps 實現數據工程的自動化與標準化。
+【工作內容】
+    容器化平台管理：負責 Kubernetes 叢集的日常維運、資源調度與自動</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ve8x</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>永慶房產集團_永慶房屋仲介股份有限公司</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段77號12樓</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>永慶房產集團為房仲產業龍頭，用科技創新引領創新變革，歡迎IT領域的優秀夥伴加入!
+工作內容如下：
+1.規劃集團資料流程，達成資料整合綜效。
+2.建置企業數據中台，管控集團資料倉儲品質與正確性。
+3.與資料分析師協同合作，進行資料分析前處理，提供</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78pf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>20260808</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>技術專案工程師／Technical Project Engineer</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>捷銻熙工具有限公司</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>其他商品批發業</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>台中市東區 東光園路100巷47號</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>月薪 60,000元以上</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>• 負責國外客戶與國內外工廠之間的技術溝通及需求確認。
+• 將客戶需求轉化為產品規格、圖面要求及可執行的開發項目。
+• 負責新產品及客製化工具的專案規劃、時程追蹤與執行。
+• 協調設計、採購、製造、品管、物流及客戶端相關人員。
+• 追蹤樣品製作、設計審查、測試驗證、問題改善及量產導入。
+• 審閱2D／3D圖面、規格書、測試報告及其他技術文件。
+• 彙整會議紀錄、專案進度、問題清單及改善措施。
+• 配合國外出差，前往工廠或客戶端進行技術討論、產品驗證及問題處理。
+• 協助處理售後技術問題、故障分析及改善追蹤。</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/941v7</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Field Service Engineer 醫療設備工程師</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>思泰瑞台灣股份有限公司</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>機械器具批發業</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段206號18樓</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>設備工程師加入團隊。此職位將扮演台灣技術服務能力建立的重要角色，負責 STERIS 醫療設備之安裝、保養、維修及技術支援，並與授權經銷商、醫院客戶及全球 STERIS 技術團隊密切合作，共同提供專業且高品質的服務。
+這不只是一個設備維修職位，更是</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/9481d</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>20260729</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>【健康台灣深耕計畫】資料工程師(範疇三-數位醫療中心)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>三軍總醫院附設民眾診療服務處_醫務企劃管理部</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>醫院</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>台北市內湖區 成功路二段325號</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>年薪 700,000 ~ 840,000元</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>職位簡介
+加入三軍總醫院數位醫療中心 (DMC)，您將成為一名資料工程師 (Data Engineer)，專注於醫療數據管線（Data Pipeline）的建置、標準化整合與資料庫維運。我們的目標是應用資料科學技術，提升健康照護品質，並推動 AI</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92w6s</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>數據工程師 - WS215</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>朋昶數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路三段51號5樓</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1.  參與 Data Migration 專案規劃與執行。
+2.  負責既有 SQL 程式分析、修改及優化。
+3.  負責 ETL 流程開發、修改、測試及維護。
+4.  進行來源系統與目標系統之資料整合及轉換設計。
+5.  撰寫 Stored</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92xr1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>【台北 / 彈性遠端】Sr. Data Engineer 資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>布魯斯人事顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中正區 </t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>月薪 1,400,000元以上</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1. 負責大規模資料的雲端基礎架構設計與演進，涵蓋資料流、整合處理、儲存分析與事件偵測等核心能力。
+2. 與相關團隊協作，提出並實作資料架構的優化與轉移計畫，打造具高可用性、可擴展性與韌性的基礎設施。
+3. 兼顧業務成長與工程實作</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wrnj</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>英屬開曼群島商萬里雲互聯股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段333號33樓</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>【職務說明】
+       我們正在尋找一位具備高度專業技能的資深資料工程師，加入我們快速成長的資料與AI解決方案團隊。此角色將負責設計並交付可擴展的資料平台、建置資料管道，並推動雲端/地端環境下的資料搬遷，以銜接AI分析應用落地。</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p7ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>資深數據工程師 Senior Data Engineer -集團徵才-數據科技 (數數發中心, DDT)_I00015418</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>國泰金控_國泰金融控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>金融控股業</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市信義區 </t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 跟踪新興技術和行業趨勢，並提供相應的技術建議和改進方案。
+[團隊文化]
+- 團隊特色：我們是數據分析團隊，專注在數據創新、商業分析、資料探索。重視團隊橫向溝通，樂於相互學習也樂於分享。
+- 團隊目標：配合數位科技發展目標，開發可落地之新興技術或</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/87vsz</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>20260808</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>AI醫療資料工程師（Medical AI Data Engineer）</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>杏創生物科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>藥品／化妝品及清潔用品零售業</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>台北市中山區 新生北路一段66號4樓</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>月薪 48,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+工作內容
+1. 協助整理細胞檢測資料與臨床資料
+2. 建立細胞檢測資料庫與管理系統
+3. 協助將Flow Cytometry數據自動化匯入系統
+4. 協助建立AI細胞檢測知識庫
+5. 串接AI工具，協助自動產生檢測報告
+6. 協助開發醫療數據</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/88ifz</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>數據工程師｜打造零售界的神級Data Build</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>統一資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路155號8F~10F</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>你是資料界的打怪高手嗎？
+我們正在尋找一位能將數據煉金的工程師，一起升級零售產業的數據系統，從地端到雲端，穩定輸出、精準命中！
+這份工作不只是 coding，更是策略規劃、技術架構與商業價值的 combo 技。
+如果你喜歡優化效能、挑戰架構、解任</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4bma8</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ETL資料工程師</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>緯德科技股份有限公司 (TechLink Corporation)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號8F-13</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>- 熟悉資料庫之SQL語法執行ETL資料轉換作業(ETL Job Developing、IBM DataStage、Informatica PowerCenter、Microsoft SSIS、Trinity)實務經驗1年以上。
+- 熟悉資料庫安</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5e9ei</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>資料工程師 (BI)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>(本職務主要為技術工作而非單純的數據分析)
+1.  商業智慧(BI)專案需求訪談、系統分析並製作系統需求規格書文件
+2.  撰寫整合測試計畫書、測試案例、準備測試資料及測試
+3.  Metadata 中介層設計、Dashboard、Report設</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/37tef</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>AI 原生資料工程師</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>104人力銀行_一零四資訊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>新北市新店區 寶中路119號之一10樓(231)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>月薪 65,000元以上</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>一、協助 AP 遷移與營運
+  1. 將運作於 legacy 資料湖上的 APs 遷移到湖倉上。
+    - 會掌握到支援實際產品、基於 AWS 的開發生命週期及實務 CI/CD 流水線。
+    - 可參與 Databricks 資料應用程式的</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91l06</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>系統分析師 數據工程師</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>智遊旅程股份有限公司</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>桃園市中壢區 環北路</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>月薪 60,000元以上</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>PBKDF2、AES等。
+程式上版、版本控制。
+金流串接。
+規劃執行軟體架構及模組之開發設計，並控管軟體設計進度。
+規劃、執行與維護量產的應用程式。
+協助研發軟體新技術與新工具。
+進行軟體之測試與修改。
+具溝通協調能力，能與UI、PM、工程師等相互配合</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pxmp</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>20260808</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>軟體工程師</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>泰坦分子生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 生醫園區</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>月薪 60,000元以上</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>我們正在開發新一代快速分子診斷設備，需要一位對「軟體＋UI＋資料分析＋硬體整合」有興趣的工程師，參與從儀器控制、使用者介面到檢測資料分析的完整產品開發。
+1. 負責分子診斷儀器之軟體與使用者介面（UI）開發。
+2. 設計及開發儀器操作流程、檢測</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94mp9</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>【Data Engineer】 資料工程師</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>新加坡商昇新科技股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞湖街58號5樓</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>我們正處於數據架構升級的關鍵階段。尋找一位數據工程專家與我們共同重新定義數據流。
+你將負責冷熱數據分離架構的落地，並優化我們的 Data Warehouse 架構，確保在海量數據環境下，數據依然能兼具查詢效能與成本。
+【你將面臨的核心技術挑戰】</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x352</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>資料整合副工程師</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>台灣美日先進光罩股份有限公司</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>半導體製造業</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>新竹市 力行路2號1樓(300)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>月薪 33,000元以上</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>IQC team：
+✓客戶資料下載及文件彙整
+✓進案資訊異常分析及回饋
+✓生產管理系統資料輸入及檢查
+✓客戶資料異動的辨別與解讀
+TP1 team：
+✓光罩資料轉檔
+✓提供光罩檢驗資料
+✓依照需求提供Remote JDV資料
+✓支援異地工廠的光罩</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/2om9y</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>20260807</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>資料科學工程師</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>基士德環科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>機械器具批發業</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>高雄市鼓山區 民利街19號</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 進行特徵工程、趨勢分析、時序資料分析與加藥反應關係建模。
+3. 開發規則式、統計式或機器學習式控制模型，支援自動調節機制。
+4. 建立數據回放、模擬測試、模型穩定性評估與現場成效驗證流程。
+5. 與後端工程師協作完成模型部署與系統整合。
+6. 產出</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/93pop</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>數據工程師－B10B</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>精誠資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路258巷2號7樓</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1. 設計、構建和維護資料庫與數據倉儲系統，包括數據抽取、轉換、加載(ETL)流程、數據變更擷取設計、和資料庫結構設計等。
+ 2. 協助業務單位建構數據中台(Data Fabric)，制定數據抽象化結構，透過數據虛擬化平台(Data</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92x29</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據應用工程師) – (數數發中心, DDT)_I00020717</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+* 目標成果導向：重視成果並具合作互助精神
+* 積極主動、持續進步：樂於學習與自我成長
+* 熱愛數據、對技術充滿熱忱：積極探索與應用新技術
+【工作內容】
+資料工程的世界千變萬化，以下是你的任務指南：
+1. 數據蒐集與處理，接觸各種資料來源，進行</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n8v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>資料工程師 (資料治理/ETL)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1. 使用 ETL工具開發或是資料庫/資料表系統相關之程式設計及開發
+2. 依規格設計開發包含 SQL Script 以及 Store Procedure 等對資料進行處理的程式，並進行UT測試，撰寫驗證報告
+3. 資料管理與處理相關專案之需求訪</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/81zdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>20260806</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>AI 研究工程師 AI Research Engineer</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>大拇哥證券投資顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段95號10樓</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>、深度學習等技術，設計端到端的數據分析流程，產出可直接支援投資決策的洞察
+主導數據策略,包含數據來源評估、特徵工程方法論、模型效能追蹤機制
+前沿AI技術落地
+深度應用生成式AI、RAG、Prompt Engineering、Agentic AI等技</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94jr8</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>資料工程師 (資料治理/資料倉儲 DW)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>(本職務主要為技術專長的工作)
+1.  資料倉儲系統之程式設計及開發
+2.  負責專案之程式開發與測試及Code review；包含撰寫SQL/SP及使用ETL工具對資料進行處理、建置資料倉儲，並進行UT測試，撰寫驗證報告
+3.   配合專案需求</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/74xkx</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>軟體工程師 (Junior Software Engineer)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>愛訊電網科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>電信相關業</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>台北市中正區 衡陽路51號11樓之4</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>【關於這個職位】
+我們正在打造下一代電信核心應用，尋找能與我們一起定義未來電信軟體服務的工程師。
+在這裡，您不只是開發功能，而是參與設計高效能、可擴充、具商業價值的電信平台。
+您的程式將直接影響數百萬用戶的網路體驗。
+您會與專業技術團隊、架構師</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94jmz</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>半導體FAE工程師 ※產能增加擴大召募</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>奇鼎科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>精密儀器相關製造業</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>新竹縣湖口鄉 鳳山工業區鳳工二街86號</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 針對客戶端工程師進行產品操作、測試與規格說明
+ </t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92nuz</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>20260731</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>AW0810-資料平台工程師</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>啟碁科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>通訊機械器材相關業</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>新竹縣寶山鄉 園區二路20號</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>你用軟體工程的思維，重新定義數據維運。
+【工作內容說明 | 資料平台工程師】
+本職位強調「以軟體工程驅動平台演進」，你將參與以下核心領域：
+•資料工程與自動化開發： 
+1.負責開發高品質、具備容錯能力的 ETL / ELT 資料管線 (data</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8zqeh</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer【數位數據發展本部】</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>東南旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段60號</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>月薪 60,000元以上</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>統性整合資料支撐分析與AI應用的發展
+●	建置優化Data Pipeline，並建立資料品質監控管理機制，確保資料品質和效率
+●	與DA / DS 協作，開發實作數據 / AI產品，參與模型的部署上線與維運
+●	協作工程師設計大規模資料遷移，參與</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tbys</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>20260721</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>資料工程師 (竹科)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>富采光電股份有限公司 (原為晶元光電及隆達電子)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>新竹市 力行路21號</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>【資訊中心】
+在富采，資訊中心涵蓋智慧製造、AI 應用、網頁與系統開發、ERP與資訊安全等關鍵領域，
+驅動企業數位轉型，為富采建構智慧化、數據化與可擴展的營運發展。
+【工作內容】
+1.設計並維護數據治理平台、資料商城。
+2.設計、開發和維護可擴</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7csd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>產品三部 | 資料工程師(高雄)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>騰雲科技服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中華四路45號2樓</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>✅ 工作內容｜你會負責的任務
+1.數據建模：負責設計與維護 MDP 平台的資料模型，確保能有效支撐財務、銷售、行為等多維度主題數據。
+2.ETL 流程開發：配合使用 ETL 工具，撰寫高效能的 T-SQL 邏輯進行數據清洗、轉換與載入。
+3.效能</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xvzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市萬華區 </t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>【職務需求】
+1. 以 Data Engineering 為主，包含 hands-on data pipeline、ETL、data modeling、以及上游系統整合經驗。
+2. 需具備資料整合、資料品質與資料模型設計能力。
+3. 熟悉</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>20260727</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>聯樂數位行銷股份有限公司</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段285號4樓</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1. 負責資料的雲端基礎架構設計與演進，涵蓋資料流、整合處理、監控狀態等。
+2. 開發和串接API，提供穩定、可重複使用的資料服務。。
+3. 兼顧業務成長與工程實作需求，將資料相關能力平台化，提供穩定、可重複使用的基礎服務。
+4.</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92g11</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>【台中】資料工程師</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>敦謙國際智能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>台中市西區 國泰金融大樓(台中市西區英才路 530 號) 24 樓</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 90,000元</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>職務工作內容：
+營運策略系統 (RMS)
+透過資料分析、資料探勘和數據處理技術，為旅宿提供精準的營運決策依據。
+建模預測，根據歷史銷售資料，建立銷售量、住宿率等預測模型，為旅宿決策的制定提供參考。
+協助開發專為旅宿設計的智能客服機器人。
+職務需</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/75oc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>20260810</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師 (桃園龜山近林口長庚)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>桃園市龜山區 頂湖路33號 (近林口長庚)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>職務影響力
+本職位以資料工程與分析平台建設為核心，負責打造穩定、可擴展且可維運的工程數據基礎設施，作為工程與研發團隊進行數據決策的關鍵支撐。透過提升資料管道品質、系統自動化與整體擴展性，使資料分析工程師與工程團隊能在一致且可信的數據基礎上，規模化</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wzpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據架構工程師) – (數數發中心, DDT)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>【關於我們】
+我們是國泰產險的資料科學（DS）團隊，使命在於持續進化數據應用，創造並釋放數據價值。目前正在藉由數據上雲、數據治理與 AI 技術應用，推動由底層架構到業務應用的全端數據生態建構與 AI 轉型準備。
+我們尋找認同以下團隊文化的夥伴：</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8opms</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>AI 提示工程師（Prompt Engineer）</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>台灣骨王生技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>醫療器材製造業</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>台中市大雅區 科雅路41號2樓</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>AI 提示工程師（Prompt Engineer）
+地點：台中市／台中科學園區
+部門：研發部
+職位性質：全職
+職務說明
+我們正在尋找一位具備語言模型理解與應用能力，並能結合提示工程與 Python 開發技能的 AI 提示工程師，加入公司產品開</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8r08j</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>數據工程師（Data Engineer）</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>創代科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路101號10樓</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>定性。
+- 運用 Airflow、dbt 等工具，設計並優化高效、可觀測（Observable）的現代化資料管線。
+- 與機器學習工程師合作，建置穩定可靠的機器學習資料管線（ML Pipeline），支援模型訓練、部署與推論流程。
+- 參與資料湖倉</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ys29</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>數據工程師 (AI演算開發)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>悠由數據應用股份有限公司</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>其他專業／科學及技術業</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞光路258巷55-1號4樓</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 資料工程師
+【工作內容】
+1.	資料處理
+•處理衛星影像與時間序列空間資料
+•進行影像前處理、切片、特徵計算
+2.	Data Pipeline建構
+•設計並實作可擴展的資料管線（ETL / ELT）
+•整合影像資料、氣象資料、IoT 或其他外</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pqo4</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>可樂旅遊旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段90號12樓</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>資料運用並創造商業價值，並積極探索 AI 技術，提升整體營運效率與決策品質。
+【工作內容】
+1. 設計、開發與維護數據流程，打造穩定且高效的數據基礎架構
+2. 使用 Python 進行數據清理、轉換與處理
+3. 將數據處理流程自動化，並協助部署至雲</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/853np</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>20260809</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>知名SI廠核心技術團隊招募｜大型政府專案｜資料治理工程師｜105CC</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>萬寶華企業管理顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路2段105號13樓</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Job Description： 資料治理工程師負責規劃與落實企業資料治理架構，包含資料分類分級、存取控管、資料保護與合規監管，確保企業資料在全生命週期中安全、可控且可稽核。
+技術需求與技能：
+1. 熟悉資料治理與法規（Data</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92wqh</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>數據工程師｜AI產業｜新創｜Python｜歡迎新鮮人與資深開發者</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>睿思智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>新北市板橋區 中山路2段443巷77號10樓</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>最佳夥伴。未來也將持續擴展Neuro家族，讓AI應用更親民、更普及。
+如果你喜歡學習、願意動手做事，歡迎加入我們，一起努力成長，創造更多可能！
+【主要任務】
+1. 與資料科學家、雲端架構師、資料分析師及專案經理密切合作，提供高品質的雲端數據服務給</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xq4h</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>20260428</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>[ Python ] Senior Data Engineer 資料工程師  #Data &amp; AI  #ACT年度敏捷組織</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>炬識科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>台北市中山區 長安東路一段23號3樓</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Athemaster 以 MetaRoots 與 DQSentry 為核心，服務金融與零售企業，打造高擴充性的資料平台與品質監控框架，從 DataOps 到 AI 應用，挑戰真實企業級資料環境。
+▎你想知道的 Athemaster：
+請</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7kabt</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>【資訊技術】數據工程師</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>中華電信關係企業_神腦國際企業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>電子通訊／電腦週邊零售業</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>新北市新店區 中正路531號(總公司)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>具備撰寫SQL Script與Stored Procedure的實務經驗。
+•熟悉資料庫設計原則，能夠進行資料查詢優化及結構調整。
+加分條件
+•至少3年以上數據工程相關經驗，並能展示數據管道或數據平台的相關專案成果。
+•有使用AWS、Azure、</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mgwd</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>20260803</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>P7-Python資料工程師</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>意藍資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>台北市中正區 杭州北路26號12樓 (新光華山金融中心)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>月薪 35,000 ~ 45,000元</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>本公司是國內搜尋及語意分析市占率最高的廠商，專注研發非結構資料之數據處理，尋找熟悉Python及物件導向設計的人才加入。工作主要為開發與維運資料產線，搜集語料、資料儲存處理，並提供API服務供下游服務使用。
+工作內容如下：
+- 資料搜集程式開發</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7csnw</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>20260804</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>DBA資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>立視科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>多媒體傳播相關業</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>台北市松山區 八德路四段760號6樓</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1. 負責 Amazon RDS for Oracle、MariaDB、MongoDB Atlas、CloudSQL 等資料庫之建置、管理與維運。
+2. 監控資料庫效能、容量及系統資源，持續進行效能最佳化。
+3. 分析 Slow Query、</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/948ou</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>20260730</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>D21-資料工程師(DE)_旅遊科技部_數據營運組</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>雄獅資訊科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路151號</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>義技術方向的資深工程師加入，以 AI 輔助開發加速交付、強化資料平台能力，同時在數據中台的基礎上打造 AI 應用可信賴的資料服務基石，你將深度參與：
+•	以 AI 輔助為核心工作方式，重塑資料團隊的開發與交付模式。
+•	設計並建置可擴展的大數據資料</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ppdw</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
